--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 01.02.2025 11:35:11</t>
+    <t>Период: на 14.10.2025 15:55:18</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,24 +62,33 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
@@ -89,7 +98,16 @@
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Какао-порошок 100г/40 УБ</t>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
   </si>
   <si>
     <t>ДОБАВКИ</t>
@@ -101,10 +119,19 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желатин УБ 25г /42шт</t>
+  </si>
+  <si>
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт</t>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
@@ -134,9 +161,15 @@
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
@@ -167,16 +200,13 @@
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
-    <t>Суміш прянощів Італійські трави УБ 10г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Часник гранульований сушений УБ 15г /42шт</t>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт АКЦІЯ ВІП</t>
@@ -206,7 +236,7 @@
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Перець духм"яний УБ 20г /22шт</t>
+    <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
@@ -215,9 +245,18 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
@@ -227,55 +266,88 @@
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>РОШЕН</t>
   </si>
   <si>
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт ДС</t>
-  </si>
-  <si>
-    <t>БАТОН ROSHEN з начинкою 43г/180</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г/180 шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон мол-шок карамель 40г/180/30</t>
-  </si>
-  <si>
-    <t>Батон мол-шок крем-брюле 43г/180/30</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN Toffler з начинкою ВКФ 41г /180шт</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN Toffler з начинкою ВКФ 41г /180шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -308,18 +380,27 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -329,33 +410,57 @@
     <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
+    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>KONAFETTO з кокосовою начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з молочною начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -371,48 +476,45 @@
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers горіх ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
+    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Wafers какао ККФ 72г /22шт AR /</t>
+  </si>
+  <si>
+    <t>Wafers какао ККФ 72г /22шт AR /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Wafers молоко ВКФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -425,27 +527,15 @@
     <t>Beri РЦ 180г /12шт</t>
   </si>
   <si>
-    <t>Beri РЦ 180г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
-    <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Bonny-Fruit цитрусовий мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
-    <t>Bonny-Fruit цитрусовий мікс ВКФ 200г /18шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Bonny-Fruit ягідний мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
-    <t>Bonny-Fruit ягідний мікс ВКФ 200г /18шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
@@ -455,9 +545,6 @@
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
-    <t>Milky Splash РЦ 150г /12пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Mintex+ Berry зі смаком лісових ягід та ментолу ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -467,7 +554,13 @@
     <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
@@ -476,7 +569,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
@@ -485,6 +578,9 @@
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -497,6 +593,9 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -506,12 +605,39 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -521,12 +647,21 @@
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -536,9 +671,66 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -548,6 +740,12 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -557,6 +755,12 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -566,6 +770,18 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -575,6 +791,15 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -584,6 +809,9 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -593,6 +821,9 @@
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -602,7 +833,10 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
@@ -611,6 +845,9 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -620,6 +857,9 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -629,6 +869,9 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -638,40 +881,40 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
-    <t>Бім-Бом РЦ 200г /11шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
-    <t>Джеллі РЦ 200г /13шт АКЦІЯ ВІП 1</t>
+    <t>Джеллі РЦ 200г /13шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
+    <t>Льодяник мікс РЦ 200г /24шт /АКЦИЯ ВІП</t>
+  </si>
+  <si>
     <t>Молочна крапля РЦ 150г /12шт</t>
   </si>
   <si>
-    <t>Молочна крапля РЦ 150г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Рошен евкаліпт-ментол РЦ 200г /12шт</t>
   </si>
   <si>
-    <t>Рошен евкаліпт-ментол РЦ 200г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Шалена бджілка ВКФ 200г /12шт</t>
   </si>
   <si>
-    <t>Шалена бджілка ВКФ 200г /12шт АКЦІЯ ВІП</t>
+    <t>Шалена бджілка РЦ 200г /12шт</t>
+  </si>
+  <si>
+    <t>Шалена бджілка РЦ 200г /12шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
@@ -680,13 +923,13 @@
     <t>Beri РЦ 1кг /8пак /</t>
   </si>
   <si>
-    <t>CoffeeLike ВКФ 1кг /7пак</t>
+    <t>Coconut КрКФ 1кг /7пак</t>
   </si>
   <si>
     <t>CoffeeLike ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Fudgenta ВКФ 0.785кг /9пак</t>
+    <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
@@ -695,6 +938,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
@@ -704,6 +950,9 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
+    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -752,7 +1001,7 @@
     <t>Карамелькино КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+    <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
@@ -782,13 +1031,19 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт ДС</t>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
@@ -803,9 +1058,15 @@
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -815,13 +1076,22 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 352г /7шт</t>
+  </si>
+  <si>
     <t>Київ вечірній ККФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 352г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній Новий Рік ККФ 176г /7шт</t>
+    <t>Київ вечірній ККФ 176г /7шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Стріла Подільска 200г/10</t>
@@ -830,6 +1100,42 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /28шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -848,18 +1154,15 @@
     <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -881,6 +1184,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -890,34 +1199,37 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою вишня-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао ККФ 180г /28шт UA FP</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /35шт UA</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою чорниця-крем ККФ 180г /28шт</t>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
@@ -929,52 +1241,133 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт UA</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з шоколадною начинкою ККФ 235г /14шт</t>
+    <t>ПОДАРУНКИ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ 2026</t>
+  </si>
+  <si>
+    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
+  </si>
+  <si>
+    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
+  </si>
+  <si>
+    <t>Н/п №2 26 Новорічна сумочка РЦ 330г /8шт</t>
+  </si>
+  <si>
+    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №5 26 Ведмедик Roshen РЦ 426г /12шт</t>
+  </si>
+  <si>
+    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №9 26 Різдвяний вінок РЦ 598г /6шт</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
-    <t>Candy Nut м"яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+    <t>Boo! Bear РЦ 1кг /5пак</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Hola! Granola РЦ 0.5кг /8пак</t>
+    <t>Flaksi какао ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Flaksi кокос ККФ 500г /8шт</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт /</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ВКФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 2кг /5пак</t>
+    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
+    <t>Sorrento ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Winter dream ВКФ 1кг /5пак</t>
   </si>
   <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
@@ -995,22 +1388,19 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак АКЦІЯ</t>
+    <t>Ромашка ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
@@ -1028,73 +1418,115 @@
     <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
   </si>
   <si>
-    <t>Монблан РЦ 240г /15шт</t>
-  </si>
-  <si>
     <t>Монблан РЦ 240г /15шт /</t>
   </si>
   <si>
-    <t>Монблан РЦ 240г /15шт /АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ВІП 1</t>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
@@ -1103,12 +1535,15 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1118,19 +1553,28 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ВІП 1</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
@@ -1139,61 +1583,73 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /21шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
   </si>
   <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт АКЦІЯ ВІП 1</t>
+    <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ВІП 1</t>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
@@ -1202,34 +1658,31 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP /</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA АКЦІЯ</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
@@ -1241,13 +1694,19 @@
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
+  </si>
+  <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ Цінова</t>
+    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
@@ -1256,10 +1715,31 @@
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen зимовий ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Набір Зимові Друзі 3х20 РЦ 60г /22шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1483,6 +1963,15 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1502,7 +1991,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C414"/>
+  <dimension ref="C574"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1567,7 +2056,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>508</v>
+        <v>994</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1575,7 +2064,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>540421</v>
+        <v>1039404</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1583,7 +2072,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>93475</v>
+        <v>220903</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1591,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>15686</v>
+        <v>27543</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1599,7 +2088,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2264</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1607,7 +2096,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>644</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1615,7 +2104,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>1492</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1623,7 +2112,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2658</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1631,39 +2120,39 @@
         <v>18</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>1102</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>644</v>
+      <c r="C20" s="16" t="n">
+        <v>3021</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
       <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>1810</v>
+      <c r="C21" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>634</v>
+      <c r="C22" s="16" t="n">
+        <v>2113</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>1774</v>
+      <c r="C23" s="11" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1671,15 +2160,15 @@
         <v>23</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>2664</v>
-      </c>
-    </row>
-    <row r="25" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B25" s="14" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="25" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>24497</v>
+      <c r="C25" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1687,15 +2176,15 @@
         <v>25</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>1426</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>21912</v>
+      <c r="C27" s="11" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1703,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>9</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1711,7 +2200,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>1137</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1719,7 +2208,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>13</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="2">
@@ -1727,23 +2216,23 @@
         <v>30</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>15351</v>
+        <v>89942</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>858</v>
+      <c r="C32" s="16" t="n">
+        <v>7707</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>137</v>
+      <c r="C33" s="16" t="n">
+        <v>52647</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1751,31 +2240,31 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1177</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>566</v>
+      <c r="C35" s="16" t="n">
+        <v>17177</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>863</v>
+      <c r="C36" s="16" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>151</v>
+      <c r="C37" s="16" t="n">
+        <v>4640</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1783,55 +2272,55 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>280</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="40" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B40" s="15" t="s">
+      <c r="C39" s="16" t="n">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="40" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B40" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>860</v>
+      <c r="C40" s="12" t="n">
+        <v>26512</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>129</v>
+      <c r="C41" s="16" t="n">
+        <v>1489</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>2219</v>
+      <c r="C42" s="11" t="n">
+        <v>332</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>525</v>
+      <c r="C43" s="16" t="n">
+        <v>1353</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="n">
-        <v>1003</v>
+      <c r="C44" s="11" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1839,31 +2328,31 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>519</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>710</v>
+      <c r="C46" s="16" t="n">
+        <v>1018</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C47" s="16" t="n">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>206</v>
+        <v>590</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1871,7 +2360,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>800</v>
+        <v>986</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1879,7 +2368,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>716</v>
+        <v>958</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1887,7 +2376,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>773</v>
+        <v>817</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1895,7 +2384,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>50</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1903,7 +2392,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="16" t="n">
-        <v>1110</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1911,15 +2400,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B55" s="14" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="12" t="n">
-        <v>37941</v>
+      <c r="C55" s="16" t="n">
+        <v>1650</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1927,7 +2416,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>536</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1935,7 +2424,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>1361</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1943,15 +2432,15 @@
         <v>57</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="3">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>2044</v>
+      <c r="C59" s="11" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1959,23 +2448,23 @@
         <v>59</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>3679</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>1216</v>
+      <c r="C61" s="11" t="n">
+        <v>827</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>2011</v>
+      <c r="C62" s="11" t="n">
+        <v>861</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1983,7 +2472,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>1524</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -1991,15 +2480,15 @@
         <v>63</v>
       </c>
       <c r="C64" s="16" t="n">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="65" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B65" s="15" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="65" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B65" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>2771</v>
+      <c r="C65" s="12" t="n">
+        <v>76906</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2007,71 +2496,71 @@
         <v>65</v>
       </c>
       <c r="C66" s="16" t="n">
-        <v>18042</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>749</v>
+      <c r="C67" s="16" t="n">
+        <v>3371</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>104</v>
+      <c r="C68" s="16" t="n">
+        <v>1786</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>395</v>
+      <c r="C69" s="16" t="n">
+        <v>3150</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B71" s="13" t="s">
+      <c r="C70" s="16" t="n">
+        <v>10427</v>
+      </c>
+    </row>
+    <row r="71" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="12" t="n">
-        <v>446946</v>
-      </c>
-    </row>
-    <row r="72" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B72" s="14" t="s">
+      <c r="C71" s="16" t="n">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="72" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="12" t="n">
-        <v>130437</v>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C72" s="16" t="n">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>29933</v>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="true" outlineLevel="3">
+        <v>5197</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C74" s="16" t="n">
-        <v>1620</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2079,15 +2568,15 @@
         <v>74</v>
       </c>
       <c r="C75" s="16" t="n">
-        <v>12668</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="16" t="n">
-        <v>2340</v>
+      <c r="C76" s="11" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2095,15 +2584,15 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="true" outlineLevel="3">
+        <v>21707</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>5400</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2111,79 +2600,79 @@
         <v>78</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>12123</v>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="true" outlineLevel="3">
+        <v>5116</v>
+      </c>
+    </row>
+    <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="true" outlineLevel="3">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>22266</v>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C81" s="11" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+      <c r="C82" s="11" t="n">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B83" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="16" t="n">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B84" s="15" t="s">
+      <c r="C83" s="12" t="n">
+        <v>818501</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C84" s="12" t="n">
+        <v>53891</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>14973</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C85" s="11" t="n">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="16" t="n">
-        <v>15074</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B87" s="14" t="s">
+      <c r="C86" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="12" t="n">
-        <v>4799</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C87" s="11" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>504</v>
+      <c r="C88" s="16" t="n">
+        <v>10800</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2191,7 +2680,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2199,183 +2688,183 @@
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>41</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="16" t="n">
-        <v>1003</v>
+      <c r="C91" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C92" s="16" t="n">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+        <v>-229</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C96" s="16" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B99" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="12" t="n">
-        <v>39279</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C99" s="16" t="n">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C101" s="16" t="n">
+        <v>9790</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
       <c r="C102" s="16" t="n">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C103" s="16" t="n">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="16" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="16" t="n">
-        <v>4471</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>15106</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C108" s="11" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C109" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B111" s="15" t="s">
+      <c r="C110" s="16" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B111" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>70</v>
+      <c r="C111" s="12" t="n">
+        <v>10165</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>96</v>
+      <c r="C112" s="16" t="n">
+        <v>1496</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2383,15 +2872,15 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>118</v>
+        <v>64</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="11" t="n">
-        <v>625</v>
+      <c r="C114" s="16" t="n">
+        <v>1140</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2399,15 +2888,15 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>542</v>
+        <v>939</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="11" t="n">
-        <v>412</v>
+      <c r="C116" s="16" t="n">
+        <v>2204</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2415,7 +2904,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>625</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2423,23 +2912,23 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>50</v>
+        <v>859</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>99</v>
+      <c r="C119" s="16" t="n">
+        <v>1823</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="16" t="n">
-        <v>2957</v>
+      <c r="C120" s="11" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2447,15 +2936,15 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="16" t="n">
-        <v>1167</v>
+      <c r="C122" s="11" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2463,23 +2952,23 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="true" outlineLevel="3">
       <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="16" t="n">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="125" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B125" s="15" t="s">
+      <c r="C124" s="11" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B125" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>407</v>
+      <c r="C125" s="12" t="n">
+        <v>212705</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2487,15 +2976,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="127" ht="11" customHeight="true" outlineLevel="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2503,15 +2992,15 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>85</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="16" t="n">
-        <v>1490</v>
+      <c r="C129" s="11" t="n">
+        <v>581</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2519,7 +3008,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2527,7 +3016,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2535,7 +3024,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>504</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2543,23 +3032,23 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B134" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="12" t="n">
-        <v>60599</v>
+      <c r="C134" s="11" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>53</v>
+      <c r="C135" s="16" t="n">
+        <v>52820</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2567,23 +3056,23 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>352</v>
+      <c r="C137" s="16" t="n">
+        <v>50812</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
       <c r="B138" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="11" t="n">
-        <v>317</v>
+      <c r="C138" s="16" t="n">
+        <v>36600</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2591,15 +3080,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>516</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>315</v>
+      <c r="C140" s="16" t="n">
+        <v>55179</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2607,7 +3096,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>563</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2615,15 +3104,15 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>202</v>
+        <v>725</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="16" t="n">
-        <v>1229</v>
+      <c r="C143" s="11" t="n">
+        <v>237</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2631,7 +3120,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>375</v>
+        <v>105</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2639,7 +3128,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2647,7 +3136,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2655,7 +3144,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>516</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2663,31 +3152,31 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>659</v>
+      <c r="C149" s="16" t="n">
+        <v>1461</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="11" t="n">
-        <v>54</v>
+      <c r="C150" s="16" t="n">
+        <v>1584</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="16" t="n">
-        <v>3162</v>
+      <c r="C151" s="11" t="n">
+        <v>409</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2695,7 +3184,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>342</v>
+        <v>633</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2703,7 +3192,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>211</v>
+        <v>18</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2711,7 +3200,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>342</v>
+        <v>302</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2719,15 +3208,15 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>42</v>
+        <v>349</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="16" t="n">
-        <v>3312</v>
+      <c r="C156" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2735,7 +3224,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="16" t="n">
-        <v>1911</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2743,7 +3232,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>327</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2751,15 +3240,15 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>568</v>
+        <v>544</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="16" t="n">
-        <v>2631</v>
+      <c r="C160" s="11" t="n">
+        <v>565</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2767,7 +3256,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>327</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2775,7 +3264,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>604</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2783,31 +3272,31 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>940</v>
+        <v>392</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>30</v>
+      <c r="C164" s="16" t="n">
+        <v>2706</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="16" t="n">
-        <v>1045</v>
+      <c r="C165" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>45</v>
+      <c r="C166" s="16" t="n">
+        <v>2490</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2815,15 +3304,15 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="168" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B168" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="168" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B168" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>539</v>
+      <c r="C168" s="12" t="n">
+        <v>88686</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2831,15 +3320,15 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>31</v>
+        <v>643</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
       <c r="B170" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="16" t="n">
-        <v>2924</v>
+      <c r="C170" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2847,7 +3336,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>342</v>
+        <v>362</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2855,15 +3344,15 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>261</v>
+        <v>158</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="16" t="n">
-        <v>1218</v>
+      <c r="C173" s="11" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2871,7 +3360,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>779</v>
+        <v>600</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2879,7 +3368,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>30</v>
+        <v>409</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2887,15 +3376,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>260</v>
+        <v>575</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="16" t="n">
-        <v>2661</v>
+      <c r="C177" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2903,7 +3392,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>342</v>
+        <v>245</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2911,7 +3400,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>131</v>
+        <v>360</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2919,7 +3408,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>277</v>
+        <v>102</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2927,7 +3416,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2935,15 +3424,15 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>85</v>
+        <v>337</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="16" t="n">
-        <v>3132</v>
+      <c r="C183" s="11" t="n">
+        <v>437</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2951,7 +3440,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>342</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2959,7 +3448,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>194</v>
+        <v>89</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2967,7 +3456,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>501</v>
+        <v>849</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2975,7 +3464,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>45</v>
+        <v>209</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2983,7 +3472,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>206</v>
+        <v>114</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -2991,7 +3480,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>451</v>
+        <v>264</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2999,7 +3488,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>30</v>
+        <v>598</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3007,23 +3496,23 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>280</v>
+        <v>324</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="16" t="n">
-        <v>3553</v>
+      <c r="C192" s="11" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>342</v>
+      <c r="C193" s="16" t="n">
+        <v>4791</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3031,15 +3520,15 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>97</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="16" t="n">
-        <v>1458</v>
+      <c r="C195" s="11" t="n">
+        <v>599</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3047,7 +3536,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3055,15 +3544,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>12</v>
+        <v>558</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="16" t="n">
-        <v>3094</v>
+      <c r="C198" s="11" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3071,7 +3560,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>342</v>
+        <v>154</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3079,15 +3568,15 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>147</v>
+        <v>196</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="16" t="n">
-        <v>1442</v>
+      <c r="C201" s="11" t="n">
+        <v>481</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3095,7 +3584,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>30</v>
+        <v>774</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3103,15 +3592,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>100</v>
+        <v>329</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="16" t="n">
-        <v>2841</v>
+      <c r="C204" s="11" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3119,7 +3608,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3127,7 +3616,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>173</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3135,7 +3624,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>25</v>
+        <v>602</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3143,7 +3632,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>479</v>
+        <v>428</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3151,15 +3640,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>333</v>
+        <v>750</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="16" t="n">
-        <v>2549</v>
+      <c r="C210" s="11" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3167,15 +3656,15 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>253</v>
+        <v>640</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="16" t="n">
-        <v>1016</v>
+      <c r="C212" s="11" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3183,7 +3672,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>454</v>
+        <v>790</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3191,7 +3680,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>253</v>
+        <v>120</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3199,39 +3688,39 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>314</v>
+        <v>40</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>97</v>
+      <c r="C216" s="16" t="n">
+        <v>1829</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="16" t="n">
-        <v>1956</v>
+      <c r="C217" s="11" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="16" t="n">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="219" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B219" s="14" t="s">
+      <c r="C218" s="11" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="219" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="12" t="n">
-        <v>30989</v>
+      <c r="C219" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3239,15 +3728,15 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>987</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="11" t="n">
-        <v>359</v>
+      <c r="C221" s="16" t="n">
+        <v>1705</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3255,7 +3744,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>834</v>
+        <v>185</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3263,7 +3752,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>432</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3271,15 +3760,15 @@
         <v>223</v>
       </c>
       <c r="C224" s="16" t="n">
-        <v>2559</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="11" t="n">
-        <v>44</v>
+      <c r="C225" s="16" t="n">
+        <v>8526</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3287,15 +3776,15 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>86</v>
+        <v>137</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="11" t="n">
-        <v>235</v>
+      <c r="C227" s="16" t="n">
+        <v>7623</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3303,15 +3792,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>357</v>
+        <v>110</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>733</v>
+      <c r="C229" s="16" t="n">
+        <v>1936</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3319,7 +3808,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="16" t="n">
-        <v>1035</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3327,7 +3816,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>759</v>
+        <v>52</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3335,7 +3824,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>595</v>
+        <v>393</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3343,7 +3832,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>468</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3351,7 +3840,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>190</v>
+        <v>761</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3359,15 +3848,15 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>164</v>
+        <v>372</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>546</v>
+      <c r="C236" s="16" t="n">
+        <v>1248</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3375,7 +3864,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>843</v>
+        <v>9</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3383,7 +3872,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>262</v>
+        <v>347</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3391,7 +3880,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>866</v>
+        <v>237</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3399,87 +3888,87 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>894</v>
+        <v>430</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="16" t="n">
-        <v>2436</v>
+      <c r="C241" s="11" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="16" t="n">
-        <v>1050</v>
+      <c r="C242" s="11" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="16" t="n">
-        <v>1267</v>
+      <c r="C243" s="11" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="16" t="n">
-        <v>1739</v>
+      <c r="C244" s="11" t="n">
+        <v>592</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="16" t="n">
-        <v>1350</v>
+      <c r="C245" s="11" t="n">
+        <v>825</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="16" t="n">
-        <v>1600</v>
+      <c r="C246" s="11" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="16" t="n">
-        <v>1097</v>
+      <c r="C247" s="11" t="n">
+        <v>869</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="16" t="n">
-        <v>2239</v>
+      <c r="C248" s="11" t="n">
+        <v>702</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="16" t="n">
-        <v>1181</v>
+      <c r="C249" s="11" t="n">
+        <v>542</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="16" t="n">
-        <v>2899</v>
+      <c r="C250" s="11" t="n">
+        <v>254</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3487,15 +3976,15 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="252" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B252" s="14" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="12" t="n">
-        <v>4209</v>
+      <c r="C252" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3503,7 +3992,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>579</v>
+        <v>36</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3511,7 +4000,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>687</v>
+        <v>65</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3519,23 +4008,23 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>370</v>
+        <v>213</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="11" t="n">
-        <v>192</v>
+      <c r="C256" s="16" t="n">
+        <v>1375</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="n">
-        <v>157</v>
+      <c r="C257" s="16" t="n">
+        <v>1051</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3543,7 +4032,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3551,7 +4040,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3559,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3567,7 +4056,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>609</v>
+        <v>428</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3575,7 +4064,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>238</v>
+        <v>84</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3583,7 +4072,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>194</v>
+        <v>238</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3591,7 +4080,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>121</v>
+        <v>550</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3599,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>226</v>
+        <v>281</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3607,7 +4096,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3615,7 +4104,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>147</v>
+        <v>214</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3623,7 +4112,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>10</v>
+        <v>308</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3631,31 +4120,31 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="270" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B270" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="12" t="n">
-        <v>27820</v>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C270" s="16" t="n">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="272" ht="22" customHeight="true" outlineLevel="3">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>16</v>
+        <v>308</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3663,7 +4152,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>146</v>
+        <v>36</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3671,15 +4160,15 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>169</v>
+        <v>892</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="16" t="n">
-        <v>1358</v>
+      <c r="C275" s="11" t="n">
+        <v>367</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3687,7 +4176,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>808</v>
+        <v>470</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3695,119 +4184,119 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>608</v>
+        <v>128</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="279" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C278" s="16" t="n">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="280" ht="22" customHeight="true" outlineLevel="3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="282" ht="22" customHeight="true" outlineLevel="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="15" t="s">
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="283" ht="22" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="284" ht="22" customHeight="true" outlineLevel="3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="285" ht="22" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="286" ht="22" customHeight="true" outlineLevel="3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="287" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C286" s="16" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>157</v>
+        <v>688</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="11" t="n">
-        <v>560</v>
+      <c r="C288" s="16" t="n">
+        <v>1128</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="11" t="n">
-        <v>671</v>
+      <c r="C289" s="16" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>70</v>
+      <c r="C290" s="16" t="n">
+        <v>1945</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="11" t="n">
-        <v>339</v>
+      <c r="C291" s="16" t="n">
+        <v>1512</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3815,15 +4304,15 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>272</v>
+        <v>433</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="16" t="n">
-        <v>2888</v>
+      <c r="C293" s="11" t="n">
+        <v>429</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3831,15 +4320,15 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>781</v>
+        <v>96</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="11" t="n">
-        <v>352</v>
+      <c r="C295" s="16" t="n">
+        <v>2087</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -3847,7 +4336,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>883</v>
+        <v>57</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3855,7 +4344,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="16" t="n">
-        <v>2045</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3863,7 +4352,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3871,15 +4360,15 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B300" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B300" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="C300" s="11" t="n">
-        <v>34</v>
+      <c r="C300" s="12" t="n">
+        <v>80578</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3895,15 +4384,15 @@
         <v>301</v>
       </c>
       <c r="C302" s="16" t="n">
-        <v>8283</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="11" t="n">
-        <v>846</v>
+      <c r="C303" s="16" t="n">
+        <v>3864</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3911,23 +4400,23 @@
         <v>303</v>
       </c>
       <c r="C304" s="16" t="n">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="306" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C305" s="16" t="n">
+        <v>5819</v>
+      </c>
+    </row>
+    <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3935,7 +4424,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>169</v>
+        <v>50</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3943,15 +4432,15 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B309" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="12" t="n">
-        <v>31018</v>
+      <c r="C309" s="11" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -3959,55 +4448,55 @@
         <v>309</v>
       </c>
       <c r="C310" s="16" t="n">
-        <v>2169</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="16" t="n">
-        <v>1338</v>
+      <c r="C311" s="11" t="n">
+        <v>273</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="16" t="n">
-        <v>2706</v>
+      <c r="C312" s="11" t="n">
+        <v>462</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="11" t="n">
-        <v>554</v>
+      <c r="C313" s="16" t="n">
+        <v>2616</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>809</v>
+      <c r="C314" s="16" t="n">
+        <v>1971</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="11" t="n">
-        <v>445</v>
+      <c r="C315" s="16" t="n">
+        <v>3136</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="11" t="n">
-        <v>224</v>
+      <c r="C316" s="16" t="n">
+        <v>1226</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4015,7 +4504,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="16" t="n">
-        <v>1002</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4023,95 +4512,95 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>775</v>
+        <v>932</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="11" t="n">
-        <v>435</v>
+      <c r="C319" s="16" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="11" t="n">
-        <v>711</v>
+      <c r="C320" s="16" t="n">
+        <v>1381</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>977</v>
+      <c r="C321" s="16" t="n">
+        <v>1132</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>279</v>
+      <c r="C322" s="16" t="n">
+        <v>2714</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>239</v>
+      <c r="C323" s="16" t="n">
+        <v>3035</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="11" t="n">
-        <v>181</v>
+      <c r="C324" s="16" t="n">
+        <v>4836</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C325" s="16" t="n">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>164</v>
+      <c r="C326" s="16" t="n">
+        <v>3655</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="11" t="n">
-        <v>188</v>
+      <c r="C327" s="16" t="n">
+        <v>4167</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="11" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C328" s="16" t="n">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>211</v>
+      <c r="C329" s="16" t="n">
+        <v>3741</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4119,15 +4608,15 @@
         <v>329</v>
       </c>
       <c r="C330" s="16" t="n">
-        <v>9980</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>24</v>
+      <c r="C331" s="16" t="n">
+        <v>3181</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4135,7 +4624,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="16" t="n">
-        <v>4573</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4143,15 +4632,15 @@
         <v>332</v>
       </c>
       <c r="C333" s="16" t="n">
-        <v>1756</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="11" t="n">
-        <v>827</v>
+      <c r="C334" s="16" t="n">
+        <v>1821</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="2">
@@ -4159,7 +4648,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="12" t="n">
-        <v>2155</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4167,7 +4656,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>21</v>
+        <v>253</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4175,7 +4664,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>48</v>
+        <v>259</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4183,7 +4672,7 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>7</v>
+        <v>152</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4191,23 +4680,23 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>445</v>
+        <v>8</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="16" t="n">
-        <v>1634</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B341" s="14" t="s">
+      <c r="C340" s="11" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="12" t="n">
-        <v>115641</v>
+      <c r="C341" s="11" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4215,55 +4704,55 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="344" ht="22" customHeight="true" outlineLevel="3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="345" ht="22" customHeight="true" outlineLevel="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>3616</v>
-      </c>
-    </row>
-    <row r="346" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C345" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="347" ht="22" customHeight="true" outlineLevel="3">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="16" t="n">
-        <v>3785</v>
+      <c r="C348" s="11" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="349" ht="22" customHeight="true" outlineLevel="3">
@@ -4271,15 +4760,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4287,23 +4776,23 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>216</v>
+        <v>148</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="16" t="n">
-        <v>1379</v>
+      <c r="C352" s="11" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="16" t="n">
-        <v>2198</v>
+      <c r="C353" s="11" t="n">
+        <v>297</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4311,151 +4800,151 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="355" ht="22" customHeight="true" outlineLevel="3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="357" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="359" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B360" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B360" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="16" t="n">
-        <v>4393</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C360" s="12" t="n">
+        <v>53519</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="364" ht="22" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="11" t="n">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C365" s="16" t="n">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
       <c r="C368" s="16" t="n">
-        <v>9947</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="16" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C371" s="16" t="n">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="16" t="n">
-        <v>4259</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="373" ht="22" customHeight="true" outlineLevel="3">
@@ -4463,15 +4952,15 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>787</v>
+        <v>6</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4479,7 +4968,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>537</v>
+        <v>216</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4487,7 +4976,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4495,15 +4984,15 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>2</v>
+        <v>318</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>990</v>
+      <c r="C378" s="16" t="n">
+        <v>1252</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="true" outlineLevel="3">
@@ -4511,23 +5000,23 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C380" s="16" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>216</v>
+        <v>11</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
@@ -4535,15 +5024,15 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>24</v>
+        <v>181</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="16" t="n">
-        <v>3153</v>
+      <c r="C383" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="true" outlineLevel="3">
@@ -4551,23 +5040,23 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>48</v>
+        <v>404</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="16" t="n">
-        <v>2536</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C385" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>256</v>
+        <v>864</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="true" outlineLevel="3">
@@ -4575,23 +5064,23 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>40</v>
+        <v>475</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
@@ -4599,7 +5088,7 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4607,15 +5096,15 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
       <c r="B392" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="C392" s="11" t="n">
-        <v>669</v>
+      <c r="C392" s="16" t="n">
+        <v>1348</v>
       </c>
     </row>
     <row r="393" ht="11" customHeight="true" outlineLevel="3">
@@ -4623,71 +5112,71 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>167</v>
+        <v>360</v>
       </c>
     </row>
     <row r="395" ht="11" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="16" t="n">
-        <v>3058</v>
+      <c r="C395" s="11" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="16" t="n">
-        <v>2431</v>
+      <c r="C396" s="11" t="n">
+        <v>445</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C397" s="16" t="n">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="16" t="n">
-        <v>2044</v>
+      <c r="C398" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C399" s="16" t="n">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="16" t="n">
-        <v>2318</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="16" t="n">
-        <v>1709</v>
+      <c r="C401" s="11" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="402" ht="11" customHeight="true" outlineLevel="3">
@@ -4695,7 +5184,7 @@
         <v>401</v>
       </c>
       <c r="C402" s="16" t="n">
-        <v>3762</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="403" ht="11" customHeight="true" outlineLevel="3">
@@ -4703,7 +5192,7 @@
         <v>402</v>
       </c>
       <c r="C403" s="16" t="n">
-        <v>4358</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
@@ -4711,31 +5200,31 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
     </row>
     <row r="405" ht="11" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="11" t="n">
-        <v>178</v>
+      <c r="C405" s="16" t="n">
+        <v>3746</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="11" t="n">
-        <v>50</v>
+      <c r="C406" s="16" t="n">
+        <v>9084</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="11" t="n">
-        <v>119</v>
+      <c r="C407" s="16" t="n">
+        <v>4656</v>
       </c>
     </row>
     <row r="408" ht="11" customHeight="true" outlineLevel="3">
@@ -4743,7 +5232,7 @@
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>353</v>
+        <v>194</v>
       </c>
     </row>
     <row r="409" ht="11" customHeight="true" outlineLevel="3">
@@ -4751,47 +5240,1327 @@
         <v>408</v>
       </c>
       <c r="C409" s="16" t="n">
-        <v>4067</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="16" t="n">
-        <v>12076</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
+      <c r="C410" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B411" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="16" t="n">
-        <v>11758</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
+      <c r="C411" s="12" t="n">
+        <v>14094</v>
+      </c>
+    </row>
+    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B412" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="C412" s="11" t="n">
+      <c r="C412" s="12" t="n">
+        <v>14094</v>
+      </c>
+    </row>
+    <row r="413" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B413" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="16" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B414" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="16" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B415" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="16" t="n">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B416" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="16" t="n">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B417" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="16" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B418" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="16" t="n">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B419" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="16" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B420" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="16" t="n">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B421" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="16" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B422" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="16" t="n">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="423" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B423" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B424" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="16" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B425" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="12" t="n">
+        <v>67589</v>
+      </c>
+    </row>
+    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="16" t="n">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="16" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="16" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="16" t="n">
+        <v>5125</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="16" t="n">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="437" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="11" t="n">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="438" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B438" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="11" t="n">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="439" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="440" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="11" t="n">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="441" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="442" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="443" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="11" t="n">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="444" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="11" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="16" t="n">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="446" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="16" t="n">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="447" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="16" t="n">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="449" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="451" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="16" t="n">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="16" t="n">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="453" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="11" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="454" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="455" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="11" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="457" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="458" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="11" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="16" t="n">
+        <v>12586</v>
+      </c>
+    </row>
+    <row r="460" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="461" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="16" t="n">
+        <v>5898</v>
+      </c>
+    </row>
+    <row r="462" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="16" t="n">
+        <v>7555</v>
+      </c>
+    </row>
+    <row r="463" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B463" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="16" t="n">
+        <v>3923</v>
+      </c>
+    </row>
+    <row r="464" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B464" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="16" t="n">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="465" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B465" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="19" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="466" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B466" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="467" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B467" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="468" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B468" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="469" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B469" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="470" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B470" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="12" t="n">
+        <v>231984</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B471" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="11" t="n">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="473" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B473" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="11" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="474" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B474" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="475" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B475" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="11" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="476" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B476" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B477" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C477" s="11" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B478" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C478" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B479" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C479" s="11" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="480" ht="33" customHeight="true" outlineLevel="3">
+      <c r="B480" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C480" s="16" t="n">
+        <v>9361</v>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B481" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="C481" s="11" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="482" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B482" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C482" s="11" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="483" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B483" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="C483" s="11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="484" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B484" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C484" s="16" t="n">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="485" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B485" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C485" s="11" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="486" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B486" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C486" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B487" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C487" s="16" t="n">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="488" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B488" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="C488" s="11" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="489" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B489" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C489" s="11" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="490" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B490" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="C490" s="16" t="n">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="491" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B491" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C491" s="11" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="492" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B492" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="C492" s="11" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="493" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B493" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C493" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B494" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="C494" s="16" t="n">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="495" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B495" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="C495" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="496" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B496" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="C496" s="11" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="497" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B497" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="C497" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="498" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B498" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="C498" s="11" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="499" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B499" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="C499" s="16" t="n">
+        <v>7329</v>
+      </c>
+    </row>
+    <row r="500" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B500" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="C500" s="11" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B501" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="C501" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="502" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B502" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="C502" s="16" t="n">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="503" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B503" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C503" s="11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="504" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B504" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C504" s="16" t="n">
+        <v>6649</v>
+      </c>
+    </row>
+    <row r="505" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B505" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="C505" s="11" t="n">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="506" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B506" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="C506" s="11" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="507" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B507" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C507" s="16" t="n">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="508" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B508" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C508" s="11" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B509" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C509" s="11" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="510" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B510" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="C510" s="16" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="511" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B511" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="C511" s="11" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="512" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B512" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C512" s="11" t="n">
         <v>216</v>
       </c>
     </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>17724</v>
+    <row r="513" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B513" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="C513" s="16" t="n">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="514" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B514" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="C514" s="11" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="515" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B515" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="C515" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="516" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B516" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="C516" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="517" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B517" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="C517" s="11" t="n">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="518" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B518" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C518" s="11" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="519" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B519" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="C519" s="11" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="520" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B520" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="C520" s="16" t="n">
+        <v>11658</v>
+      </c>
+    </row>
+    <row r="521" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B521" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="C521" s="11" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="522" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B522" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="C522" s="11" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="523" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B523" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="C523" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="524" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B524" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="C524" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="525" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B525" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="C525" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="526" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B526" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="C526" s="16" t="n">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="527" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B527" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="C527" s="11" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="528" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B528" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="C528" s="16" t="n">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="529" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B529" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="C529" s="11" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="530" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B530" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="C530" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="531" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B531" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="C531" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="532" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B532" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C532" s="11" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="533" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B533" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="C533" s="11" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="534" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B534" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C534" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="535" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B535" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="C535" s="16" t="n">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="536" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B536" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="C536" s="11" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="537" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B537" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="C537" s="11" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="538" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B538" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="C538" s="16" t="n">
+        <v>5352</v>
+      </c>
+    </row>
+    <row r="539" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B539" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="C539" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="540" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B540" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="C540" s="11" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="541" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B541" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="C541" s="11" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="542" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B542" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="C542" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="543" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B543" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="C543" s="11" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="544" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B544" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="C544" s="11" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="545" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B545" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="C545" s="11" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="546" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B546" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="C546" s="16" t="n">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="547" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B547" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="C547" s="11" t="n">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="548" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B548" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="C548" s="16" t="n">
+        <v>27099</v>
+      </c>
+    </row>
+    <row r="549" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B549" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C549" s="11" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="550" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B550" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C550" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="551" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B551" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="C551" s="11" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="552" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B552" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="C552" s="11" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="553" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B553" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="C553" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="554" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B554" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="C554" s="11" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="555" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B555" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="C555" s="16" t="n">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="556" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B556" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="C556" s="11" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="557" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B557" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C557" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="558" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B558" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="C558" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="559" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B559" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="C559" s="16" t="n">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="560" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B560" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="C560" s="11" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="561" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B561" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="C561" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="562" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B562" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C562" s="16" t="n">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="563" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B563" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="C563" s="11" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="564" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B564" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C564" s="16" t="n">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="565" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B565" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C565" s="11" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="566" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B566" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="C566" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="567" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B567" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="C567" s="12" t="n">
+        <v>100913</v>
+      </c>
+    </row>
+    <row r="568" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B568" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="C568" s="16" t="n">
+        <v>21735</v>
+      </c>
+    </row>
+    <row r="569" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B569" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="C569" s="16" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="570" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B570" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="C570" s="16" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="571" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B571" s="18" t="s">
+        <v>570</v>
+      </c>
+      <c r="C571" s="16" t="n">
+        <v>36330</v>
+      </c>
+    </row>
+    <row r="572" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B572" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="C572" s="16" t="n">
+        <v>21048</v>
+      </c>
+    </row>
+    <row r="573" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B573" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C573" s="16" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="574" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B574" s="18" t="s">
+        <v>573</v>
+      </c>
+      <c r="C574" s="16" t="n">
+        <v>15940</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="566">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 14.10.2025 15:55:18</t>
+    <t>Период: на 02.12.2025 15:35:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -65,7 +65,7 @@
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт</t>
@@ -74,9 +74,15 @@
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -98,7 +104,7 @@
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
@@ -137,12 +143,24 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -155,12 +173,18 @@
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -170,7 +194,7 @@
     <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт</t>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ</t>
   </si>
   <si>
     <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
@@ -188,12 +212,21 @@
     <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Суміш зелені УБ 10г /24шт</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -206,10 +239,16 @@
     <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт</t>
+  </si>
+  <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт АКЦІЯ ВІП</t>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Часник гранульований сушений УБ 15г /42шт АКЦІЯ</t>
   </si>
   <si>
     <t>СПЕЦІЇ</t>
@@ -224,6 +263,9 @@
     <t>Коріандр мелений УБ 20г /30шт</t>
   </si>
   <si>
+    <t>Коріандр мелений УБ 20г /30шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Куркума мелена УБ 15г /38шт</t>
   </si>
   <si>
@@ -239,15 +281,15 @@
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
+    <t>Перець духмяний УБ 20г /22шт</t>
+  </si>
+  <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
   </si>
   <si>
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
@@ -275,24 +317,24 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN Toffler з начинкою ВКФ 41г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN Toffler з начинкою ВКФ 41г /180шт АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -302,46 +344,34 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
@@ -350,6 +380,12 @@
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -386,6 +422,9 @@
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -398,9 +437,6 @@
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -410,22 +446,16 @@
     <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
   </si>
   <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>KONAFETTO з кокосовою начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
+    <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
     <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з молочною начинкою ВКФ 140г /15шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП</t>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
@@ -434,7 +464,7 @@
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
@@ -443,40 +473,46 @@
     <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП</t>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /АКЦИЯ ВИП</t>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers горіх ВКФ 216г /16шт</t>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Wafers горіх ВКФ 216г /16шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers горіх ККФ 216г /16шт</t>
+    <t>Wafers горіх ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
@@ -485,13 +521,13 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 72г /22шт AR /АКЦІЯ ВІП</t>
+    <t>Wafers какао ККФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
@@ -500,15 +536,21 @@
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 216г /16шт</t>
+    <t>Wafers кокос та мигдаль ВКФ 216г /16шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -521,12 +563,12 @@
     <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
-    <t>Beri РЦ 180г /12шт</t>
-  </si>
-  <si>
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
@@ -539,9 +581,6 @@
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 205г /12шт EU АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
@@ -557,9 +596,6 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -569,9 +605,6 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
@@ -590,10 +623,7 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
@@ -602,10 +632,7 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
@@ -617,7 +644,7 @@
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
@@ -629,9 +656,6 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -647,7 +671,7 @@
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
@@ -656,10 +680,7 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
@@ -671,9 +692,6 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -683,7 +701,7 @@
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
@@ -695,13 +713,19 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
@@ -710,7 +734,7 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
@@ -719,12 +743,6 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -740,9 +758,6 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -755,9 +770,6 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -767,10 +779,7 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
@@ -788,12 +797,6 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -806,22 +809,13 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
@@ -833,19 +827,19 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
@@ -857,7 +851,7 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
@@ -866,10 +860,7 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
@@ -878,30 +869,15 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Бім-Бом РЦ 200г /11шт</t>
-  </si>
-  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
-    <t>Джеллі РЦ 200г /13шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
-    <t>Льодяник мікс РЦ 200г /24шт /АКЦИЯ ВІП</t>
-  </si>
-  <si>
     <t>Молочна крапля РЦ 150г /12шт</t>
   </si>
   <si>
@@ -914,9 +890,6 @@
     <t>Шалена бджілка РЦ 200г /12шт</t>
   </si>
   <si>
-    <t>Шалена бджілка РЦ 200г /12шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
@@ -926,9 +899,15 @@
     <t>Coconut КрКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>CoffeeLike ВКФ 1кг /7пак</t>
+  </si>
+  <si>
     <t>CoffeeLike ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>CoffeeLike КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
@@ -950,9 +929,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -1004,6 +980,9 @@
     <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
   </si>
   <si>
@@ -1031,19 +1010,10 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Assortment Elegant 145г/8</t>
-  </si>
-  <si>
-    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
@@ -1058,13 +1028,13 @@
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
-    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦИЯ ВИП</t>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
   </si>
   <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
@@ -1091,12 +1061,6 @@
     <t>Київ вечірній ККФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 176г /7шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Стріла Подільска 200г/10</t>
-  </si>
-  <si>
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
@@ -1106,7 +1070,7 @@
     <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
   </si>
   <si>
-    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт АКЦІЯ ВІП</t>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>2 CRACK з шоколадною начинкою ККФ 190г /28шт</t>
@@ -1130,21 +1094,30 @@
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
   </si>
   <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Brownie з какао ККФ 152г /21шт</t>
   </si>
   <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
-    <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
+    <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
@@ -1154,7 +1127,7 @@
     <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт АКЦІЯ ВІП</t>
+    <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
@@ -1163,6 +1136,9 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -1172,9 +1148,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -1199,7 +1172,7 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ ВІП</t>
+    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
@@ -1208,6 +1181,9 @@
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
+    <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1256,27 +1232,12 @@
     <t>ПОДАРУНКИ 2026</t>
   </si>
   <si>
-    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
-  </si>
-  <si>
     <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
   </si>
   <si>
-    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
-  </si>
-  <si>
     <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
   </si>
   <si>
-    <t>Н/п №2 26 Новорічна сумочка РЦ 330г /8шт</t>
-  </si>
-  <si>
-    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
-  </si>
-  <si>
     <t>Н/п №5 26 Ведмедик Roshen РЦ 426г /12шт</t>
   </si>
   <si>
@@ -1298,12 +1259,12 @@
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
+    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1313,42 +1274,21 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
-    <t>Flaksi кокос ККФ 500г /8шт</t>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
   </si>
   <si>
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
-  </si>
-  <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>KONAFETTO blanc ВКФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1358,9 +1298,6 @@
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1376,6 +1313,9 @@
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1391,7 +1331,7 @@
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
@@ -1409,6 +1349,9 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1418,12 +1361,6 @@
     <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
-  </si>
-  <si>
-    <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
-  </si>
-  <si>
     <t>Монблан РЦ 240г /15шт /</t>
   </si>
   <si>
@@ -1433,9 +1370,6 @@
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
@@ -1448,19 +1382,25 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
+    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
@@ -1475,12 +1415,18 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1496,13 +1442,7 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт</t>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
@@ -1511,9 +1451,6 @@
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1526,34 +1463,52 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
@@ -1562,7 +1517,7 @@
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
@@ -1574,27 +1529,30 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1625,9 +1583,6 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1643,31 +1598,49 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
@@ -1676,19 +1649,28 @@
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦИЯ ВИП</t>
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
@@ -1697,6 +1679,9 @@
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1715,6 +1700,9 @@
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1724,22 +1712,10 @@
     <t>Кролик Roshen зимовий ВКФ 25г /35шт</t>
   </si>
   <si>
-    <t>Набір Зимові Друзі 3х20 РЦ 60г /22шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
-  </si>
-  <si>
     <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +1967,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C574"/>
+  <dimension ref="C566"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -2056,7 +2032,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>994</v>
+        <v>885</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -2064,7 +2040,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1039404</v>
+        <v>1029475</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -2072,7 +2048,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>220903</v>
+        <v>149877</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -2080,7 +2056,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>27543</v>
+        <v>22004</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -2088,7 +2064,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2353</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -2096,7 +2072,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>280</v>
+        <v>719</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -2104,23 +2080,23 @@
         <v>16</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>2455</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>1223</v>
+      <c r="C18" s="11" t="n">
+        <v>568</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>2819</v>
+      <c r="C19" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -2128,7 +2104,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3021</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -2136,7 +2112,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>30</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -2144,7 +2120,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>2113</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -2152,55 +2128,55 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>280</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16" t="n">
-        <v>2364</v>
+      <c r="C24" s="11" t="n">
+        <v>212</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>30</v>
+      <c r="C25" s="16" t="n">
+        <v>1216</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>3474</v>
+      <c r="C26" s="11" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>400</v>
+      <c r="C27" s="16" t="n">
+        <v>1319</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>112</v>
+      <c r="C28" s="16" t="n">
+        <v>2119</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>6093</v>
+      <c r="C29" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -2208,31 +2184,31 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="31" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B31" s="14" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="31" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="12" t="n">
-        <v>89942</v>
+      <c r="C31" s="16" t="n">
+        <v>4957</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>7707</v>
-      </c>
-    </row>
-    <row r="33" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B33" s="15" t="s">
+      <c r="C32" s="11" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B33" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>52647</v>
+      <c r="C33" s="12" t="n">
+        <v>86248</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -2240,7 +2216,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>4794</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -2248,7 +2224,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>17177</v>
+        <v>61784</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -2256,7 +2232,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>1030</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -2264,7 +2240,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>4640</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -2272,7 +2248,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>43</v>
+        <v>722</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -2280,31 +2256,31 @@
         <v>38</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="40" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B40" s="14" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="40" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>26512</v>
+      <c r="C40" s="11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1489</v>
+      <c r="C41" s="11" t="n">
+        <v>502</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>332</v>
+      <c r="C42" s="16" t="n">
+        <v>1230</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -2312,39 +2288,39 @@
         <v>42</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>1353</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B45" s="15" t="s">
+      <c r="C44" s="16" t="n">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>191</v>
+      <c r="C45" s="12" t="n">
+        <v>17157</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="16" t="n">
-        <v>1018</v>
+      <c r="C46" s="11" t="n">
+        <v>578</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="16" t="n">
-        <v>1601</v>
+      <c r="C47" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -2352,7 +2328,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>590</v>
+        <v>664</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -2360,7 +2336,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>986</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2368,7 +2344,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>958</v>
+        <v>723</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2376,7 +2352,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>817</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2384,15 +2360,15 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>352</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="16" t="n">
-        <v>2254</v>
+      <c r="C53" s="11" t="n">
+        <v>628</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2400,15 +2376,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>996</v>
+        <v>560</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="16" t="n">
-        <v>1650</v>
+      <c r="C55" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2416,7 +2392,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>112</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2424,39 +2400,39 @@
         <v>56</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>1506</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C58" s="11" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>950</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>2573</v>
+      <c r="C60" s="11" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>827</v>
+      <c r="C61" s="16" t="n">
+        <v>1626</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2464,47 +2440,47 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>861</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>2261</v>
+      <c r="C63" s="11" t="n">
+        <v>454</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="65" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B65" s="14" t="s">
+      <c r="C64" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="12" t="n">
-        <v>76906</v>
+      <c r="C65" s="16" t="n">
+        <v>1558</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>2291</v>
+      <c r="C66" s="11" t="n">
+        <v>476</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>3371</v>
+      <c r="C67" s="11" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2512,95 +2488,95 @@
         <v>67</v>
       </c>
       <c r="C68" s="16" t="n">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="69" ht="11" customHeight="true" outlineLevel="3">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="70" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C69" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>10427</v>
+      <c r="C70" s="11" t="n">
+        <v>470</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>2768</v>
+      <c r="C71" s="11" t="n">
+        <v>673</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>4615</v>
+      <c r="C72" s="11" t="n">
+        <v>798</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="16" t="n">
-        <v>5197</v>
+      <c r="C73" s="11" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>2563</v>
+      <c r="C74" s="11" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="16" t="n">
-        <v>10400</v>
+      <c r="C75" s="11" t="n">
+        <v>924</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>64</v>
+      <c r="C76" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>21707</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B78" s="15" t="s">
+      <c r="C77" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B78" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>1020</v>
+      <c r="C78" s="12" t="n">
+        <v>24468</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>5116</v>
+      <c r="C79" s="11" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2608,15 +2584,15 @@
         <v>79</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>1388</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>336</v>
+      <c r="C81" s="16" t="n">
+        <v>1611</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2624,79 +2600,79 @@
         <v>81</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B83" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>818501</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="14" t="s">
+      <c r="C83" s="16" t="n">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>53891</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C84" s="16" t="n">
+        <v>3462</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C85" s="16" t="n">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C87" s="16" t="n">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>10800</v>
+      <c r="C88" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>1</v>
+      <c r="C89" s="16" t="n">
+        <v>1761</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>148</v>
+      <c r="C90" s="16" t="n">
+        <v>1845</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>10</v>
+      <c r="C91" s="16" t="n">
+        <v>2585</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2704,87 +2680,87 @@
         <v>91</v>
       </c>
       <c r="C92" s="16" t="n">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="true" outlineLevel="3">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>-229</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="16" t="n">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C94" s="11" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B97" s="15" t="s">
+      <c r="C96" s="11" t="n">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B97" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B98" s="15" t="s">
+      <c r="C97" s="12" t="n">
+        <v>879598</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B98" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>1</v>
+      <c r="C98" s="12" t="n">
+        <v>243286</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>1620</v>
+      <c r="C99" s="11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>41</v>
+      <c r="C100" s="16" t="n">
+        <v>17682</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>9790</v>
+      <c r="C101" s="11" t="n">
+        <v>407</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>4256</v>
+      <c r="C102" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
@@ -2792,39 +2768,39 @@
         <v>102</v>
       </c>
       <c r="C103" s="16" t="n">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+        <v>7870</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C104" s="16" t="n">
+        <v>10665</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C105" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="16" t="n">
-        <v>1215</v>
+        <v>34314</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="11" t="n">
-        <v>70</v>
+      <c r="C107" s="16" t="n">
+        <v>7506</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="true" outlineLevel="3">
@@ -2832,15 +2808,15 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>380</v>
+        <v>916</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>1</v>
+      <c r="C109" s="16" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
@@ -2848,127 +2824,127 @@
         <v>109</v>
       </c>
       <c r="C110" s="16" t="n">
-        <v>8100</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B111" s="14" t="s">
+        <v>27973</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="12" t="n">
-        <v>10165</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C111" s="16" t="n">
+        <v>36249</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="16" t="n">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C112" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="114" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C113" s="16" t="n">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="16" t="n">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="115" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C114" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C115" s="16" t="n">
+        <v>18754</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="16" t="n">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+        <v>7733</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C117" s="16" t="n">
+        <v>6540</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="11" t="n">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C118" s="16" t="n">
+        <v>8906</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="16" t="n">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="3">
+        <v>28434</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C120" s="16" t="n">
+        <v>16655</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" ht="11" customHeight="true" outlineLevel="3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B123" s="15" t="s">
+      <c r="C122" s="16" t="n">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B123" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C123" s="12" t="n">
+        <v>20628</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="125" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B125" s="14" t="s">
+      <c r="C124" s="16" t="n">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="125" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="12" t="n">
-        <v>212705</v>
+      <c r="C125" s="11" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2976,23 +2952,23 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="127" ht="22" customHeight="true" outlineLevel="3">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>20</v>
+      <c r="C127" s="16" t="n">
+        <v>1033</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>314</v>
+      <c r="C128" s="16" t="n">
+        <v>1580</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -3000,23 +2976,23 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>581</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>31</v>
+      <c r="C130" s="16" t="n">
+        <v>1461</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>10</v>
+      <c r="C131" s="16" t="n">
+        <v>1163</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -3024,15 +3000,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>92</v>
+        <v>364</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>85</v>
+      <c r="C133" s="16" t="n">
+        <v>3835</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -3040,7 +3016,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>31</v>
+        <v>959</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -3048,7 +3024,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="16" t="n">
-        <v>52820</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -3056,23 +3032,23 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="137" ht="11" customHeight="true" outlineLevel="3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C137" s="16" t="n">
-        <v>50812</v>
-      </c>
-    </row>
-    <row r="138" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B138" s="15" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="138" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B138" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="16" t="n">
-        <v>36600</v>
+      <c r="C138" s="12" t="n">
+        <v>64428</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -3080,15 +3056,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="16" t="n">
-        <v>55179</v>
+      <c r="C140" s="11" t="n">
+        <v>576</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -3096,7 +3072,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>5</v>
+        <v>702</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -3104,7 +3080,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>725</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -3112,7 +3088,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>237</v>
+        <v>899</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -3120,15 +3096,15 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>105</v>
+        <v>731</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="11" t="n">
-        <v>31</v>
+      <c r="C145" s="16" t="n">
+        <v>3394</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -3136,31 +3112,31 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>263</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>7</v>
+      <c r="C147" s="16" t="n">
+        <v>2442</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="11" t="n">
-        <v>252</v>
+      <c r="C148" s="16" t="n">
+        <v>12850</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="16" t="n">
-        <v>1461</v>
+      <c r="C149" s="11" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -3168,7 +3144,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="16" t="n">
-        <v>1584</v>
+        <v>24004</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -3176,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>409</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -3184,7 +3160,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>633</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -3192,7 +3168,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>18</v>
+        <v>236</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -3200,7 +3176,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>302</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -3208,7 +3184,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>349</v>
+        <v>375</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -3216,15 +3192,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>8</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="16" t="n">
-        <v>1495</v>
+      <c r="C157" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -3232,7 +3208,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>7</v>
+        <v>304</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -3240,15 +3216,15 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>544</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="11" t="n">
-        <v>565</v>
+      <c r="C160" s="16" t="n">
+        <v>1034</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -3256,7 +3232,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>4</v>
+        <v>749</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3264,7 +3240,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>351</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -3272,7 +3248,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>392</v>
+        <v>268</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3280,7 +3256,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="16" t="n">
-        <v>2706</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3288,15 +3264,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>16</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="16" t="n">
-        <v>2490</v>
+      <c r="C166" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -3304,15 +3280,15 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="168" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B168" s="14" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="168" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="12" t="n">
-        <v>88686</v>
+      <c r="C168" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3320,7 +3296,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>643</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3328,7 +3304,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -3336,7 +3312,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>362</v>
+        <v>492</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3344,7 +3320,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>158</v>
+        <v>617</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3352,15 +3328,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>888</v>
+        <v>500</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>600</v>
+      <c r="C174" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3368,7 +3344,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>409</v>
+        <v>250</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3376,7 +3352,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>575</v>
+        <v>679</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3384,15 +3360,15 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>219</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>245</v>
+      <c r="C178" s="16" t="n">
+        <v>1173</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3400,15 +3376,15 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>360</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>102</v>
+      <c r="C180" s="16" t="n">
+        <v>1123</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3416,7 +3392,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3424,15 +3400,15 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="183" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B183" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="183" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B183" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>437</v>
+      <c r="C183" s="12" t="n">
+        <v>210841</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3440,7 +3416,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>196</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3448,7 +3424,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>89</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3456,15 +3432,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>849</v>
+        <v>329</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>209</v>
+      <c r="C187" s="16" t="n">
+        <v>2715</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3472,7 +3448,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>114</v>
+        <v>446</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3480,15 +3456,15 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>264</v>
+        <v>586</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="11" t="n">
-        <v>598</v>
+      <c r="C190" s="16" t="n">
+        <v>1328</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3496,7 +3472,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>324</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3504,7 +3480,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>418</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3512,7 +3488,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="16" t="n">
-        <v>4791</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3520,7 +3496,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>460</v>
+        <v>477</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3528,7 +3504,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>599</v>
+        <v>407</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3536,7 +3512,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3544,15 +3520,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>558</v>
+        <v>200</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>130</v>
+      <c r="C198" s="16" t="n">
+        <v>9959</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3560,7 +3536,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>154</v>
+        <v>411</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3568,7 +3544,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3576,15 +3552,15 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>481</v>
+        <v>568</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>774</v>
+      <c r="C202" s="16" t="n">
+        <v>14578</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3592,7 +3568,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>329</v>
+        <v>642</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3600,15 +3576,15 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>418</v>
+        <v>430</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>282</v>
+      <c r="C205" s="16" t="n">
+        <v>10531</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3616,7 +3592,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>15</v>
+        <v>336</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3624,7 +3600,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>602</v>
+        <v>130</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3632,15 +3608,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>428</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>750</v>
+      <c r="C209" s="16" t="n">
+        <v>14941</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3648,7 +3624,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>262</v>
+        <v>312</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3656,7 +3632,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>640</v>
+        <v>734</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3664,15 +3640,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>54</v>
+        <v>285</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>790</v>
+      <c r="C213" s="16" t="n">
+        <v>3748</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3680,7 +3656,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3688,15 +3664,15 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="16" t="n">
-        <v>1829</v>
+      <c r="C216" s="11" t="n">
+        <v>428</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3704,15 +3680,15 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>320</v>
+        <v>44</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="11" t="n">
-        <v>636</v>
+      <c r="C218" s="16" t="n">
+        <v>1280</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3720,7 +3696,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>22</v>
+        <v>589</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3728,7 +3704,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3736,79 +3712,79 @@
         <v>220</v>
       </c>
       <c r="C221" s="16" t="n">
-        <v>1705</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="11" t="n">
-        <v>185</v>
+      <c r="C222" s="16" t="n">
+        <v>1428</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>620</v>
+      <c r="C223" s="16" t="n">
+        <v>1789</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
       <c r="B224" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="16" t="n">
-        <v>1347</v>
+      <c r="C224" s="11" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="16" t="n">
-        <v>8526</v>
+      <c r="C225" s="11" t="n">
+        <v>935</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>137</v>
+      <c r="C226" s="16" t="n">
+        <v>6385</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="16" t="n">
-        <v>7623</v>
+      <c r="C227" s="11" t="n">
+        <v>228</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="11" t="n">
-        <v>110</v>
+      <c r="C228" s="16" t="n">
+        <v>1947</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>1936</v>
+      <c r="C229" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="16" t="n">
-        <v>3691</v>
+      <c r="C230" s="11" t="n">
+        <v>366</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3816,15 +3792,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="232" ht="11" customHeight="true" outlineLevel="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>393</v>
+      <c r="C232" s="16" t="n">
+        <v>4799</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3832,7 +3808,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>503</v>
+        <v>85</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3840,23 +3816,23 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>761</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="11" t="n">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="236" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C235" s="16" t="n">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
       <c r="C236" s="16" t="n">
-        <v>1248</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3864,7 +3840,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>9</v>
+        <v>436</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3872,15 +3848,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="239" ht="11" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>237</v>
+      <c r="C239" s="16" t="n">
+        <v>2910</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3888,7 +3864,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>430</v>
+        <v>281</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3896,15 +3872,15 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>110</v>
+        <v>473</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="11" t="n">
-        <v>62</v>
+      <c r="C242" s="16" t="n">
+        <v>2817</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3912,7 +3888,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3920,7 +3896,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>592</v>
+        <v>569</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3928,7 +3904,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>825</v>
+        <v>237</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3936,15 +3912,15 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>372</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="11" t="n">
-        <v>869</v>
+      <c r="C247" s="16" t="n">
+        <v>14068</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3952,7 +3928,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>702</v>
+        <v>726</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3960,7 +3936,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>542</v>
+        <v>552</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3968,15 +3944,15 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>254</v>
+        <v>196</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>674</v>
+      <c r="C251" s="16" t="n">
+        <v>9745</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3984,7 +3960,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>45</v>
+        <v>682</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3992,7 +3968,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>36</v>
+        <v>512</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -4000,7 +3976,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>65</v>
+        <v>468</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -4008,15 +3984,15 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>213</v>
+        <v>7</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="16" t="n">
-        <v>1375</v>
+      <c r="C256" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -4024,15 +4000,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="16" t="n">
-        <v>1051</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>240</v>
+      <c r="C258" s="16" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -4040,23 +4016,23 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>15</v>
+        <v>428</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>13</v>
+      <c r="C260" s="16" t="n">
+        <v>2538</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>428</v>
+      <c r="C261" s="16" t="n">
+        <v>6964</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -4064,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -4072,7 +4048,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>238</v>
+        <v>54</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -4080,7 +4056,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>550</v>
+        <v>166</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -4088,31 +4064,31 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>281</v>
+        <v>189</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="11" t="n">
-        <v>189</v>
+      <c r="C266" s="16" t="n">
+        <v>6715</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="11" t="n">
-        <v>214</v>
+      <c r="C267" s="16" t="n">
+        <v>1102</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="11" t="n">
-        <v>308</v>
+      <c r="C268" s="16" t="n">
+        <v>1898</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -4120,7 +4096,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>42</v>
+        <v>462</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -4128,15 +4104,15 @@
         <v>269</v>
       </c>
       <c r="C270" s="16" t="n">
-        <v>1951</v>
+        <v>6726</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>946</v>
+      <c r="C271" s="16" t="n">
+        <v>7283</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -4144,7 +4120,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>308</v>
+        <v>408</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -4152,15 +4128,15 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>36</v>
+        <v>861</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>892</v>
+      <c r="C274" s="16" t="n">
+        <v>8283</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -4168,15 +4144,15 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>367</v>
+        <v>198</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>470</v>
+      <c r="C276" s="16" t="n">
+        <v>1725</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -4184,7 +4160,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -4192,7 +4168,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="16" t="n">
-        <v>1765</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -4200,7 +4176,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>278</v>
+        <v>331</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -4208,15 +4184,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>440</v>
+        <v>79</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>24</v>
+      <c r="C281" s="16" t="n">
+        <v>8650</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -4224,15 +4200,15 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>110</v>
+        <v>543</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>638</v>
+      <c r="C283" s="16" t="n">
+        <v>1780</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -4240,23 +4216,23 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>30</v>
+        <v>533</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>442</v>
+      <c r="C285" s="16" t="n">
+        <v>3152</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="16" t="n">
-        <v>1820</v>
+      <c r="C286" s="11" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -4264,15 +4240,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>688</v>
+        <v>367</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="16" t="n">
-        <v>1128</v>
+      <c r="C288" s="11" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -4280,55 +4256,55 @@
         <v>288</v>
       </c>
       <c r="C289" s="16" t="n">
-        <v>1410</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="16" t="n">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="291" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B291" s="15" t="s">
+      <c r="C290" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B291" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="16" t="n">
-        <v>1512</v>
+      <c r="C291" s="12" t="n">
+        <v>64863</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="11" t="n">
-        <v>433</v>
+      <c r="C292" s="16" t="n">
+        <v>1728</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="11" t="n">
-        <v>429</v>
+      <c r="C293" s="16" t="n">
+        <v>1040</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="11" t="n">
-        <v>96</v>
+      <c r="C294" s="16" t="n">
+        <v>2540</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="16" t="n">
-        <v>2087</v>
+      <c r="C295" s="11" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4336,7 +4312,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>57</v>
+        <v>477</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4344,15 +4320,15 @@
         <v>296</v>
       </c>
       <c r="C297" s="16" t="n">
-        <v>2482</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="11" t="n">
-        <v>53</v>
+      <c r="C298" s="16" t="n">
+        <v>8140</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -4360,47 +4336,47 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B300" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="C300" s="12" t="n">
-        <v>80578</v>
+      <c r="C300" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="16" t="n">
-        <v>2265</v>
+      <c r="C301" s="11" t="n">
+        <v>371</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="16" t="n">
-        <v>2307</v>
+      <c r="C302" s="11" t="n">
+        <v>822</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>3864</v>
+      <c r="C303" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="16" t="n">
-        <v>1853</v>
+      <c r="C304" s="11" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4408,31 +4384,31 @@
         <v>304</v>
       </c>
       <c r="C305" s="16" t="n">
-        <v>5819</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>87</v>
+      <c r="C306" s="16" t="n">
+        <v>1607</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>50</v>
+      <c r="C307" s="16" t="n">
+        <v>1601</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="11" t="n">
-        <v>265</v>
+      <c r="C308" s="16" t="n">
+        <v>1251</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4440,23 +4416,23 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>441</v>
+        <v>951</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="16" t="n">
-        <v>1512</v>
+      <c r="C310" s="11" t="n">
+        <v>845</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="11" t="n">
-        <v>273</v>
+      <c r="C311" s="16" t="n">
+        <v>1563</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4464,15 +4440,15 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>462</v>
+        <v>761</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="16" t="n">
-        <v>2616</v>
+      <c r="C313" s="11" t="n">
+        <v>755</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -4480,7 +4456,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="16" t="n">
-        <v>1971</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4488,7 +4464,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="16" t="n">
-        <v>3136</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4496,7 +4472,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="16" t="n">
-        <v>1226</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4504,15 +4480,15 @@
         <v>316</v>
       </c>
       <c r="C317" s="16" t="n">
-        <v>1485</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>932</v>
+      <c r="C318" s="16" t="n">
+        <v>2148</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4520,15 +4496,15 @@
         <v>318</v>
       </c>
       <c r="C319" s="16" t="n">
-        <v>1398</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="16" t="n">
-        <v>1381</v>
+      <c r="C320" s="11" t="n">
+        <v>831</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -4536,7 +4512,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="16" t="n">
-        <v>1132</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -4544,7 +4520,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="16" t="n">
-        <v>2714</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4552,7 +4528,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="16" t="n">
-        <v>3035</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4560,15 +4536,15 @@
         <v>323</v>
       </c>
       <c r="C324" s="16" t="n">
-        <v>4836</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>3374</v>
+      <c r="C325" s="11" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4576,7 +4552,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="16" t="n">
-        <v>3655</v>
+        <v>7258</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -4584,39 +4560,39 @@
         <v>326</v>
       </c>
       <c r="C327" s="16" t="n">
-        <v>4167</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B328" s="15" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B328" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="16" t="n">
-        <v>4280</v>
+      <c r="C328" s="12" t="n">
+        <v>6548</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="16" t="n">
-        <v>3741</v>
+      <c r="C329" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="16" t="n">
-        <v>2323</v>
+      <c r="C330" s="11" t="n">
+        <v>671</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="16" t="n">
-        <v>3181</v>
+      <c r="C331" s="11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4624,31 +4600,31 @@
         <v>331</v>
       </c>
       <c r="C332" s="16" t="n">
-        <v>2765</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="16" t="n">
-        <v>6212</v>
+      <c r="C333" s="11" t="n">
+        <v>417</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="16" t="n">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B335" s="14" t="s">
+      <c r="C334" s="11" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="12" t="n">
-        <v>5189</v>
+      <c r="C335" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4656,7 +4632,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>253</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4664,7 +4640,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>259</v>
+        <v>200</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4672,7 +4648,7 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>152</v>
+        <v>290</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4680,7 +4656,7 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4688,7 +4664,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>721</v>
+        <v>395</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4696,7 +4672,7 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>120</v>
+        <v>503</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4704,7 +4680,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4712,7 +4688,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>251</v>
+        <v>536</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4720,7 +4696,7 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>247</v>
+        <v>499</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4728,7 +4704,7 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>24</v>
+        <v>183</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4736,7 +4712,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>814</v>
+        <v>74</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4744,23 +4720,23 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B348" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B348" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C348" s="12" t="n">
+        <v>61196</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>95</v>
+        <v>439</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
@@ -4768,7 +4744,7 @@
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>192</v>
+        <v>27</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4776,7 +4752,7 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>148</v>
+        <v>78</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4784,7 +4760,7 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>213</v>
+        <v>419</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4792,7 +4768,7 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>297</v>
+        <v>955</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4800,7 +4776,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>499</v>
+        <v>252</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4808,15 +4784,15 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>80</v>
+        <v>465</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>112</v>
+      <c r="C356" s="16" t="n">
+        <v>1167</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4824,7 +4800,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>48</v>
+        <v>465</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4832,7 +4808,7 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>7</v>
+        <v>462</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4840,15 +4816,15 @@
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B360" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="12" t="n">
-        <v>53519</v>
+      <c r="C360" s="11" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4856,7 +4832,7 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>156</v>
+        <v>350</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4864,7 +4840,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>146</v>
+        <v>592</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4872,31 +4848,31 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="364" ht="22" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>501</v>
+        <v>126</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="16" t="n">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C365" s="11" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>252</v>
+        <v>4</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4904,31 +4880,31 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="16" t="n">
-        <v>2387</v>
+      <c r="C368" s="11" t="n">
+        <v>866</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="C369" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C369" s="16" t="n">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="16" t="n">
-        <v>1009</v>
+      <c r="C370" s="11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4936,15 +4912,15 @@
         <v>370</v>
       </c>
       <c r="C371" s="16" t="n">
-        <v>1058</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="16" t="n">
-        <v>1782</v>
+      <c r="C372" s="11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="373" ht="22" customHeight="true" outlineLevel="3">
@@ -4952,7 +4928,7 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="374" ht="22" customHeight="true" outlineLevel="3">
@@ -4960,39 +4936,39 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="16" t="n">
-        <v>1252</v>
+      <c r="C378" s="11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="true" outlineLevel="3">
@@ -5000,87 +4976,87 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="16" t="n">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C380" s="11" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="382" ht="22" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="383" ht="22" customHeight="true" outlineLevel="3">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="384" ht="22" customHeight="true" outlineLevel="3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
       <c r="B384" s="15" t="s">
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="385" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
       <c r="B387" s="15" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="388" ht="22" customHeight="true" outlineLevel="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="11" t="n">
-        <v>475</v>
+      <c r="C389" s="16" t="n">
+        <v>4140</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
@@ -5088,15 +5064,15 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>40</v>
+        <v>186</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
       <c r="B391" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="C391" s="11" t="n">
-        <v>385</v>
+      <c r="C391" s="16" t="n">
+        <v>2358</v>
       </c>
     </row>
     <row r="392" ht="11" customHeight="true" outlineLevel="3">
@@ -5104,7 +5080,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="16" t="n">
-        <v>1348</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="393" ht="11" customHeight="true" outlineLevel="3">
@@ -5112,23 +5088,23 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>11</v>
+        <v>108</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="11" t="n">
-        <v>360</v>
+      <c r="C394" s="16" t="n">
+        <v>1886</v>
       </c>
     </row>
     <row r="395" ht="11" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="11" t="n">
-        <v>443</v>
+      <c r="C395" s="16" t="n">
+        <v>4390</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -5136,7 +5112,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>445</v>
+        <v>275</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
@@ -5144,15 +5120,15 @@
         <v>396</v>
       </c>
       <c r="C397" s="16" t="n">
-        <v>3514</v>
-      </c>
-    </row>
-    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+        <v>6613</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="11" t="n">
-        <v>186</v>
+      <c r="C398" s="16" t="n">
+        <v>16942</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -5160,215 +5136,215 @@
         <v>398</v>
       </c>
       <c r="C399" s="16" t="n">
-        <v>3069</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="16" t="n">
-        <v>1631</v>
+      <c r="C400" s="11" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C401" s="16" t="n">
+        <v>5519</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="C402" s="16" t="n">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B403" s="15" t="s">
+      <c r="C402" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B403" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="16" t="n">
-        <v>1619</v>
+      <c r="C403" s="12" t="n">
+        <v>3914</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B404" s="15" t="s">
+      <c r="B404" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="11" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B405" s="15" t="s">
+      <c r="C404" s="12" t="n">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B405" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="16" t="n">
-        <v>3746</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B406" s="15" t="s">
+      <c r="C405" s="11" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B406" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="16" t="n">
-        <v>9084</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B407" s="15" t="s">
+      <c r="C406" s="11" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B407" s="18" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="16" t="n">
-        <v>4656</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B408" s="18" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B409" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="C409" s="16" t="n">
-        <v>5790</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
+      <c r="C409" s="11" t="n">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B410" s="18" t="s">
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B411" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B411" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="12" t="n">
-        <v>14094</v>
-      </c>
-    </row>
-    <row r="412" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B412" s="17" t="s">
+      <c r="C411" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="412" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B412" s="14" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="12" t="n">
-        <v>14094</v>
-      </c>
-    </row>
-    <row r="413" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B413" s="18" t="s">
+        <v>56296</v>
+      </c>
+    </row>
+    <row r="413" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
         <v>412</v>
       </c>
       <c r="C413" s="16" t="n">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B414" s="18" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="16" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B415" s="18" t="s">
+      <c r="C414" s="11" t="n">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="16" t="n">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B416" s="18" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="16" t="n">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B417" s="18" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="16" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B418" s="18" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="C418" s="16" t="n">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="419" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B419" s="18" t="s">
+      <c r="C418" s="11" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C419" s="16" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B420" s="18" t="s">
+      <c r="C419" s="11" t="n">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="16" t="n">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B421" s="18" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="16" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B422" s="18" t="s">
+      <c r="C421" s="11" t="n">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="16" t="n">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="423" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B423" s="18" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="C423" s="11" t="n">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B424" s="18" t="s">
+      <c r="C423" s="16" t="n">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="C424" s="16" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B425" s="14" t="s">
+      <c r="C424" s="11" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="C425" s="12" t="n">
-        <v>67589</v>
+      <c r="C425" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="426" ht="11" customHeight="true" outlineLevel="3">
@@ -5376,31 +5352,31 @@
         <v>425</v>
       </c>
       <c r="C426" s="16" t="n">
-        <v>2952</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="427" ht="11" customHeight="true" outlineLevel="3">
       <c r="B427" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="C427" s="11" t="n">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C427" s="16" t="n">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
       <c r="B428" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="11" t="n">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="429" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C428" s="16" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
       <c r="B429" s="15" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>377</v>
+        <v>524</v>
       </c>
     </row>
     <row r="430" ht="11" customHeight="true" outlineLevel="3">
@@ -5408,15 +5384,15 @@
         <v>429</v>
       </c>
       <c r="C430" s="16" t="n">
-        <v>2384</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="431" ht="11" customHeight="true" outlineLevel="3">
       <c r="B431" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="C431" s="11" t="n">
-        <v>708</v>
+      <c r="C431" s="16" t="n">
+        <v>3116</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
@@ -5424,23 +5400,23 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>87</v>
+        <v>54</v>
       </c>
     </row>
     <row r="433" ht="11" customHeight="true" outlineLevel="3">
       <c r="B433" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="C433" s="16" t="n">
-        <v>1544</v>
+      <c r="C433" s="11" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="434" ht="11" customHeight="true" outlineLevel="3">
       <c r="B434" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="C434" s="16" t="n">
-        <v>5125</v>
+      <c r="C434" s="11" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="435" ht="11" customHeight="true" outlineLevel="3">
@@ -5448,15 +5424,15 @@
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>807</v>
+        <v>421</v>
       </c>
     </row>
     <row r="436" ht="11" customHeight="true" outlineLevel="3">
       <c r="B436" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C436" s="16" t="n">
-        <v>1277</v>
+      <c r="C436" s="11" t="n">
+        <v>399</v>
       </c>
     </row>
     <row r="437" ht="11" customHeight="true" outlineLevel="3">
@@ -5464,23 +5440,23 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="438" ht="11" customHeight="true" outlineLevel="3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
       <c r="B438" s="15" t="s">
         <v>437</v>
       </c>
       <c r="C438" s="11" t="n">
-        <v>695</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" ht="11" customHeight="true" outlineLevel="3">
       <c r="B439" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="C439" s="11" t="n">
-        <v>847</v>
+      <c r="C439" s="16" t="n">
+        <v>13518</v>
       </c>
     </row>
     <row r="440" ht="11" customHeight="true" outlineLevel="3">
@@ -5488,7 +5464,7 @@
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>836</v>
+        <v>134</v>
       </c>
     </row>
     <row r="441" ht="11" customHeight="true" outlineLevel="3">
@@ -5496,31 +5472,31 @@
         <v>440</v>
       </c>
       <c r="C441" s="11" t="n">
-        <v>850</v>
+        <v>234</v>
       </c>
     </row>
     <row r="442" ht="11" customHeight="true" outlineLevel="3">
       <c r="B442" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="C442" s="11" t="n">
-        <v>89</v>
+      <c r="C442" s="16" t="n">
+        <v>3664</v>
       </c>
     </row>
     <row r="443" ht="11" customHeight="true" outlineLevel="3">
       <c r="B443" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C443" s="11" t="n">
-        <v>754</v>
+      <c r="C443" s="16" t="n">
+        <v>2829</v>
       </c>
     </row>
     <row r="444" ht="11" customHeight="true" outlineLevel="3">
       <c r="B444" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="11" t="n">
-        <v>730</v>
+      <c r="C444" s="16" t="n">
+        <v>3324</v>
       </c>
     </row>
     <row r="445" ht="11" customHeight="true" outlineLevel="3">
@@ -5528,23 +5504,23 @@
         <v>444</v>
       </c>
       <c r="C445" s="16" t="n">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="446" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B446" s="15" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="446" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B446" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="C446" s="16" t="n">
-        <v>1942</v>
+      <c r="C446" s="19" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="447" ht="11" customHeight="true" outlineLevel="3">
       <c r="B447" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="C447" s="16" t="n">
-        <v>3110</v>
+      <c r="C447" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="448" ht="11" customHeight="true" outlineLevel="3">
@@ -5552,15 +5528,15 @@
         <v>447</v>
       </c>
       <c r="C448" s="11" t="n">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="449" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B449" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="449" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B449" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C449" s="11" t="n">
-        <v>907</v>
+      <c r="C449" s="12" t="n">
+        <v>147391</v>
       </c>
     </row>
     <row r="450" ht="11" customHeight="true" outlineLevel="3">
@@ -5568,23 +5544,23 @@
         <v>449</v>
       </c>
       <c r="C450" s="11" t="n">
-        <v>203</v>
+        <v>156</v>
       </c>
     </row>
     <row r="451" ht="11" customHeight="true" outlineLevel="3">
       <c r="B451" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="C451" s="16" t="n">
-        <v>1791</v>
+      <c r="C451" s="11" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="452" ht="11" customHeight="true" outlineLevel="3">
       <c r="B452" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="C452" s="16" t="n">
-        <v>2651</v>
+      <c r="C452" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="453" ht="11" customHeight="true" outlineLevel="3">
@@ -5592,103 +5568,103 @@
         <v>452</v>
       </c>
       <c r="C453" s="11" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="454" ht="11" customHeight="true" outlineLevel="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="454" ht="22" customHeight="true" outlineLevel="3">
       <c r="B454" s="15" t="s">
         <v>453</v>
       </c>
       <c r="C454" s="11" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="455" ht="11" customHeight="true" outlineLevel="3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
       <c r="B455" s="15" t="s">
         <v>454</v>
       </c>
       <c r="C455" s="11" t="n">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="true" outlineLevel="3">
       <c r="B456" s="15" t="s">
         <v>455</v>
       </c>
       <c r="C456" s="11" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="true" outlineLevel="3">
       <c r="B457" s="15" t="s">
         <v>456</v>
       </c>
       <c r="C457" s="11" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" ht="33" customHeight="true" outlineLevel="3">
       <c r="B458" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="C458" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C458" s="16" t="n">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="459" ht="22" customHeight="true" outlineLevel="3">
       <c r="B459" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="C459" s="16" t="n">
-        <v>12586</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C459" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="true" outlineLevel="3">
       <c r="B460" s="15" t="s">
         <v>459</v>
       </c>
       <c r="C460" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="true" outlineLevel="3">
       <c r="B461" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="C461" s="16" t="n">
-        <v>5898</v>
-      </c>
-    </row>
-    <row r="462" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C461" s="11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="true" outlineLevel="3">
       <c r="B462" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="C462" s="16" t="n">
-        <v>7555</v>
-      </c>
-    </row>
-    <row r="463" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C462" s="11" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
       <c r="B463" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="C463" s="16" t="n">
-        <v>3923</v>
-      </c>
-    </row>
-    <row r="464" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C463" s="11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="true" outlineLevel="3">
       <c r="B464" s="15" t="s">
         <v>463</v>
       </c>
       <c r="C464" s="16" t="n">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="465" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B465" s="14" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="465" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B465" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="C465" s="19" t="n">
-        <v>101</v>
+      <c r="C465" s="11" t="n">
+        <v>313</v>
       </c>
     </row>
     <row r="466" ht="11" customHeight="true" outlineLevel="3">
@@ -5696,7 +5672,7 @@
         <v>465</v>
       </c>
       <c r="C466" s="11" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="467" ht="11" customHeight="true" outlineLevel="3">
@@ -5704,15 +5680,15 @@
         <v>466</v>
       </c>
       <c r="C467" s="11" t="n">
-        <v>40</v>
+        <v>260</v>
       </c>
     </row>
     <row r="468" ht="11" customHeight="true" outlineLevel="3">
       <c r="B468" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="C468" s="11" t="n">
-        <v>34</v>
+      <c r="C468" s="16" t="n">
+        <v>3353</v>
       </c>
     </row>
     <row r="469" ht="11" customHeight="true" outlineLevel="3">
@@ -5720,31 +5696,31 @@
         <v>468</v>
       </c>
       <c r="C469" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B470" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B470" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="C470" s="12" t="n">
-        <v>231984</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C470" s="11" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="471" ht="22" customHeight="true" outlineLevel="3">
       <c r="B471" s="15" t="s">
         <v>470</v>
       </c>
       <c r="C471" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="472" ht="22" customHeight="true" outlineLevel="3">
       <c r="B472" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="C472" s="11" t="n">
-        <v>908</v>
+      <c r="C472" s="16" t="n">
+        <v>2654</v>
       </c>
     </row>
     <row r="473" ht="11" customHeight="true" outlineLevel="3">
@@ -5752,7 +5728,7 @@
         <v>472</v>
       </c>
       <c r="C473" s="11" t="n">
-        <v>257</v>
+        <v>32</v>
       </c>
     </row>
     <row r="474" ht="11" customHeight="true" outlineLevel="3">
@@ -5760,7 +5736,7 @@
         <v>473</v>
       </c>
       <c r="C474" s="11" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="475" ht="11" customHeight="true" outlineLevel="3">
@@ -5768,31 +5744,31 @@
         <v>474</v>
       </c>
       <c r="C475" s="11" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="true" outlineLevel="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="476" ht="11" customHeight="true" outlineLevel="3">
       <c r="B476" s="15" t="s">
         <v>475</v>
       </c>
       <c r="C476" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="477" ht="11" customHeight="true" outlineLevel="3">
       <c r="B477" s="15" t="s">
         <v>476</v>
       </c>
       <c r="C477" s="11" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="478" ht="11" customHeight="true" outlineLevel="3">
       <c r="B478" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="C478" s="11" t="n">
-        <v>6</v>
+      <c r="C478" s="16" t="n">
+        <v>4151</v>
       </c>
     </row>
     <row r="479" ht="22" customHeight="true" outlineLevel="3">
@@ -5800,15 +5776,15 @@
         <v>478</v>
       </c>
       <c r="C479" s="11" t="n">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="480" ht="33" customHeight="true" outlineLevel="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="true" outlineLevel="3">
       <c r="B480" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="C480" s="16" t="n">
-        <v>9361</v>
+      <c r="C480" s="11" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="481" ht="22" customHeight="true" outlineLevel="3">
@@ -5816,7 +5792,7 @@
         <v>480</v>
       </c>
       <c r="C481" s="11" t="n">
-        <v>311</v>
+        <v>711</v>
       </c>
     </row>
     <row r="482" ht="22" customHeight="true" outlineLevel="3">
@@ -5824,7 +5800,7 @@
         <v>481</v>
       </c>
       <c r="C482" s="11" t="n">
-        <v>64</v>
+        <v>945</v>
       </c>
     </row>
     <row r="483" ht="22" customHeight="true" outlineLevel="3">
@@ -5832,39 +5808,39 @@
         <v>482</v>
       </c>
       <c r="C483" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="484" ht="22" customHeight="true" outlineLevel="3">
       <c r="B484" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="C484" s="16" t="n">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="485" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C484" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="485" ht="22" customHeight="true" outlineLevel="3">
       <c r="B485" s="15" t="s">
         <v>484</v>
       </c>
       <c r="C485" s="11" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="486" ht="11" customHeight="true" outlineLevel="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="486" ht="22" customHeight="true" outlineLevel="3">
       <c r="B486" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="C486" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C486" s="16" t="n">
+        <v>6774</v>
+      </c>
+    </row>
+    <row r="487" ht="22" customHeight="true" outlineLevel="3">
       <c r="B487" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="C487" s="16" t="n">
-        <v>4525</v>
+      <c r="C487" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="488" ht="22" customHeight="true" outlineLevel="3">
@@ -5872,7 +5848,7 @@
         <v>487</v>
       </c>
       <c r="C488" s="11" t="n">
-        <v>948</v>
+        <v>992</v>
       </c>
     </row>
     <row r="489" ht="22" customHeight="true" outlineLevel="3">
@@ -5880,7 +5856,7 @@
         <v>488</v>
       </c>
       <c r="C489" s="11" t="n">
-        <v>459</v>
+        <v>44</v>
       </c>
     </row>
     <row r="490" ht="22" customHeight="true" outlineLevel="3">
@@ -5888,79 +5864,79 @@
         <v>489</v>
       </c>
       <c r="C490" s="16" t="n">
-        <v>4921</v>
-      </c>
-    </row>
-    <row r="491" ht="11" customHeight="true" outlineLevel="3">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="491" ht="22" customHeight="true" outlineLevel="3">
       <c r="B491" s="15" t="s">
         <v>490</v>
       </c>
       <c r="C491" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="492" ht="11" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="492" ht="22" customHeight="true" outlineLevel="3">
       <c r="B492" s="15" t="s">
         <v>491</v>
       </c>
       <c r="C492" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="493" ht="11" customHeight="true" outlineLevel="3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="493" ht="22" customHeight="true" outlineLevel="3">
       <c r="B493" s="15" t="s">
         <v>492</v>
       </c>
       <c r="C493" s="11" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="494" ht="22" customHeight="true" outlineLevel="3">
       <c r="B494" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="C494" s="16" t="n">
-        <v>2602</v>
-      </c>
-    </row>
-    <row r="495" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C494" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="495" ht="22" customHeight="true" outlineLevel="3">
       <c r="B495" s="15" t="s">
         <v>494</v>
       </c>
       <c r="C495" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="496" ht="11" customHeight="true" outlineLevel="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="496" ht="22" customHeight="true" outlineLevel="3">
       <c r="B496" s="15" t="s">
         <v>495</v>
       </c>
       <c r="C496" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="497" ht="11" customHeight="true" outlineLevel="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="497" ht="22" customHeight="true" outlineLevel="3">
       <c r="B497" s="15" t="s">
         <v>496</v>
       </c>
       <c r="C497" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="498" ht="11" customHeight="true" outlineLevel="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="498" ht="22" customHeight="true" outlineLevel="3">
       <c r="B498" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="C498" s="11" t="n">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="499" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C498" s="16" t="n">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="499" ht="22" customHeight="true" outlineLevel="3">
       <c r="B499" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="C499" s="16" t="n">
-        <v>7329</v>
+      <c r="C499" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="500" ht="22" customHeight="true" outlineLevel="3">
@@ -5968,7 +5944,7 @@
         <v>499</v>
       </c>
       <c r="C500" s="11" t="n">
-        <v>153</v>
+        <v>254</v>
       </c>
     </row>
     <row r="501" ht="22" customHeight="true" outlineLevel="3">
@@ -5976,7 +5952,7 @@
         <v>500</v>
       </c>
       <c r="C501" s="11" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="502" ht="22" customHeight="true" outlineLevel="3">
@@ -5984,23 +5960,23 @@
         <v>501</v>
       </c>
       <c r="C502" s="16" t="n">
-        <v>1763</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="503" ht="22" customHeight="true" outlineLevel="3">
       <c r="B503" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="C503" s="11" t="n">
-        <v>418</v>
+      <c r="C503" s="16" t="n">
+        <v>1109</v>
       </c>
     </row>
     <row r="504" ht="22" customHeight="true" outlineLevel="3">
       <c r="B504" s="15" t="s">
         <v>503</v>
       </c>
-      <c r="C504" s="16" t="n">
-        <v>6649</v>
+      <c r="C504" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="505" ht="22" customHeight="true" outlineLevel="3">
@@ -6008,23 +5984,23 @@
         <v>504</v>
       </c>
       <c r="C505" s="11" t="n">
-        <v>685</v>
+        <v>242</v>
       </c>
     </row>
     <row r="506" ht="22" customHeight="true" outlineLevel="3">
       <c r="B506" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="C506" s="11" t="n">
-        <v>264</v>
+      <c r="C506" s="16" t="n">
+        <v>11209</v>
       </c>
     </row>
     <row r="507" ht="22" customHeight="true" outlineLevel="3">
       <c r="B507" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="C507" s="16" t="n">
-        <v>4046</v>
+      <c r="C507" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="508" ht="22" customHeight="true" outlineLevel="3">
@@ -6032,7 +6008,7 @@
         <v>507</v>
       </c>
       <c r="C508" s="11" t="n">
-        <v>410</v>
+        <v>68</v>
       </c>
     </row>
     <row r="509" ht="22" customHeight="true" outlineLevel="3">
@@ -6040,15 +6016,15 @@
         <v>508</v>
       </c>
       <c r="C509" s="11" t="n">
-        <v>432</v>
+        <v>275</v>
       </c>
     </row>
     <row r="510" ht="22" customHeight="true" outlineLevel="3">
       <c r="B510" s="15" t="s">
         <v>509</v>
       </c>
-      <c r="C510" s="16" t="n">
-        <v>2250</v>
+      <c r="C510" s="11" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="511" ht="22" customHeight="true" outlineLevel="3">
@@ -6056,7 +6032,7 @@
         <v>510</v>
       </c>
       <c r="C511" s="11" t="n">
-        <v>125</v>
+        <v>41</v>
       </c>
     </row>
     <row r="512" ht="22" customHeight="true" outlineLevel="3">
@@ -6064,31 +6040,31 @@
         <v>511</v>
       </c>
       <c r="C512" s="11" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="513" ht="22" customHeight="true" outlineLevel="3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="513" ht="11" customHeight="true" outlineLevel="3">
       <c r="B513" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="C513" s="16" t="n">
-        <v>4803</v>
-      </c>
-    </row>
-    <row r="514" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C513" s="11" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="514" ht="11" customHeight="true" outlineLevel="3">
       <c r="B514" s="15" t="s">
         <v>513</v>
       </c>
-      <c r="C514" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="515" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C514" s="16" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="515" ht="11" customHeight="true" outlineLevel="3">
       <c r="B515" s="15" t="s">
         <v>514</v>
       </c>
       <c r="C515" s="11" t="n">
-        <v>23</v>
+        <v>289</v>
       </c>
     </row>
     <row r="516" ht="22" customHeight="true" outlineLevel="3">
@@ -6096,7 +6072,7 @@
         <v>515</v>
       </c>
       <c r="C516" s="11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" ht="22" customHeight="true" outlineLevel="3">
@@ -6104,7 +6080,7 @@
         <v>516</v>
       </c>
       <c r="C517" s="11" t="n">
-        <v>798</v>
+        <v>116</v>
       </c>
     </row>
     <row r="518" ht="22" customHeight="true" outlineLevel="3">
@@ -6112,7 +6088,7 @@
         <v>517</v>
       </c>
       <c r="C518" s="11" t="n">
-        <v>522</v>
+        <v>93</v>
       </c>
     </row>
     <row r="519" ht="22" customHeight="true" outlineLevel="3">
@@ -6120,15 +6096,15 @@
         <v>518</v>
       </c>
       <c r="C519" s="11" t="n">
-        <v>388</v>
+        <v>40</v>
       </c>
     </row>
     <row r="520" ht="22" customHeight="true" outlineLevel="3">
       <c r="B520" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C520" s="16" t="n">
-        <v>11658</v>
+      <c r="C520" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="521" ht="22" customHeight="true" outlineLevel="3">
@@ -6136,7 +6112,7 @@
         <v>520</v>
       </c>
       <c r="C521" s="11" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" ht="22" customHeight="true" outlineLevel="3">
@@ -6144,15 +6120,15 @@
         <v>521</v>
       </c>
       <c r="C522" s="11" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="523" ht="22" customHeight="true" outlineLevel="3">
       <c r="B523" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="C523" s="11" t="n">
-        <v>72</v>
+      <c r="C523" s="16" t="n">
+        <v>3246</v>
       </c>
     </row>
     <row r="524" ht="22" customHeight="true" outlineLevel="3">
@@ -6160,63 +6136,63 @@
         <v>523</v>
       </c>
       <c r="C524" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="525" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" ht="11" customHeight="true" outlineLevel="3">
       <c r="B525" s="15" t="s">
         <v>524</v>
       </c>
       <c r="C525" s="11" t="n">
-        <v>9</v>
+        <v>357</v>
       </c>
     </row>
     <row r="526" ht="22" customHeight="true" outlineLevel="3">
       <c r="B526" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="C526" s="16" t="n">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="527" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C526" s="11" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="527" ht="22" customHeight="true" outlineLevel="3">
       <c r="B527" s="15" t="s">
         <v>526</v>
       </c>
-      <c r="C527" s="11" t="n">
-        <v>185</v>
+      <c r="C527" s="16" t="n">
+        <v>5209</v>
       </c>
     </row>
     <row r="528" ht="11" customHeight="true" outlineLevel="3">
       <c r="B528" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="C528" s="16" t="n">
-        <v>2449</v>
-      </c>
-    </row>
-    <row r="529" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C528" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="529" ht="22" customHeight="true" outlineLevel="3">
       <c r="B529" s="15" t="s">
         <v>528</v>
       </c>
       <c r="C529" s="11" t="n">
-        <v>556</v>
+        <v>191</v>
       </c>
     </row>
     <row r="530" ht="22" customHeight="true" outlineLevel="3">
       <c r="B530" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="C530" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="531" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C530" s="16" t="n">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="531" ht="11" customHeight="true" outlineLevel="3">
       <c r="B531" s="15" t="s">
         <v>530</v>
       </c>
       <c r="C531" s="11" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532" ht="22" customHeight="true" outlineLevel="3">
@@ -6224,23 +6200,23 @@
         <v>531</v>
       </c>
       <c r="C532" s="11" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
     <row r="533" ht="22" customHeight="true" outlineLevel="3">
       <c r="B533" s="15" t="s">
         <v>532</v>
       </c>
-      <c r="C533" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="534" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C533" s="16" t="n">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="534" ht="11" customHeight="true" outlineLevel="3">
       <c r="B534" s="15" t="s">
         <v>533</v>
       </c>
       <c r="C534" s="11" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="535" ht="22" customHeight="true" outlineLevel="3">
@@ -6248,55 +6224,55 @@
         <v>534</v>
       </c>
       <c r="C535" s="16" t="n">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="536" ht="22" customHeight="true" outlineLevel="3">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="536" ht="11" customHeight="true" outlineLevel="3">
       <c r="B536" s="15" t="s">
         <v>535</v>
       </c>
       <c r="C536" s="11" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="537" ht="22" customHeight="true" outlineLevel="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="537" ht="11" customHeight="true" outlineLevel="3">
       <c r="B537" s="15" t="s">
         <v>536</v>
       </c>
       <c r="C537" s="11" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="538" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="538" ht="11" customHeight="true" outlineLevel="3">
       <c r="B538" s="15" t="s">
         <v>537</v>
       </c>
       <c r="C538" s="16" t="n">
-        <v>5352</v>
-      </c>
-    </row>
-    <row r="539" ht="22" customHeight="true" outlineLevel="3">
+        <v>16850</v>
+      </c>
+    </row>
+    <row r="539" ht="11" customHeight="true" outlineLevel="3">
       <c r="B539" s="15" t="s">
         <v>538</v>
       </c>
       <c r="C539" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="540" ht="11" customHeight="true" outlineLevel="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="540" ht="22" customHeight="true" outlineLevel="3">
       <c r="B540" s="15" t="s">
         <v>539</v>
       </c>
       <c r="C540" s="11" t="n">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="541" ht="22" customHeight="true" outlineLevel="3">
       <c r="B541" s="15" t="s">
         <v>540</v>
       </c>
-      <c r="C541" s="11" t="n">
-        <v>564</v>
+      <c r="C541" s="16" t="n">
+        <v>7601</v>
       </c>
     </row>
     <row r="542" ht="11" customHeight="true" outlineLevel="3">
@@ -6304,55 +6280,55 @@
         <v>541</v>
       </c>
       <c r="C542" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="543" ht="11" customHeight="true" outlineLevel="3">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="543" ht="22" customHeight="true" outlineLevel="3">
       <c r="B543" s="15" t="s">
         <v>542</v>
       </c>
       <c r="C543" s="11" t="n">
-        <v>324</v>
+        <v>430</v>
       </c>
     </row>
     <row r="544" ht="22" customHeight="true" outlineLevel="3">
       <c r="B544" s="15" t="s">
         <v>543</v>
       </c>
-      <c r="C544" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="545" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C544" s="16" t="n">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="545" ht="22" customHeight="true" outlineLevel="3">
       <c r="B545" s="15" t="s">
         <v>544</v>
       </c>
       <c r="C545" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="546" ht="22" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="546" ht="11" customHeight="true" outlineLevel="3">
       <c r="B546" s="15" t="s">
         <v>545</v>
       </c>
-      <c r="C546" s="16" t="n">
-        <v>2262</v>
-      </c>
-    </row>
-    <row r="547" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C546" s="11" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="547" ht="22" customHeight="true" outlineLevel="3">
       <c r="B547" s="15" t="s">
         <v>546</v>
       </c>
       <c r="C547" s="11" t="n">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="548" ht="11" customHeight="true" outlineLevel="3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="548" ht="22" customHeight="true" outlineLevel="3">
       <c r="B548" s="15" t="s">
         <v>547</v>
       </c>
       <c r="C548" s="16" t="n">
-        <v>27099</v>
+        <v>11685</v>
       </c>
     </row>
     <row r="549" ht="11" customHeight="true" outlineLevel="3">
@@ -6360,15 +6336,15 @@
         <v>548</v>
       </c>
       <c r="C549" s="11" t="n">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="550" ht="22" customHeight="true" outlineLevel="3">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="550" ht="11" customHeight="true" outlineLevel="3">
       <c r="B550" s="15" t="s">
         <v>549</v>
       </c>
       <c r="C550" s="11" t="n">
-        <v>5</v>
+        <v>315</v>
       </c>
     </row>
     <row r="551" ht="11" customHeight="true" outlineLevel="3">
@@ -6376,15 +6352,15 @@
         <v>550</v>
       </c>
       <c r="C551" s="11" t="n">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="552" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="552" ht="11" customHeight="true" outlineLevel="3">
       <c r="B552" s="15" t="s">
         <v>551</v>
       </c>
       <c r="C552" s="11" t="n">
-        <v>200</v>
+        <v>599</v>
       </c>
     </row>
     <row r="553" ht="11" customHeight="true" outlineLevel="3">
@@ -6392,23 +6368,23 @@
         <v>552</v>
       </c>
       <c r="C553" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="554" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="554" ht="11" customHeight="true" outlineLevel="3">
       <c r="B554" s="15" t="s">
         <v>553</v>
       </c>
       <c r="C554" s="11" t="n">
-        <v>354</v>
+        <v>730</v>
       </c>
     </row>
     <row r="555" ht="11" customHeight="true" outlineLevel="3">
       <c r="B555" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="C555" s="16" t="n">
-        <v>1788</v>
+      <c r="C555" s="11" t="n">
+        <v>739</v>
       </c>
     </row>
     <row r="556" ht="11" customHeight="true" outlineLevel="3">
@@ -6416,23 +6392,23 @@
         <v>555</v>
       </c>
       <c r="C556" s="11" t="n">
-        <v>363</v>
+        <v>440</v>
       </c>
     </row>
     <row r="557" ht="11" customHeight="true" outlineLevel="3">
       <c r="B557" s="15" t="s">
         <v>556</v>
       </c>
-      <c r="C557" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="558" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C557" s="16" t="n">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="558" ht="22" customHeight="true" outlineLevel="3">
       <c r="B558" s="15" t="s">
         <v>557</v>
       </c>
       <c r="C558" s="11" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="559" ht="11" customHeight="true" outlineLevel="3">
@@ -6440,127 +6416,63 @@
         <v>558</v>
       </c>
       <c r="C559" s="16" t="n">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="560" ht="11" customHeight="true" outlineLevel="3">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="560" ht="22" customHeight="true" outlineLevel="3">
       <c r="B560" s="15" t="s">
         <v>559</v>
       </c>
       <c r="C560" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="561" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="561" ht="22" customHeight="true" outlineLevel="3">
       <c r="B561" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="C561" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="562" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C561" s="16" t="n">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="562" ht="22" customHeight="true" outlineLevel="3">
       <c r="B562" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="C562" s="16" t="n">
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="563" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B563" s="15" t="s">
+      <c r="C562" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="563" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B563" s="17" t="s">
         <v>562</v>
       </c>
-      <c r="C563" s="11" t="n">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="564" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B564" s="15" t="s">
+      <c r="C563" s="12" t="n">
+        <v>19673</v>
+      </c>
+    </row>
+    <row r="564" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B564" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="C564" s="16" t="n">
-        <v>4699</v>
-      </c>
-    </row>
-    <row r="565" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B565" s="15" t="s">
+      <c r="C564" s="11" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="565" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B565" s="18" t="s">
         <v>564</v>
       </c>
       <c r="C565" s="11" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="566" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B566" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="566" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B566" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="C566" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="567" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B567" s="17" t="s">
-        <v>566</v>
-      </c>
-      <c r="C567" s="12" t="n">
-        <v>100913</v>
-      </c>
-    </row>
-    <row r="568" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B568" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="C568" s="16" t="n">
-        <v>21735</v>
-      </c>
-    </row>
-    <row r="569" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B569" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="C569" s="16" t="n">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="570" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B570" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="C570" s="16" t="n">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="571" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B571" s="18" t="s">
-        <v>570</v>
-      </c>
-      <c r="C571" s="16" t="n">
-        <v>36330</v>
-      </c>
-    </row>
-    <row r="572" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B572" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="C572" s="16" t="n">
-        <v>21048</v>
-      </c>
-    </row>
-    <row r="573" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B573" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="C573" s="16" t="n">
-        <v>2880</v>
-      </c>
-    </row>
-    <row r="574" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B574" s="18" t="s">
-        <v>573</v>
-      </c>
-      <c r="C574" s="16" t="n">
-        <v>15940</v>
+      <c r="C566" s="16" t="n">
+        <v>19008</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:13</t>
+    <t>Период: на 16.01.2026 15:05:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,48 +62,57 @@
     <t>Картонна коробка "Новорічні іграшки" (26-14*4 )</t>
   </si>
   <si>
-    <t>Коробка "Куб синій з оленем" (26-03*2 )</t>
-  </si>
-  <si>
     <t>МРІЯ</t>
   </si>
   <si>
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
-    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -122,39 +131,39 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
-    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -167,18 +176,12 @@
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -191,9 +194,6 @@
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -221,9 +221,6 @@
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -239,18 +236,12 @@
     <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт</t>
-  </si>
-  <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -263,9 +254,6 @@
     <t>Коріандр мелений УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Коріандр мелений УБ 20г /30шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Куркума мелена УБ 15г /38шт</t>
   </si>
   <si>
@@ -281,9 +269,6 @@
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
-    <t>Перець духмяний УБ 20г /22шт</t>
-  </si>
-  <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
   </si>
   <si>
@@ -299,6 +284,9 @@
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
@@ -308,36 +296,21 @@
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
+    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>РОШЕН</t>
   </si>
   <si>
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -347,9 +320,6 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -362,45 +332,21 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -410,9 +356,6 @@
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -422,21 +365,12 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -446,16 +380,13 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з ванільною начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з молочною начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
+    <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
@@ -464,57 +395,27 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ВКФ 216г /16шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -527,6 +428,9 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -542,24 +446,15 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -599,15 +494,6 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -617,72 +503,39 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -698,73 +551,37 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
@@ -773,72 +590,42 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
@@ -884,9 +671,6 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -899,9 +683,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -980,42 +761,24 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
-    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -1028,12 +791,6 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -1049,27 +806,15 @@
     <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
-    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>2 CRACK з шоколадною начинкою ККФ 190г /28шт</t>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
@@ -1085,9 +830,6 @@
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
-    <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
@@ -1100,16 +842,13 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /АКЦІЯ ВІП 1</t>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
@@ -1118,9 +857,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -1133,49 +869,31 @@
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
@@ -1193,31 +911,13 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Набір кондитерських виробів4</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Boo! Bear РЦ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
@@ -1226,7 +926,7 @@
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
@@ -1235,6 +935,9 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
@@ -1259,9 +962,6 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -1271,6 +971,9 @@
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
@@ -1283,6 +986,9 @@
     <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Sorrento ВКФ 1кг /9пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1316,12 +1022,6 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
@@ -1355,12 +1055,6 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -1370,39 +1064,18 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1421,64 +1094,49 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
@@ -1490,28 +1148,13 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
@@ -1523,10 +1166,7 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
@@ -1544,13 +1184,19 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1559,27 +1205,15 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
@@ -1595,9 +1229,6 @@
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
@@ -1616,45 +1247,33 @@
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦИЯ ВИП</t>
+    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
-  </si>
-  <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
   </si>
   <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1662,18 +1281,6 @@
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1535,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C552"/>
+  <dimension ref="C421"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1993,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>903</v>
+        <v>594</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -2001,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>939275</v>
+        <v>675310</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -2009,7 +1616,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -2020,28 +1627,28 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B15" s="15" t="s">
+    <row r="15" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B16" s="13" t="s">
+      <c r="C15" s="12" t="n">
+        <v>157301</v>
+      </c>
+    </row>
+    <row r="16" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>217931</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B17" s="16" t="s">
+        <v>26151</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>20263</v>
+      <c r="C17" s="18" t="n">
+        <v>7453</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -2049,7 +1656,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>2845</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -2057,15 +1664,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>178</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>4200</v>
+      <c r="C20" s="11" t="n">
+        <v>539</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -2073,15 +1680,15 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>30</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>555</v>
+      <c r="C22" s="18" t="n">
+        <v>2348</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -2089,7 +1696,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>824</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,7 +1704,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -2105,23 +1712,23 @@
         <v>24</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>3549</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>1055</v>
+      <c r="C26" s="11" t="n">
+        <v>920</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="18" t="n">
-        <v>5293</v>
+      <c r="C27" s="11" t="n">
+        <v>375</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -2129,23 +1736,23 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B29" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B29" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>89573</v>
+      <c r="C29" s="11" t="n">
+        <v>394</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="18" t="n">
-        <v>6029</v>
+      <c r="C30" s="11" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -2153,15 +1760,15 @@
         <v>30</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>28214</v>
-      </c>
-    </row>
-    <row r="32" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B32" s="17" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="32" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B32" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>4794</v>
+      <c r="C32" s="12" t="n">
+        <v>61965</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -2169,15 +1776,15 @@
         <v>32</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>22598</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>722</v>
+      <c r="C34" s="18" t="n">
+        <v>39962</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -2185,7 +1792,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>12925</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -2193,31 +1800,31 @@
         <v>35</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>3252</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>6870</v>
+      <c r="C37" s="11" t="n">
+        <v>608</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>43</v>
+      <c r="C38" s="18" t="n">
+        <v>6504</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="18" t="n">
-        <v>1492</v>
+      <c r="C39" s="11" t="n">
+        <v>938</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -2225,7 +1832,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -2233,7 +1840,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>842</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -2241,23 +1848,23 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B43" s="16" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="12" t="n">
-        <v>32062</v>
-      </c>
-    </row>
-    <row r="44" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C43" s="11" t="n">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="true" outlineLevel="3">
       <c r="B44" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="18" t="n">
-        <v>1146</v>
+      <c r="C44" s="11" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -2265,23 +1872,23 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" ht="11" customHeight="true" outlineLevel="3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="true" outlineLevel="3">
       <c r="B46" s="17" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="47" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B47" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B47" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="18" t="n">
-        <v>2291</v>
+      <c r="C47" s="12" t="n">
+        <v>20914</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -2289,15 +1896,15 @@
         <v>47</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>1229</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="18" t="n">
-        <v>2751</v>
+      <c r="C49" s="11" t="n">
+        <v>532</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2305,23 +1912,23 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1</v>
+        <v>658</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>964</v>
+      <c r="C51" s="18" t="n">
+        <v>1233</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="18" t="n">
-        <v>1247</v>
+      <c r="C52" s="11" t="n">
+        <v>924</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2329,23 +1936,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2</v>
+        <v>723</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>743</v>
+      <c r="C54" s="18" t="n">
+        <v>1439</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="18" t="n">
-        <v>1966</v>
+      <c r="C55" s="11" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2353,23 +1960,23 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>46</v>
+        <v>845</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="18" t="n">
-        <v>2277</v>
+      <c r="C57" s="11" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>1</v>
+      <c r="C58" s="18" t="n">
+        <v>1333</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2377,15 +1984,15 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>630</v>
+        <v>785</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="18" t="n">
-        <v>1013</v>
+      <c r="C60" s="11" t="n">
+        <v>795</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2393,7 +2000,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>898</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2401,7 +2008,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>1402</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2409,7 +2016,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>437</v>
+        <v>800</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2417,7 +2024,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1380</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2425,7 +2032,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>413</v>
+        <v>337</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2433,39 +2040,39 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>414</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="18" t="n">
-        <v>1449</v>
+      <c r="C67" s="11" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C68" s="18" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>858</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>942</v>
+      <c r="C70" s="18" t="n">
+        <v>1172</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2473,15 +2080,15 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>296</v>
+        <v>737</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="18" t="n">
-        <v>1076</v>
+      <c r="C72" s="11" t="n">
+        <v>557</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2489,7 +2096,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>518</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2497,15 +2104,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B75" s="17" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B75" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="18" t="n">
-        <v>3996</v>
+      <c r="C75" s="12" t="n">
+        <v>48271</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2513,23 +2120,23 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>954</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B78" s="16" t="s">
+      <c r="C77" s="18" t="n">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="12" t="n">
-        <v>76033</v>
+      <c r="C78" s="18" t="n">
+        <v>1805</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2537,7 +2144,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="18" t="n">
-        <v>1793</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,7 +2152,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>4052</v>
+        <v>8091</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2553,15 +2160,15 @@
         <v>80</v>
       </c>
       <c r="C81" s="18" t="n">
-        <v>2233</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>10</v>
+      <c r="C82" s="18" t="n">
+        <v>1744</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
@@ -2569,15 +2176,15 @@
         <v>82</v>
       </c>
       <c r="C83" s="18" t="n">
-        <v>3053</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="18" t="n">
-        <v>12771</v>
+      <c r="C84" s="11" t="n">
+        <v>617</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,7 +2192,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>2636</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2593,7 +2200,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>4322</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,7 +2208,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>4142</v>
+        <v>12613</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2609,7 +2216,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2617,79 +2224,79 @@
         <v>88</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>1454</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="18" t="n">
-        <v>8781</v>
+      <c r="C90" s="11" t="n">
+        <v>959</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="18" t="n">
-        <v>2304</v>
+      <c r="C91" s="11" t="n">
+        <v>607</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="18" t="n">
-        <v>24627</v>
+      <c r="C92" s="11" t="n">
+        <v>838</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
       <c r="B93" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="18" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B94" s="17" t="s">
+      <c r="C93" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B94" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="18" t="n">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B95" s="17" t="s">
+      <c r="C94" s="12" t="n">
+        <v>517958</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B95" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="12" t="n">
+        <v>148563</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B97" s="13" t="s">
+      <c r="C96" s="18" t="n">
+        <v>12593</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B97" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="12" t="n">
-        <v>721228</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B98" s="16" t="s">
+      <c r="C97" s="18" t="n">
+        <v>20589</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B98" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="12" t="n">
-        <v>182551</v>
+      <c r="C98" s="18" t="n">
+        <v>5730</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
@@ -2697,7 +2304,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>38</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
@@ -2705,7 +2312,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="18" t="n">
-        <v>4059</v>
+        <v>14427</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2713,15 +2320,15 @@
         <v>100</v>
       </c>
       <c r="C101" s="18" t="n">
-        <v>10752</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>600</v>
+      <c r="C102" s="18" t="n">
+        <v>15042</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
@@ -2729,183 +2336,183 @@
         <v>102</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>4450</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+        <v>7421</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="18" t="n">
-        <v>3204</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+        <v>12043</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="17" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="18" t="n">
-        <v>5430</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+        <v>22937</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="17" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="18" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="17" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>14405</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B108" s="17" t="s">
+        <v>30550</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B108" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="18" t="n">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C108" s="12" t="n">
+        <v>5081</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="18" t="n">
-        <v>2786</v>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C109" s="11" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="18" t="n">
-        <v>4740</v>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C110" s="11" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="18" t="n">
-        <v>15555</v>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C111" s="11" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="3">
       <c r="B112" s="17" t="s">
         <v>111</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>6960</v>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="true" outlineLevel="3">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="17" t="s">
         <v>112</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>16103</v>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="true" outlineLevel="3">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="114" ht="11" customHeight="true" outlineLevel="3">
       <c r="B114" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="18" t="n">
-        <v>10444</v>
-      </c>
-    </row>
-    <row r="115" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C114" s="11" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="115" ht="11" customHeight="true" outlineLevel="3">
       <c r="B115" s="17" t="s">
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="18" t="n">
-        <v>3909</v>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C116" s="11" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="18" t="n">
-        <v>5829</v>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B118" s="17" t="s">
+      <c r="C117" s="11" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="118" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B118" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="18" t="n">
-        <v>26062</v>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C118" s="12" t="n">
+        <v>81395</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="18" t="n">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C119" s="11" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="18" t="n">
-        <v>6306</v>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C120" s="11" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="3">
       <c r="B121" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="18" t="n">
-        <v>10928</v>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C121" s="11" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="18" t="n">
-        <v>17915</v>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C122" s="11" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C123" s="18" t="n">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="17" t="s">
         <v>123</v>
       </c>
       <c r="C124" s="18" t="n">
-        <v>4660</v>
-      </c>
-    </row>
-    <row r="125" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B125" s="16" t="s">
+        <v>23734</v>
+      </c>
+    </row>
+    <row r="125" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B125" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="12" t="n">
-        <v>12212</v>
+      <c r="C125" s="18" t="n">
+        <v>27230</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2913,7 +2520,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>1439</v>
+        <v>11753</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2921,31 +2528,31 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>152</v>
+        <v>439</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="18" t="n">
-        <v>1094</v>
+      <c r="C128" s="11" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="18" t="n">
-        <v>1278</v>
+      <c r="C129" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="18" t="n">
-        <v>1908</v>
+      <c r="C130" s="11" t="n">
+        <v>659</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2953,7 +2560,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>112</v>
+        <v>231</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2961,7 +2568,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>963</v>
+        <v>500</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2969,7 +2576,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="18" t="n">
-        <v>1536</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2977,7 +2584,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>308</v>
+        <v>985</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2985,23 +2592,23 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>214</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>639</v>
+      <c r="C136" s="18" t="n">
+        <v>1888</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="18" t="n">
-        <v>1058</v>
+      <c r="C137" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -3009,23 +2616,23 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="139" ht="22" customHeight="true" outlineLevel="3">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="18" t="n">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="140" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B140" s="16" t="s">
+      <c r="C139" s="11" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="140" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B140" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="12" t="n">
-        <v>68838</v>
+      <c r="C140" s="11" t="n">
+        <v>374</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -3033,47 +2640,47 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>734</v>
+        <v>762</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>377</v>
+      <c r="C142" s="18" t="n">
+        <v>1876</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="11" t="n">
-        <v>5</v>
+      <c r="C143" s="18" t="n">
+        <v>1081</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
       <c r="B144" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="11" t="n">
-        <v>31</v>
+      <c r="C144" s="18" t="n">
+        <v>2085</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="11" t="n">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="146" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B146" s="17" t="s">
+      <c r="C145" s="18" t="n">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="146" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B146" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="11" t="n">
-        <v>5</v>
+      <c r="C146" s="12" t="n">
+        <v>98835</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -3081,31 +2688,31 @@
         <v>146</v>
       </c>
       <c r="C147" s="18" t="n">
-        <v>10860</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="18" t="n">
-        <v>12862</v>
+      <c r="C148" s="11" t="n">
+        <v>402</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="18" t="n">
-        <v>8460</v>
+      <c r="C149" s="11" t="n">
+        <v>317</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="18" t="n">
-        <v>4818</v>
+      <c r="C150" s="11" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -3113,15 +2720,15 @@
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>15578</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>5</v>
+      <c r="C152" s="18" t="n">
+        <v>1180</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -3129,7 +2736,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>368</v>
+        <v>250</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -3137,7 +2744,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -3145,7 +2752,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>255</v>
+        <v>224</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -3153,15 +2760,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>308</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>15</v>
+      <c r="C157" s="18" t="n">
+        <v>3332</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -3169,15 +2776,15 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>196</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>30</v>
+      <c r="C159" s="18" t="n">
+        <v>2722</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -3185,7 +2792,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>704</v>
+        <v>149</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -3193,15 +2800,15 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>10</v>
+        <v>636</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="11" t="n">
-        <v>311</v>
+      <c r="C162" s="18" t="n">
+        <v>5018</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -3209,15 +2816,15 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>13</v>
+      <c r="C164" s="18" t="n">
+        <v>1463</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3225,7 +2832,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>26</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3233,7 +2840,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="18" t="n">
-        <v>2058</v>
+        <v>7023</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -3241,7 +2848,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="18" t="n">
-        <v>1269</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -3249,7 +2856,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3257,39 +2864,39 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>925</v>
+        <v>978</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
       <c r="B170" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="18" t="n">
-        <v>1898</v>
+      <c r="C170" s="11" t="n">
+        <v>437</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>392</v>
+      <c r="C171" s="18" t="n">
+        <v>2114</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="11" t="n">
-        <v>562</v>
+      <c r="C172" s="18" t="n">
+        <v>2653</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="11" t="n">
-        <v>669</v>
+      <c r="C173" s="18" t="n">
+        <v>1094</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -3297,7 +2904,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>731</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3305,15 +2912,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="18" t="n">
-        <v>1864</v>
+      <c r="C176" s="11" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,7 +2928,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>16</v>
+        <v>308</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3329,7 +2936,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3337,31 +2944,31 @@
         <v>178</v>
       </c>
       <c r="C179" s="18" t="n">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="180" ht="11" customHeight="true" outlineLevel="3">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="true" outlineLevel="3">
       <c r="B180" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B181" s="16" t="s">
+      <c r="C180" s="18" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B181" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="12" t="n">
-        <v>170377</v>
+      <c r="C181" s="11" t="n">
+        <v>454</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="18" t="n">
-        <v>1633</v>
+      <c r="C182" s="11" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3369,15 +2976,15 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>289</v>
+        <v>333</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>60</v>
+      <c r="C184" s="18" t="n">
+        <v>6812</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,7 +2992,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>149</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3393,15 +3000,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="18" t="n">
-        <v>2624</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="18" t="n">
-        <v>1341</v>
+      <c r="C187" s="11" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3409,15 +3016,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>599</v>
+        <v>372</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>701</v>
+      <c r="C189" s="18" t="n">
+        <v>3684</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3425,23 +3032,23 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>533</v>
+        <v>888</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="11" t="n">
-        <v>347</v>
+      <c r="C191" s="18" t="n">
+        <v>1635</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="18" t="n">
-        <v>3815</v>
+      <c r="C192" s="11" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3449,31 +3056,31 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>788</v>
+        <v>424</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>407</v>
+      <c r="C194" s="18" t="n">
+        <v>2417</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="11" t="n">
-        <v>59</v>
+      <c r="C195" s="18" t="n">
+        <v>1913</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="11" t="n">
-        <v>200</v>
+      <c r="C196" s="18" t="n">
+        <v>1058</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3481,23 +3088,23 @@
         <v>196</v>
       </c>
       <c r="C197" s="18" t="n">
-        <v>5252</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>111</v>
+      <c r="C198" s="18" t="n">
+        <v>1776</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>161</v>
+      <c r="C199" s="18" t="n">
+        <v>19209</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3505,7 +3112,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>568</v>
+        <v>302</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3513,31 +3120,31 @@
         <v>200</v>
       </c>
       <c r="C201" s="18" t="n">
-        <v>10811</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>342</v>
+      <c r="C202" s="18" t="n">
+        <v>1868</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="11" t="n">
-        <v>430</v>
+      <c r="C203" s="18" t="n">
+        <v>1646</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="18" t="n">
-        <v>4626</v>
+      <c r="C204" s="11" t="n">
+        <v>522</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3545,31 +3152,31 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>290</v>
+        <v>252</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="11" t="n">
-        <v>130</v>
+      <c r="C206" s="18" t="n">
+        <v>2771</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>192</v>
+      <c r="C207" s="18" t="n">
+        <v>4457</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="18" t="n">
-        <v>10876</v>
+      <c r="C208" s="11" t="n">
+        <v>819</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3577,23 +3184,23 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="210" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B210" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="210" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B210" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>734</v>
+      <c r="C210" s="12" t="n">
+        <v>64595</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>285</v>
+      <c r="C211" s="18" t="n">
+        <v>1127</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,15 +3208,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>27</v>
+        <v>945</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>716</v>
+      <c r="C213" s="18" t="n">
+        <v>2260</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3617,7 +3224,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>428</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,7 +3232,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>44</v>
+        <v>741</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3633,63 +3240,63 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>54</v>
+      <c r="C217" s="18" t="n">
+        <v>5794</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="18" t="n">
-        <v>3871</v>
+      <c r="C218" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="18" t="n">
-        <v>1182</v>
+      <c r="C219" s="11" t="n">
+        <v>187</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="18" t="n">
-        <v>1789</v>
+      <c r="C220" s="11" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="11" t="n">
-        <v>190</v>
+      <c r="C221" s="18" t="n">
+        <v>1458</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="18" t="n">
-        <v>2381</v>
+      <c r="C222" s="11" t="n">
+        <v>592</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>277</v>
+      <c r="C223" s="18" t="n">
+        <v>2272</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,111 +3304,111 @@
         <v>223</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>1351</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="11" t="n">
-        <v>340</v>
+      <c r="C225" s="18" t="n">
+        <v>1983</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>353</v>
+      <c r="C226" s="18" t="n">
+        <v>1154</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C227" s="18" t="n">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="18" t="n">
-        <v>3713</v>
+      <c r="C228" s="11" t="n">
+        <v>725</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>293</v>
+      <c r="C229" s="18" t="n">
+        <v>1801</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="11" t="n">
-        <v>80</v>
+      <c r="C230" s="18" t="n">
+        <v>1371</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="18" t="n">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C231" s="11" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="17" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>1101</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="11" t="n">
-        <v>685</v>
+      <c r="C233" s="18" t="n">
+        <v>2873</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C234" s="18" t="n">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="17" t="s">
         <v>234</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>1786</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>602</v>
+      <c r="C236" s="18" t="n">
+        <v>2567</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="11" t="n">
-        <v>473</v>
+      <c r="C237" s="18" t="n">
+        <v>2778</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3809,31 +3416,31 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>119</v>
+        <v>824</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>374</v>
+      <c r="C239" s="18" t="n">
+        <v>1004</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="11" t="n">
-        <v>237</v>
+      <c r="C240" s="18" t="n">
+        <v>4038</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>38</v>
+      <c r="C241" s="18" t="n">
+        <v>1833</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3841,39 +3448,39 @@
         <v>241</v>
       </c>
       <c r="C242" s="18" t="n">
-        <v>10118</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="11" t="n">
-        <v>585</v>
+      <c r="C243" s="18" t="n">
+        <v>2695</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>552</v>
+      <c r="C244" s="18" t="n">
+        <v>7807</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="246" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B246" s="17" t="s">
+      <c r="C245" s="18" t="n">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="246" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B246" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="18" t="n">
-        <v>5550</v>
+      <c r="C246" s="12" t="n">
+        <v>6194</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3881,7 +3488,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>407</v>
+        <v>868</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3889,7 +3496,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>512</v>
+        <v>711</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3897,23 +3504,23 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="18" t="n">
-        <v>4115</v>
+      <c r="C250" s="11" t="n">
+        <v>508</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="18" t="n">
-        <v>2577</v>
+      <c r="C251" s="11" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3921,15 +3528,15 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>428</v>
+        <v>615</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="18" t="n">
-        <v>2957</v>
+      <c r="C253" s="11" t="n">
+        <v>663</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3937,7 +3544,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>54</v>
+        <v>384</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3945,7 +3552,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>578</v>
+        <v>304</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3953,15 +3560,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>189</v>
+        <v>693</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="18" t="n">
-        <v>2915</v>
+      <c r="C257" s="11" t="n">
+        <v>953</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3969,15 +3576,15 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>441</v>
+        <v>91</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="18" t="n">
-        <v>1898</v>
+      <c r="C259" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3985,15 +3592,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="261" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B261" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B261" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="18" t="n">
-        <v>3279</v>
+      <c r="C261" s="12" t="n">
+        <v>28446</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -4001,7 +3608,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>331</v>
+        <v>352</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -4009,15 +3616,15 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>861</v>
+        <v>353</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="18" t="n">
-        <v>4911</v>
+      <c r="C264" s="11" t="n">
+        <v>459</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -4025,23 +3632,23 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>626</v>
+        <v>461</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="18" t="n">
-        <v>1725</v>
+      <c r="C266" s="11" t="n">
+        <v>315</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="18" t="n">
-        <v>20217</v>
+      <c r="C267" s="11" t="n">
+        <v>394</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -4049,15 +3656,15 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="269" ht="11" customHeight="true" outlineLevel="3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="true" outlineLevel="3">
       <c r="B269" s="17" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>269</v>
+        <v>39</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -4065,31 +3672,31 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>79</v>
+        <v>253</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="18" t="n">
-        <v>4897</v>
+      <c r="C271" s="11" t="n">
+        <v>435</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>224</v>
+      <c r="C272" s="18" t="n">
+        <v>1209</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="18" t="n">
-        <v>1780</v>
+      <c r="C273" s="11" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -4097,71 +3704,71 @@
         <v>273</v>
       </c>
       <c r="C274" s="18" t="n">
-        <v>3955</v>
-      </c>
-    </row>
-    <row r="275" ht="11" customHeight="true" outlineLevel="3">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="true" outlineLevel="3">
       <c r="B275" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="18" t="n">
-        <v>3124</v>
-      </c>
-    </row>
-    <row r="276" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C275" s="11" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="276" ht="22" customHeight="true" outlineLevel="3">
       <c r="B276" s="17" t="s">
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="277" ht="11" customHeight="true" outlineLevel="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="277" ht="22" customHeight="true" outlineLevel="3">
       <c r="B277" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="18" t="n">
-        <v>4574</v>
-      </c>
-    </row>
-    <row r="278" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C277" s="11" t="n">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="278" ht="22" customHeight="true" outlineLevel="3">
       <c r="B278" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="18" t="n">
-        <v>4696</v>
-      </c>
-    </row>
-    <row r="279" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C278" s="11" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="279" ht="22" customHeight="true" outlineLevel="3">
       <c r="B279" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="18" t="n">
-        <v>4755</v>
-      </c>
-    </row>
-    <row r="280" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C279" s="11" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="true" outlineLevel="3">
       <c r="B280" s="17" t="s">
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B281" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B281" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="12" t="n">
-        <v>75193</v>
-      </c>
-    </row>
-    <row r="282" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C281" s="11" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="282" ht="22" customHeight="true" outlineLevel="3">
       <c r="B282" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="18" t="n">
-        <v>1510</v>
+      <c r="C282" s="11" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -4169,15 +3776,15 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>688</v>
+        <v>817</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="18" t="n">
-        <v>2036</v>
+      <c r="C284" s="11" t="n">
+        <v>599</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -4185,15 +3792,15 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="18" t="n">
-        <v>1103</v>
+      <c r="C286" s="11" t="n">
+        <v>227</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -4201,7 +3808,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="18" t="n">
-        <v>1528</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -4209,15 +3816,15 @@
         <v>287</v>
       </c>
       <c r="C288" s="18" t="n">
-        <v>8636</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="11" t="n">
-        <v>67</v>
+      <c r="C289" s="18" t="n">
+        <v>1180</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -4225,15 +3832,15 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>50</v>
+        <v>967</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="11" t="n">
-        <v>345</v>
+      <c r="C291" s="18" t="n">
+        <v>2559</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -4241,23 +3848,23 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>566</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="11" t="n">
-        <v>976</v>
+      <c r="C293" s="18" t="n">
+        <v>2170</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="11" t="n">
-        <v>7</v>
+      <c r="C294" s="18" t="n">
+        <v>1152</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4265,15 +3872,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>364</v>
+        <v>184</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="18" t="n">
-        <v>2664</v>
+      <c r="C296" s="11" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4281,15 +3888,15 @@
         <v>296</v>
       </c>
       <c r="C297" s="18" t="n">
-        <v>3842</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B298" s="17" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B298" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="18" t="n">
-        <v>3251</v>
+      <c r="C298" s="12" t="n">
+        <v>52151</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -4297,15 +3904,15 @@
         <v>298</v>
       </c>
       <c r="C299" s="18" t="n">
-        <v>1114</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="C300" s="18" t="n">
-        <v>2050</v>
+      <c r="C300" s="11" t="n">
+        <v>910</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4313,23 +3920,23 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="302" ht="11" customHeight="true" outlineLevel="3">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="true" outlineLevel="3">
       <c r="B302" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="11" t="n">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C302" s="18" t="n">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="17" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="18" t="n">
-        <v>1631</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4337,23 +3944,23 @@
         <v>303</v>
       </c>
       <c r="C304" s="18" t="n">
-        <v>1245</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="18" t="n">
-        <v>3141</v>
+      <c r="C305" s="11" t="n">
+        <v>871</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="18" t="n">
-        <v>3319</v>
+      <c r="C306" s="11" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4361,7 +3968,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>3975</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4369,31 +3976,31 @@
         <v>307</v>
       </c>
       <c r="C308" s="18" t="n">
-        <v>2227</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="18" t="n">
-        <v>2808</v>
+      <c r="C309" s="11" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="18" t="n">
-        <v>3427</v>
+      <c r="C310" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="18" t="n">
-        <v>1017</v>
+      <c r="C311" s="11" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4401,79 +4008,79 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>810</v>
+        <v>300</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="18" t="n">
-        <v>4982</v>
+      <c r="C313" s="11" t="n">
+        <v>421</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="18" t="n">
-        <v>2103</v>
+      <c r="C314" s="11" t="n">
+        <v>525</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="18" t="n">
-        <v>1279</v>
+      <c r="C315" s="11" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="18" t="n">
-        <v>1356</v>
+      <c r="C316" s="11" t="n">
+        <v>647</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="18" t="n">
-        <v>7764</v>
+      <c r="C317" s="11" t="n">
+        <v>633</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="18" t="n">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B319" s="16" t="s">
+      <c r="C318" s="11" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B319" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="12" t="n">
-        <v>5928</v>
+      <c r="C319" s="18" t="n">
+        <v>1291</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="11" t="n">
-        <v>781</v>
+      <c r="C320" s="18" t="n">
+        <v>1391</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>374</v>
+      <c r="C321" s="18" t="n">
+        <v>2284</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -4481,7 +4088,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>157</v>
+        <v>737</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4489,7 +4096,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>392</v>
+        <v>110</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4497,7 +4104,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>39</v>
+        <v>893</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4505,15 +4112,15 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>397</v>
+        <v>675</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>59</v>
+      <c r="C326" s="18" t="n">
+        <v>2264</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -4521,7 +4128,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4529,7 +4136,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>124</v>
+        <v>889</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4537,7 +4144,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>734</v>
+        <v>512</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4545,7 +4152,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>30</v>
+        <v>989</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4553,47 +4160,47 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>214</v>
+        <v>938</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="C332" s="11" t="n">
-        <v>376</v>
+      <c r="C332" s="18" t="n">
+        <v>1067</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>359</v>
+      <c r="C333" s="18" t="n">
+        <v>1133</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="11" t="n">
-        <v>398</v>
+      <c r="C334" s="18" t="n">
+        <v>9503</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>409</v>
+      <c r="C335" s="18" t="n">
+        <v>5145</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="11" t="n">
-        <v>153</v>
+      <c r="C336" s="18" t="n">
+        <v>1135</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4601,7 +4208,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>362</v>
+        <v>430</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4609,15 +4216,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>17</v>
+      <c r="C339" s="18" t="n">
+        <v>1360</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4625,23 +4232,23 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B341" s="17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B341" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="11" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B342" s="16" t="s">
+      <c r="C341" s="14" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="12" t="n">
-        <v>56065</v>
+      <c r="C342" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4649,7 +4256,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>516</v>
+        <v>67</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4657,15 +4264,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B345" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B345" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>283</v>
+      <c r="C345" s="12" t="n">
+        <v>32609</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4673,7 +4280,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>212</v>
+        <v>90</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4681,39 +4288,39 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="17" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="17" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" ht="33" customHeight="true" outlineLevel="3">
       <c r="B350" s="17" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
       <c r="B351" s="17" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>491</v>
+        <v>87</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4721,15 +4328,15 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
       <c r="B353" s="17" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>747</v>
+        <v>424</v>
       </c>
     </row>
     <row r="354" ht="22" customHeight="true" outlineLevel="3">
@@ -4737,23 +4344,23 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="355" ht="22" customHeight="true" outlineLevel="3">
       <c r="B355" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C355" s="18" t="n">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="17" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4761,7 +4368,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>455</v>
+        <v>180</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4769,31 +4376,31 @@
         <v>357</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>1560</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="18" t="n">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C359" s="11" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="true" outlineLevel="3">
       <c r="B360" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="18" t="n">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C360" s="11" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
       <c r="B361" s="17" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>11</v>
+        <v>109</v>
       </c>
     </row>
     <row r="362" ht="22" customHeight="true" outlineLevel="3">
@@ -4801,7 +4408,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" ht="22" customHeight="true" outlineLevel="3">
@@ -4809,7 +4416,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>38</v>
+        <v>515</v>
       </c>
     </row>
     <row r="364" ht="22" customHeight="true" outlineLevel="3">
@@ -4817,7 +4424,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>21</v>
+        <v>266</v>
       </c>
     </row>
     <row r="365" ht="22" customHeight="true" outlineLevel="3">
@@ -4825,7 +4432,7 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="366" ht="22" customHeight="true" outlineLevel="3">
@@ -4833,15 +4440,15 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>608</v>
+        <v>396</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="11" t="n">
-        <v>11</v>
+      <c r="C367" s="18" t="n">
+        <v>1159</v>
       </c>
     </row>
     <row r="368" ht="22" customHeight="true" outlineLevel="3">
@@ -4849,7 +4456,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>7</v>
+        <v>616</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4857,7 +4464,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>451</v>
+        <v>122</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
@@ -4865,79 +4472,79 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="true" outlineLevel="3">
       <c r="B371" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="17" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="17" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="17" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="17" t="s">
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="17" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="17" t="s">
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
       <c r="B379" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="18" t="n">
-        <v>3812</v>
+      <c r="C379" s="11" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="true" outlineLevel="3">
@@ -4945,95 +4552,95 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="18" t="n">
-        <v>2727</v>
-      </c>
-    </row>
-    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C381" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="18" t="n">
-        <v>2378</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C382" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="17" t="s">
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
       <c r="B384" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="18" t="n">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C384" s="11" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="18" t="n">
-        <v>2321</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C385" s="11" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="17" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
       <c r="B387" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="C387" s="18" t="n">
-        <v>4761</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C387" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="18" t="n">
-        <v>15682</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C388" s="11" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="18" t="n">
-        <v>3077</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C389" s="11" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="391" ht="22" customHeight="true" outlineLevel="3">
       <c r="B391" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="C391" s="18" t="n">
-        <v>5686</v>
+      <c r="C391" s="11" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -5041,71 +4648,71 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B393" s="16" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B393" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="14" t="n">
-        <v>-44</v>
+      <c r="C393" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B394" s="19" t="s">
+      <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="14" t="n">
-        <v>-44</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B395" s="20" t="s">
+      <c r="C394" s="11" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B395" s="17" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B396" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B397" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B398" s="16" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B398" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="12" t="n">
-        <v>72498</v>
+      <c r="C398" s="11" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
       <c r="B399" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="18" t="n">
-        <v>4048</v>
+      <c r="C399" s="11" t="n">
+        <v>442</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="18" t="n">
-        <v>2167</v>
+      <c r="C400" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
@@ -5113,47 +4720,47 @@
         <v>400</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
       <c r="B402" s="17" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>341</v>
+        <v>660</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="18" t="n">
-        <v>2017</v>
+      <c r="C403" s="11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
       <c r="B404" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="18" t="n">
-        <v>4382</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C404" s="11" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="18" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C405" s="11" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="18" t="n">
-        <v>1214</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
@@ -5161,23 +4768,23 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
       <c r="B409" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="C409" s="11" t="n">
-        <v>517</v>
+      <c r="C409" s="18" t="n">
+        <v>1360</v>
       </c>
     </row>
     <row r="410" ht="11" customHeight="true" outlineLevel="3">
@@ -5185,7 +4792,7 @@
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="411" ht="11" customHeight="true" outlineLevel="3">
@@ -5193,7 +4800,7 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>226</v>
+        <v>645</v>
       </c>
     </row>
     <row r="412" ht="11" customHeight="true" outlineLevel="3">
@@ -5201,7 +4808,7 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>341</v>
+        <v>735</v>
       </c>
     </row>
     <row r="413" ht="11" customHeight="true" outlineLevel="3">
@@ -5209,7 +4816,7 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" ht="11" customHeight="true" outlineLevel="3">
@@ -5217,7 +4824,7 @@
         <v>413</v>
       </c>
       <c r="C414" s="18" t="n">
-        <v>1825</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="415" ht="11" customHeight="true" outlineLevel="3">
@@ -5225,7 +4832,7 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>547</v>
+        <v>385</v>
       </c>
     </row>
     <row r="416" ht="11" customHeight="true" outlineLevel="3">
@@ -5233,15 +4840,15 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>745</v>
+        <v>324</v>
       </c>
     </row>
     <row r="417" ht="11" customHeight="true" outlineLevel="3">
       <c r="B417" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="C417" s="11" t="n">
-        <v>741</v>
+      <c r="C417" s="18" t="n">
+        <v>2317</v>
       </c>
     </row>
     <row r="418" ht="11" customHeight="true" outlineLevel="3">
@@ -5249,1079 +4856,31 @@
         <v>417</v>
       </c>
       <c r="C418" s="18" t="n">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="419" ht="11" customHeight="true" outlineLevel="3">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="419" ht="22" customHeight="true" outlineLevel="3">
       <c r="B419" s="17" t="s">
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>438</v>
+        <v>11</v>
       </c>
     </row>
     <row r="420" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B420" s="17" t="s">
+      <c r="B420" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="C420" s="18" t="n">
-        <v>2717</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B421" s="17" t="s">
+      <c r="C420" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B421" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="18" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B422" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="C422" s="18" t="n">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="423" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B423" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="C423" s="11" t="n">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B424" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="C424" s="18" t="n">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B425" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="C425" s="11" t="n">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="426" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B426" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="C426" s="11" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B427" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="C427" s="11" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B428" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="C428" s="11" t="n">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B429" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="C429" s="11" t="n">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="430" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B430" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="C430" s="11" t="n">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="431" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B431" s="17" t="s">
-        <v>430</v>
-      </c>
-      <c r="C431" s="11" t="n">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="432" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B432" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="C432" s="18" t="n">
-        <v>16048</v>
-      </c>
-    </row>
-    <row r="433" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B433" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="C433" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B434" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="C434" s="18" t="n">
-        <v>3752</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B435" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="C435" s="18" t="n">
-        <v>9301</v>
-      </c>
-    </row>
-    <row r="436" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B436" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="C436" s="18" t="n">
-        <v>1564</v>
-      </c>
-    </row>
-    <row r="437" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B437" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="C437" s="11" t="n">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="438" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B438" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="C438" s="11" t="n">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="439" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B439" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="C439" s="18" t="n">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="440" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B440" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="C440" s="11" t="n">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="441" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B441" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="14" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B442" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="C442" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="443" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B443" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="C443" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="444" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B444" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="C444" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B445" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="C445" s="12" t="n">
-        <v>77376</v>
-      </c>
-    </row>
-    <row r="446" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B446" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="C446" s="11" t="n">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="447" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B447" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="448" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B448" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="449" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B449" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="450" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B450" s="17" t="s">
-        <v>449</v>
-      </c>
-      <c r="C450" s="11" t="n">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="451" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B451" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="C451" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="452" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B452" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="C452" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B453" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="454" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B454" s="17" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="18" t="n">
-        <v>5647</v>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B455" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B456" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B458" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="18" t="n">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B462" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B463" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="11" t="n">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B464" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="18" t="n">
-        <v>3289</v>
-      </c>
-    </row>
-    <row r="465" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B465" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="466" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B466" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="C466" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="467" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B467" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="C467" s="18" t="n">
-        <v>6662</v>
-      </c>
-    </row>
-    <row r="468" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B468" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="C468" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="469" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B469" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="C469" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B470" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="C470" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B471" s="17" t="s">
-        <v>470</v>
-      </c>
-      <c r="C471" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="472" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B472" s="17" t="s">
-        <v>471</v>
-      </c>
-      <c r="C472" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="473" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B473" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="C473" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="474" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B474" s="17" t="s">
-        <v>473</v>
-      </c>
-      <c r="C474" s="11" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="475" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B475" s="17" t="s">
-        <v>474</v>
-      </c>
-      <c r="C475" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B476" s="17" t="s">
-        <v>475</v>
-      </c>
-      <c r="C476" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B477" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="C477" s="11" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B478" s="17" t="s">
-        <v>477</v>
-      </c>
-      <c r="C478" s="18" t="n">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="479" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B479" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C479" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B480" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="C480" s="11" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="481" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B481" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="C481" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="482" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B482" s="17" t="s">
-        <v>481</v>
-      </c>
-      <c r="C482" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="483" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B483" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="C483" s="18" t="n">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="484" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B484" s="17" t="s">
-        <v>483</v>
-      </c>
-      <c r="C484" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="485" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B485" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="C485" s="11" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="486" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B486" s="17" t="s">
-        <v>485</v>
-      </c>
-      <c r="C486" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="487" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B487" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="C487" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="488" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B488" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C488" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="489" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B489" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="C489" s="11" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="490" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B490" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="C490" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="491" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B491" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C491" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="492" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B492" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C492" s="18" t="n">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="493" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B493" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="C493" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="494" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B494" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="C494" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="495" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B495" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="C495" s="11" t="n">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="496" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B496" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C496" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="497" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B497" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="C497" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="498" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B498" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="C498" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="499" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B499" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="C499" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="500" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B500" s="17" t="s">
-        <v>499</v>
-      </c>
-      <c r="C500" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="501" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B501" s="17" t="s">
-        <v>500</v>
-      </c>
-      <c r="C501" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="502" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B502" s="17" t="s">
-        <v>501</v>
-      </c>
-      <c r="C502" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="503" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B503" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="C503" s="11" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="504" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B504" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="C504" s="11" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="505" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B505" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="C505" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B506" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="C506" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="507" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B507" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="C507" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="508" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B508" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="C508" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="509" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B509" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="C509" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="510" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B510" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="C510" s="11" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="511" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B511" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="C511" s="11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="512" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B512" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="C512" s="11" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="513" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B513" s="17" t="s">
-        <v>512</v>
-      </c>
-      <c r="C513" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="514" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B514" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="C514" s="18" t="n">
-        <v>2907</v>
-      </c>
-    </row>
-    <row r="515" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B515" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="C515" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="516" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B516" s="17" t="s">
-        <v>515</v>
-      </c>
-      <c r="C516" s="11" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="517" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B517" s="17" t="s">
-        <v>516</v>
-      </c>
-      <c r="C517" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="518" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B518" s="17" t="s">
-        <v>517</v>
-      </c>
-      <c r="C518" s="11" t="n">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="519" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B519" s="17" t="s">
-        <v>518</v>
-      </c>
-      <c r="C519" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="520" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B520" s="17" t="s">
-        <v>519</v>
-      </c>
-      <c r="C520" s="11" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="521" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B521" s="17" t="s">
-        <v>520</v>
-      </c>
-      <c r="C521" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="522" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B522" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="C522" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="523" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B523" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C523" s="18" t="n">
-        <v>9759</v>
-      </c>
-    </row>
-    <row r="524" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B524" s="17" t="s">
-        <v>523</v>
-      </c>
-      <c r="C524" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="525" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B525" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C525" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="526" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B526" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="C526" s="18" t="n">
-        <v>3215</v>
-      </c>
-    </row>
-    <row r="527" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B527" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C527" s="11" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="528" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B528" s="17" t="s">
-        <v>527</v>
-      </c>
-      <c r="C528" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="529" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B529" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="C529" s="18" t="n">
-        <v>2646</v>
-      </c>
-    </row>
-    <row r="530" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B530" s="17" t="s">
-        <v>529</v>
-      </c>
-      <c r="C530" s="11" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="531" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B531" s="17" t="s">
-        <v>530</v>
-      </c>
-      <c r="C531" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="532" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B532" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="C532" s="18" t="n">
-        <v>3539</v>
-      </c>
-    </row>
-    <row r="533" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B533" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="C533" s="18" t="n">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="534" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B534" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="C534" s="11" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="535" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B535" s="17" t="s">
-        <v>534</v>
-      </c>
-      <c r="C535" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="536" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B536" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="C536" s="18" t="n">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="537" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B537" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="C537" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="538" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B538" s="17" t="s">
-        <v>537</v>
-      </c>
-      <c r="C538" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="539" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B539" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="C539" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="540" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B540" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C540" s="11" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="541" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B541" s="17" t="s">
-        <v>540</v>
-      </c>
-      <c r="C541" s="18" t="n">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="542" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B542" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="C542" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="543" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B543" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="C543" s="18" t="n">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="544" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B544" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="C544" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="545" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B545" s="17" t="s">
-        <v>544</v>
-      </c>
-      <c r="C545" s="18" t="n">
-        <v>2772</v>
-      </c>
-    </row>
-    <row r="546" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B546" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="C546" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="547" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B547" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="C547" s="12" t="n">
-        <v>7322</v>
-      </c>
-    </row>
-    <row r="548" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B548" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="C548" s="18" t="n">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="549" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B549" s="20" t="s">
-        <v>548</v>
-      </c>
-      <c r="C549" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="550" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B550" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C550" s="18" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="551" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B551" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="C551" s="18" t="n">
-        <v>4104</v>
-      </c>
-    </row>
-    <row r="552" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B552" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="C552" s="11" t="n">
-        <v>40</v>
+      <c r="C421" s="11" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="436">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.01.2026 15:05:13</t>
+    <t>Период: на 30.01.2026 8:15:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -71,21 +71,27 @@
     <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -95,16 +101,25 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
@@ -137,9 +152,18 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -149,12 +173,21 @@
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -281,9 +314,6 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -296,9 +326,6 @@
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>РОШЕН</t>
   </si>
   <si>
@@ -308,9 +335,15 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -320,27 +353,30 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -395,6 +431,9 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -509,9 +548,6 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -530,9 +566,6 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -542,6 +575,9 @@
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -551,6 +587,9 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
@@ -560,6 +599,12 @@
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -575,9 +620,6 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -593,12 +635,12 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -608,9 +650,6 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -761,9 +800,15 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Cherry Queen heart РЦ 122г /8шт</t>
+  </si>
+  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -776,10 +821,13 @@
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
@@ -788,9 +836,15 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -806,6 +860,9 @@
     <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
     <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
@@ -947,9 +1004,6 @@
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
@@ -962,9 +1016,6 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -986,9 +1037,6 @@
     <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 1кг /9пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -998,9 +1046,6 @@
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
-    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1022,6 +1067,9 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
@@ -1037,9 +1085,6 @@
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1055,6 +1100,9 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -1064,18 +1112,15 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1124,18 +1169,15 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1145,12 +1187,15 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
@@ -1166,7 +1211,7 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
@@ -1196,21 +1241,21 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1220,7 +1265,7 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
@@ -1256,13 +1301,13 @@
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
@@ -1535,7 +1580,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C421"/>
+  <dimension ref="C436"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1600,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>594</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1608,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>675310</v>
+        <v>575316</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1632,7 +1677,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>157301</v>
+        <v>157685</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
@@ -1640,7 +1685,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>26151</v>
+        <v>27876</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1648,23 +1693,23 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>7453</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>2694</v>
+      <c r="C18" s="11" t="n">
+        <v>607</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>340</v>
+      <c r="C19" s="18" t="n">
+        <v>4706</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1672,7 +1717,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>539</v>
+        <v>640</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1680,7 +1725,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>496</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1688,39 +1733,39 @@
         <v>21</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>2348</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>929</v>
+      <c r="C23" s="18" t="n">
+        <v>5474</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>3425</v>
+      <c r="C24" s="11" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>1456</v>
+      <c r="C25" s="11" t="n">
+        <v>313</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>920</v>
+      <c r="C26" s="18" t="n">
+        <v>5647</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1728,7 +1773,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>375</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1736,7 +1781,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>280</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1744,7 +1789,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>394</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1752,23 +1797,23 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>232</v>
+        <v>783</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="18" t="n">
-        <v>4270</v>
-      </c>
-    </row>
-    <row r="32" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B32" s="16" t="s">
+      <c r="C31" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B32" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="12" t="n">
-        <v>61965</v>
+      <c r="C32" s="11" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1776,39 +1821,39 @@
         <v>32</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>4252</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="18" t="n">
-        <v>39962</v>
+      <c r="C34" s="11" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="18" t="n">
-        <v>4794</v>
+      <c r="C35" s="11" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="18" t="n">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B37" s="17" t="s">
+      <c r="C36" s="11" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B37" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>608</v>
+      <c r="C37" s="12" t="n">
+        <v>73485</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1816,23 +1861,23 @@
         <v>37</v>
       </c>
       <c r="C38" s="18" t="n">
-        <v>6504</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>938</v>
+      <c r="C39" s="18" t="n">
+        <v>54325</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>901</v>
+      <c r="C40" s="18" t="n">
+        <v>4794</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1840,7 +1885,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>120</v>
+        <v>482</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1848,23 +1893,23 @@
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>811</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C43" s="18" t="n">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="17" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>80</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1872,31 +1917,31 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="17" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B47" s="16" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="47" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B47" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>20914</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C47" s="18" t="n">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="18" t="n">
-        <v>1233</v>
+      <c r="C48" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1904,7 +1949,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>532</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1912,7 +1957,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>658</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1920,31 +1965,31 @@
         <v>50</v>
       </c>
       <c r="C51" s="18" t="n">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="52" ht="11" customHeight="true" outlineLevel="3">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="53" ht="11" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="true" outlineLevel="3">
       <c r="B53" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>723</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="18" t="n">
-        <v>1439</v>
+      <c r="C54" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1952,31 +1997,31 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="56" ht="11" customHeight="true" outlineLevel="3">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="true" outlineLevel="3">
       <c r="B56" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="true" outlineLevel="3">
       <c r="B57" s="17" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B58" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B58" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="18" t="n">
-        <v>1333</v>
+      <c r="C58" s="12" t="n">
+        <v>13919</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1984,7 +2029,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>785</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1992,7 +2037,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>795</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2000,15 +2045,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>361</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="18" t="n">
-        <v>1015</v>
+      <c r="C62" s="11" t="n">
+        <v>329</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2016,15 +2061,15 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>800</v>
+        <v>893</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="18" t="n">
-        <v>1221</v>
+      <c r="C64" s="11" t="n">
+        <v>655</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2032,7 +2077,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>337</v>
+        <v>493</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2040,7 +2085,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>149</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2048,15 +2093,15 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="true" outlineLevel="3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="18" t="n">
-        <v>1000</v>
+      <c r="C68" s="11" t="n">
+        <v>643</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2064,15 +2109,15 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>319</v>
+        <v>678</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="18" t="n">
-        <v>1172</v>
+      <c r="C70" s="11" t="n">
+        <v>755</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2080,7 +2125,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>737</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2088,7 +2133,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2096,7 +2141,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>233</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2104,15 +2149,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B75" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B75" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="12" t="n">
-        <v>48271</v>
+      <c r="C75" s="11" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2120,31 +2165,31 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>410</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="18" t="n">
-        <v>1518</v>
+      <c r="C77" s="11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="18" t="n">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C78" s="11" t="n">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="true" outlineLevel="3">
       <c r="B79" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="18" t="n">
-        <v>1972</v>
+      <c r="C79" s="11" t="n">
+        <v>582</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2152,55 +2197,55 @@
         <v>79</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>8091</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="18" t="n">
-        <v>1441</v>
+      <c r="C81" s="11" t="n">
+        <v>564</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="18" t="n">
-        <v>1744</v>
+      <c r="C82" s="11" t="n">
+        <v>681</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="18" t="n">
-        <v>2889</v>
+      <c r="C83" s="11" t="n">
+        <v>437</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>617</v>
+      <c r="C84" s="18" t="n">
+        <v>1403</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="18" t="n">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B86" s="17" t="s">
+      <c r="C85" s="11" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B86" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="18" t="n">
-        <v>1783</v>
+      <c r="C86" s="12" t="n">
+        <v>42405</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2208,79 +2253,79 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>12613</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>10</v>
+      <c r="C88" s="18" t="n">
+        <v>1323</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="18" t="n">
-        <v>4503</v>
+      <c r="C89" s="11" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>959</v>
+      <c r="C90" s="18" t="n">
+        <v>2011</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>607</v>
+      <c r="C91" s="18" t="n">
+        <v>8928</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>838</v>
+      <c r="C92" s="18" t="n">
+        <v>1211</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
       <c r="B93" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B94" s="13" t="s">
+      <c r="C93" s="18" t="n">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B94" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="12" t="n">
-        <v>517958</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B95" s="16" t="s">
+      <c r="C94" s="18" t="n">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B95" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="12" t="n">
-        <v>148563</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C95" s="18" t="n">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="18" t="n">
-        <v>12593</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2288,7 +2333,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>20589</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
@@ -2296,55 +2341,55 @@
         <v>97</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>5730</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+        <v>10418</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C99" s="18" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="18" t="n">
-        <v>14427</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C100" s="11" t="n">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="18" t="n">
-        <v>3530</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C101" s="11" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="3">
       <c r="B102" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="18" t="n">
-        <v>15042</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B103" s="17" t="s">
+      <c r="C102" s="11" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B103" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="18" t="n">
-        <v>7421</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B104" s="17" t="s">
+      <c r="C103" s="12" t="n">
+        <v>417580</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B104" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="18" t="n">
-        <v>12043</v>
+      <c r="C104" s="12" t="n">
+        <v>78296</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="true" outlineLevel="3">
@@ -2352,7 +2397,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="18" t="n">
-        <v>22937</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="true" outlineLevel="3">
@@ -2360,127 +2405,127 @@
         <v>105</v>
       </c>
       <c r="C106" s="18" t="n">
-        <v>3410</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="17" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>30550</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B108" s="16" t="s">
+        <v>11318</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B108" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="12" t="n">
-        <v>5081</v>
+      <c r="C108" s="18" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C109" s="18" t="n">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="17" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
       <c r="B111" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C111" s="18" t="n">
+        <v>5577</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="17" t="s">
         <v>111</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="true" outlineLevel="3">
       <c r="B113" s="17" t="s">
         <v>112</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="114" ht="11" customHeight="true" outlineLevel="3">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="true" outlineLevel="3">
       <c r="B114" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="115" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C114" s="18" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="true" outlineLevel="3">
       <c r="B115" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C115" s="18" t="n">
+        <v>6977</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="true" outlineLevel="3">
       <c r="B116" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C116" s="11" t="n">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C116" s="18" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="true" outlineLevel="3">
       <c r="B117" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B118" s="16" t="s">
+      <c r="C117" s="18" t="n">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B118" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="12" t="n">
-        <v>81395</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C118" s="18" t="n">
+        <v>20980</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="true" outlineLevel="3">
       <c r="B119" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B120" s="17" t="s">
+      <c r="C119" s="18" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="120" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B120" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>199</v>
+      <c r="C120" s="12" t="n">
+        <v>6653</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
       <c r="B121" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="11" t="n">
-        <v>553</v>
+      <c r="C121" s="18" t="n">
+        <v>1133</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2488,15 +2533,15 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>735</v>
+        <v>490</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="18" t="n">
-        <v>1718</v>
+      <c r="C123" s="11" t="n">
+        <v>687</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2504,15 +2549,15 @@
         <v>123</v>
       </c>
       <c r="C124" s="18" t="n">
-        <v>23734</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="18" t="n">
-        <v>27230</v>
+      <c r="C125" s="11" t="n">
+        <v>459</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2520,7 +2565,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>11753</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2528,7 +2573,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>439</v>
+        <v>272</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2536,7 +2581,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>105</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2544,15 +2589,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B130" s="17" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B130" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>659</v>
+      <c r="C130" s="12" t="n">
+        <v>107219</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2560,7 +2605,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>231</v>
+        <v>301</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2568,15 +2613,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="18" t="n">
-        <v>1284</v>
+      <c r="C133" s="11" t="n">
+        <v>578</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2584,15 +2629,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>985</v>
+        <v>545</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>2</v>
+      <c r="C135" s="18" t="n">
+        <v>3579</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2600,31 +2645,31 @@
         <v>135</v>
       </c>
       <c r="C136" s="18" t="n">
-        <v>1888</v>
+        <v>22358</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>10</v>
+      <c r="C137" s="18" t="n">
+        <v>45757</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
       <c r="B138" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="11" t="n">
-        <v>981</v>
+      <c r="C138" s="18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>254</v>
+      <c r="C139" s="18" t="n">
+        <v>21079</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2632,7 +2677,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>374</v>
+        <v>178</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2640,55 +2685,55 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>762</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="18" t="n">
-        <v>1876</v>
+      <c r="C142" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="18" t="n">
-        <v>1081</v>
+      <c r="C143" s="11" t="n">
+        <v>863</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
       <c r="B144" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="18" t="n">
-        <v>2085</v>
+      <c r="C144" s="11" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="18" t="n">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="146" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B146" s="16" t="s">
+      <c r="C145" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="146" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B146" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="12" t="n">
-        <v>98835</v>
+      <c r="C146" s="11" t="n">
+        <v>533</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="18" t="n">
-        <v>1269</v>
+      <c r="C147" s="11" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2696,7 +2741,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>402</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2704,7 +2749,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>317</v>
+        <v>742</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2712,7 +2757,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>344</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2720,15 +2765,15 @@
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>1793</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="18" t="n">
-        <v>1180</v>
+      <c r="C152" s="11" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2736,63 +2781,63 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>250</v>
+        <v>449</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>43</v>
+      <c r="C154" s="18" t="n">
+        <v>1019</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
       <c r="B155" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>224</v>
+      <c r="C155" s="18" t="n">
+        <v>1416</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="11" t="n">
-        <v>19</v>
+      <c r="C156" s="18" t="n">
+        <v>1392</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="18" t="n">
-        <v>3332</v>
+      <c r="C157" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="159" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B159" s="17" t="s">
+      <c r="C158" s="18" t="n">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="159" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B159" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="18" t="n">
-        <v>2722</v>
+      <c r="C159" s="12" t="n">
+        <v>73708</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="11" t="n">
-        <v>149</v>
+      <c r="C160" s="18" t="n">
+        <v>1328</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2800,15 +2845,15 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>636</v>
+        <v>245</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="18" t="n">
-        <v>5018</v>
+      <c r="C162" s="11" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2816,7 +2861,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>403</v>
+        <v>155</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2824,7 +2869,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="18" t="n">
-        <v>1463</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2832,23 +2877,23 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>244</v>
+        <v>991</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="18" t="n">
-        <v>7023</v>
+      <c r="C166" s="11" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="18" t="n">
-        <v>1303</v>
+      <c r="C167" s="11" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2856,7 +2901,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>18</v>
+        <v>488</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2864,39 +2909,39 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>978</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
       <c r="B170" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="11" t="n">
-        <v>437</v>
+      <c r="C170" s="18" t="n">
+        <v>3892</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="18" t="n">
-        <v>2114</v>
+      <c r="C171" s="11" t="n">
+        <v>505</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="18" t="n">
-        <v>2653</v>
+      <c r="C172" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="18" t="n">
-        <v>1094</v>
+      <c r="C173" s="11" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2904,15 +2949,15 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>173</v>
+        <v>289</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="11" t="n">
-        <v>135</v>
+      <c r="C175" s="18" t="n">
+        <v>1640</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2920,7 +2965,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>215</v>
+        <v>259</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2928,31 +2973,31 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>308</v>
+        <v>685</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>11</v>
+      <c r="C178" s="18" t="n">
+        <v>3354</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="18" t="n">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="180" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C179" s="11" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="18" t="n">
-        <v>1184</v>
+      <c r="C180" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2960,31 +3005,31 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>454</v>
+        <v>906</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>119</v>
+      <c r="C182" s="18" t="n">
+        <v>1026</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>333</v>
+      <c r="C183" s="18" t="n">
+        <v>2470</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="18" t="n">
-        <v>6812</v>
+      <c r="C184" s="11" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2992,23 +3037,23 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>176</v>
+        <v>254</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
       <c r="B186" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="18" t="n">
-        <v>1040</v>
+      <c r="C186" s="11" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>170</v>
+      <c r="C187" s="18" t="n">
+        <v>1483</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3016,31 +3061,31 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>372</v>
+        <v>204</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="18" t="n">
-        <v>3684</v>
-      </c>
-    </row>
-    <row r="190" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C189" s="11" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="true" outlineLevel="3">
       <c r="B190" s="17" t="s">
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>888</v>
+        <v>257</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="18" t="n">
-        <v>1635</v>
+      <c r="C191" s="11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3048,55 +3093,55 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="17" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>424</v>
+        <v>322</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="18" t="n">
-        <v>2417</v>
-      </c>
-    </row>
-    <row r="195" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C194" s="11" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="18" t="n">
-        <v>1913</v>
+      <c r="C195" s="11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="18" t="n">
-        <v>1058</v>
+      <c r="C196" s="11" t="n">
+        <v>413</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="18" t="n">
-        <v>1414</v>
+      <c r="C197" s="11" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="18" t="n">
-        <v>1776</v>
+      <c r="C198" s="11" t="n">
+        <v>157</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3104,7 +3149,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="18" t="n">
-        <v>19209</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3112,23 +3157,23 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>302</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="18" t="n">
-        <v>2923</v>
+      <c r="C201" s="11" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="18" t="n">
-        <v>1868</v>
+      <c r="C202" s="11" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3136,7 +3181,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="18" t="n">
-        <v>1646</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3144,55 +3189,55 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>522</v>
+        <v>274</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>252</v>
+      <c r="C205" s="18" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="18" t="n">
-        <v>2771</v>
+      <c r="C206" s="11" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="18" t="n">
-        <v>4457</v>
+      <c r="C207" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="11" t="n">
-        <v>819</v>
+      <c r="C208" s="18" t="n">
+        <v>1963</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="210" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B210" s="16" t="s">
+      <c r="C209" s="18" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="210" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B210" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="12" t="n">
-        <v>64595</v>
+      <c r="C210" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3200,23 +3245,23 @@
         <v>210</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>1127</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="11" t="n">
-        <v>945</v>
+      <c r="C212" s="18" t="n">
+        <v>18770</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="18" t="n">
-        <v>2260</v>
+      <c r="C213" s="11" t="n">
+        <v>562</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3224,31 +3269,31 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>7</v>
+        <v>396</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>741</v>
+      <c r="C215" s="18" t="n">
+        <v>1276</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>484</v>
+      <c r="C216" s="18" t="n">
+        <v>1318</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="18" t="n">
-        <v>5794</v>
+      <c r="C217" s="11" t="n">
+        <v>639</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3256,23 +3301,23 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>187</v>
+      <c r="C219" s="18" t="n">
+        <v>1756</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>159</v>
+      <c r="C220" s="18" t="n">
+        <v>2951</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3280,7 +3325,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="18" t="n">
-        <v>1458</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3288,31 +3333,31 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="223" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B223" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="223" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B223" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="18" t="n">
-        <v>2272</v>
+      <c r="C223" s="12" t="n">
+        <v>42245</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
       <c r="B224" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="18" t="n">
-        <v>2730</v>
+      <c r="C224" s="11" t="n">
+        <v>870</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="18" t="n">
-        <v>1983</v>
+      <c r="C225" s="11" t="n">
+        <v>694</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3320,15 +3365,15 @@
         <v>225</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>1154</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="18" t="n">
-        <v>1178</v>
+      <c r="C227" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3336,15 +3381,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>725</v>
+        <v>598</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="18" t="n">
-        <v>1801</v>
+      <c r="C229" s="11" t="n">
+        <v>652</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3352,7 +3397,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>1371</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3360,23 +3405,23 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>377</v>
+        <v>50</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="18" t="n">
-        <v>1855</v>
+      <c r="C232" s="11" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="18" t="n">
-        <v>2873</v>
+      <c r="C233" s="11" t="n">
+        <v>173</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3384,15 +3429,15 @@
         <v>233</v>
       </c>
       <c r="C234" s="18" t="n">
-        <v>2673</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="18" t="n">
-        <v>2807</v>
+      <c r="C235" s="11" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3400,7 +3445,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="18" t="n">
-        <v>2567</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3408,39 +3453,39 @@
         <v>236</v>
       </c>
       <c r="C237" s="18" t="n">
-        <v>2778</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>824</v>
+      <c r="C238" s="18" t="n">
+        <v>1024</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="18" t="n">
-        <v>1004</v>
+      <c r="C239" s="11" t="n">
+        <v>791</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="18" t="n">
-        <v>4038</v>
+      <c r="C240" s="11" t="n">
+        <v>483</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="18" t="n">
-        <v>1833</v>
+      <c r="C241" s="11" t="n">
+        <v>515</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3448,79 +3493,79 @@
         <v>241</v>
       </c>
       <c r="C242" s="18" t="n">
-        <v>1714</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="18" t="n">
-        <v>2695</v>
+      <c r="C243" s="11" t="n">
+        <v>903</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="18" t="n">
-        <v>7807</v>
+      <c r="C244" s="11" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="18" t="n">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="246" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B246" s="16" t="s">
+      <c r="C245" s="11" t="n">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="246" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B246" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="12" t="n">
-        <v>6194</v>
+      <c r="C246" s="18" t="n">
+        <v>1891</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="11" t="n">
-        <v>868</v>
+      <c r="C247" s="18" t="n">
+        <v>2328</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>711</v>
+      <c r="C248" s="18" t="n">
+        <v>2005</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>93</v>
+      <c r="C249" s="18" t="n">
+        <v>1539</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>508</v>
+      <c r="C250" s="18" t="n">
+        <v>2028</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>70</v>
+      <c r="C251" s="18" t="n">
+        <v>1521</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3528,47 +3573,47 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>615</v>
+        <v>115</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>663</v>
+      <c r="C253" s="18" t="n">
+        <v>2015</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="11" t="n">
-        <v>384</v>
+      <c r="C254" s="18" t="n">
+        <v>1351</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>304</v>
+      <c r="C255" s="18" t="n">
+        <v>2080</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="11" t="n">
-        <v>693</v>
+      <c r="C256" s="18" t="n">
+        <v>1532</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="n">
-        <v>953</v>
+      <c r="C257" s="18" t="n">
+        <v>4315</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3576,15 +3621,15 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B259" s="17" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B259" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="11" t="n">
-        <v>7</v>
+      <c r="C259" s="12" t="n">
+        <v>5702</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3592,15 +3637,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="261" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B261" s="16" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B261" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="12" t="n">
-        <v>28446</v>
+      <c r="C261" s="11" t="n">
+        <v>251</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3608,7 +3653,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>352</v>
+        <v>625</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3616,7 +3661,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>353</v>
+        <v>25</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3624,7 +3669,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>459</v>
+        <v>777</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3632,7 +3677,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>461</v>
+        <v>201</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3640,7 +3685,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>315</v>
+        <v>64</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3648,7 +3693,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>394</v>
+        <v>336</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3656,15 +3701,15 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="269" ht="22" customHeight="true" outlineLevel="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="17" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>39</v>
+        <v>292</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3672,7 +3717,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3680,15 +3725,15 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>435</v>
+        <v>283</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="18" t="n">
-        <v>1209</v>
+      <c r="C272" s="11" t="n">
+        <v>765</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3696,79 +3741,79 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>420</v>
+        <v>85</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="18" t="n">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="275" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C274" s="11" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="17" t="s">
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="276" ht="22" customHeight="true" outlineLevel="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="17" t="s">
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="277" ht="22" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="17" t="s">
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="278" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="17" t="s">
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="279" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B279" s="17" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B279" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="280" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C279" s="12" t="n">
+        <v>32502</v>
+      </c>
+    </row>
+    <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="17" t="s">
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="17" t="s">
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="282" ht="22" customHeight="true" outlineLevel="3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="17" t="s">
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>133</v>
+        <v>90</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3776,7 +3821,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>817</v>
+        <v>716</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3784,7 +3829,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>599</v>
+        <v>539</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3792,7 +3837,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>500</v>
+        <v>893</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3800,31 +3845,31 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>227</v>
+        <v>811</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="18" t="n">
-        <v>2445</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C287" s="11" t="n">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="18" t="n">
-        <v>3739</v>
+      <c r="C288" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="18" t="n">
-        <v>1180</v>
+      <c r="C289" s="11" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3832,7 +3877,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>967</v>
+        <v>235</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3840,15 +3885,15 @@
         <v>290</v>
       </c>
       <c r="C291" s="18" t="n">
-        <v>2559</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="11" t="n">
-        <v>7</v>
+      <c r="C292" s="18" t="n">
+        <v>1164</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3856,95 +3901,95 @@
         <v>292</v>
       </c>
       <c r="C293" s="18" t="n">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="294" ht="11" customHeight="true" outlineLevel="3">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="true" outlineLevel="3">
       <c r="B294" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="18" t="n">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C294" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="true" outlineLevel="3">
       <c r="B295" s="17" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="296" ht="11" customHeight="true" outlineLevel="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="17" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="297" ht="11" customHeight="true" outlineLevel="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="true" outlineLevel="3">
       <c r="B297" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="18" t="n">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B298" s="16" t="s">
+      <c r="C297" s="11" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B298" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="12" t="n">
-        <v>52151</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C298" s="11" t="n">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="true" outlineLevel="3">
       <c r="B299" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="18" t="n">
-        <v>3776</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C299" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="true" outlineLevel="3">
       <c r="B300" s="17" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="true" outlineLevel="3">
       <c r="B301" s="17" t="s">
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="18" t="n">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C302" s="11" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="18" t="n">
-        <v>2312</v>
+      <c r="C303" s="11" t="n">
+        <v>601</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="18" t="n">
-        <v>1967</v>
+      <c r="C304" s="11" t="n">
+        <v>351</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3952,15 +3997,15 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>871</v>
+        <v>308</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>168</v>
+      <c r="C306" s="18" t="n">
+        <v>3323</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3968,15 +4013,15 @@
         <v>306</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>1056</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="18" t="n">
-        <v>1786</v>
+      <c r="C308" s="11" t="n">
+        <v>971</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3984,15 +4029,15 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>504</v>
+        <v>634</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="11" t="n">
-        <v>60</v>
+      <c r="C310" s="18" t="n">
+        <v>3209</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4000,15 +4045,15 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>217</v>
+        <v>7</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="11" t="n">
-        <v>300</v>
+      <c r="C312" s="18" t="n">
+        <v>4114</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -4016,15 +4061,15 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>421</v>
+        <v>169</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>525</v>
+      <c r="C314" s="18" t="n">
+        <v>1475</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4032,63 +4077,63 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>350</v>
+        <v>194</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="11" t="n">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B317" s="17" t="s">
+      <c r="C316" s="18" t="n">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B317" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="11" t="n">
-        <v>633</v>
+      <c r="C317" s="12" t="n">
+        <v>39803</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>398</v>
+      <c r="C318" s="18" t="n">
+        <v>3118</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="18" t="n">
-        <v>1291</v>
+      <c r="C319" s="11" t="n">
+        <v>513</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="18" t="n">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C320" s="11" t="n">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="18" t="n">
-        <v>2284</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
       <c r="B322" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>737</v>
+      <c r="C322" s="18" t="n">
+        <v>1918</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4096,7 +4141,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>110</v>
+        <v>943</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4104,7 +4149,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>893</v>
+        <v>849</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4112,7 +4157,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>675</v>
+        <v>918</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4120,15 +4165,15 @@
         <v>325</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>2264</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="11" t="n">
-        <v>164</v>
+      <c r="C327" s="18" t="n">
+        <v>1096</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4136,7 +4181,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>889</v>
+        <v>398</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4144,7 +4189,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>512</v>
+        <v>68</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4152,7 +4197,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>989</v>
+        <v>96</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4160,39 +4205,39 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>938</v>
+        <v>491</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="C332" s="18" t="n">
-        <v>1067</v>
+      <c r="C332" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="18" t="n">
-        <v>1133</v>
+      <c r="C333" s="11" t="n">
+        <v>343</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="18" t="n">
-        <v>9503</v>
+      <c r="C334" s="11" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="18" t="n">
-        <v>5145</v>
+      <c r="C335" s="11" t="n">
+        <v>398</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4200,7 +4245,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>1135</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4208,23 +4253,23 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>430</v>
+        <v>812</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="C338" s="11" t="n">
-        <v>29</v>
+      <c r="C338" s="18" t="n">
+        <v>1215</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="18" t="n">
-        <v>1360</v>
+      <c r="C339" s="11" t="n">
+        <v>498</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4232,23 +4277,23 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B341" s="16" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B341" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="14" t="n">
-        <v>89</v>
+      <c r="C341" s="11" t="n">
+        <v>403</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="11" t="n">
-        <v>6</v>
+      <c r="C342" s="18" t="n">
+        <v>1606</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4256,7 +4301,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>67</v>
+        <v>156</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4264,15 +4309,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B345" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B345" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="12" t="n">
-        <v>32609</v>
+      <c r="C345" s="11" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4280,7 +4325,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>90</v>
+        <v>299</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4288,79 +4333,79 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="17" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" ht="33" customHeight="true" outlineLevel="3">
+      <c r="C349" s="18" t="n">
+        <v>8027</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="17" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="351" ht="22" customHeight="true" outlineLevel="3">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="11" t="n">
-        <v>87</v>
+      <c r="C351" s="18" t="n">
+        <v>5551</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C352" s="18" t="n">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="17" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="354" ht="22" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="17" t="s">
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="355" ht="22" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="18" t="n">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B356" s="17" t="s">
+      <c r="C355" s="11" t="n">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B356" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>116</v>
+      <c r="C356" s="14" t="n">
+        <v>259</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4368,15 +4413,15 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="18" t="n">
-        <v>2863</v>
+      <c r="C358" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4384,39 +4429,39 @@
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B360" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B360" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C360" s="12" t="n">
+        <v>31193</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="17" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="17" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="17" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>515</v>
+        <v>212</v>
       </c>
     </row>
     <row r="364" ht="22" customHeight="true" outlineLevel="3">
@@ -4424,7 +4469,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>266</v>
+        <v>356</v>
       </c>
     </row>
     <row r="365" ht="22" customHeight="true" outlineLevel="3">
@@ -4432,23 +4477,23 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="17" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="18" t="n">
-        <v>1159</v>
+      <c r="C367" s="11" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="368" ht="22" customHeight="true" outlineLevel="3">
@@ -4456,7 +4501,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>616</v>
+        <v>701</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4464,47 +4509,47 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>122</v>
+        <v>451</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C370" s="18" t="n">
+        <v>6704</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="17" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="374" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C373" s="18" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>38</v>
+        <v>261</v>
       </c>
     </row>
     <row r="375" ht="22" customHeight="true" outlineLevel="3">
@@ -4512,7 +4557,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>41</v>
+        <v>460</v>
       </c>
     </row>
     <row r="376" ht="22" customHeight="true" outlineLevel="3">
@@ -4520,7 +4565,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="377" ht="22" customHeight="true" outlineLevel="3">
@@ -4528,15 +4573,15 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>252</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>978</v>
+      <c r="C378" s="18" t="n">
+        <v>1048</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="true" outlineLevel="3">
@@ -4544,7 +4589,7 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>320</v>
+        <v>363</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="true" outlineLevel="3">
@@ -4552,7 +4597,7 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="381" ht="22" customHeight="true" outlineLevel="3">
@@ -4560,15 +4605,15 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="11" t="n">
-        <v>180</v>
+      <c r="C382" s="18" t="n">
+        <v>2808</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
@@ -4576,15 +4621,15 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="384" ht="22" customHeight="true" outlineLevel="3">
       <c r="B384" s="17" t="s">
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>247</v>
+        <v>137</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
@@ -4592,7 +4637,7 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>182</v>
+        <v>106</v>
       </c>
     </row>
     <row r="386" ht="22" customHeight="true" outlineLevel="3">
@@ -4600,7 +4645,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>24</v>
+        <v>162</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="true" outlineLevel="3">
@@ -4608,7 +4653,7 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="true" outlineLevel="3">
@@ -4616,7 +4661,7 @@
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>177</v>
+        <v>358</v>
       </c>
     </row>
     <row r="389" ht="22" customHeight="true" outlineLevel="3">
@@ -4624,7 +4669,7 @@
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>108</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
@@ -4632,7 +4677,7 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4640,7 +4685,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4648,7 +4693,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>360</v>
+        <v>133</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4656,15 +4701,15 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
       <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>281</v>
+        <v>51</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="true" outlineLevel="3">
@@ -4672,23 +4717,23 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
       <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
       <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>265</v>
+        <v>157</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4696,7 +4741,7 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>204</v>
+        <v>330</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4704,31 +4749,31 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
       <c r="B401" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="18" t="n">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C401" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="17" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>660</v>
+        <v>6</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4736,15 +4781,15 @@
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="404" ht="22" customHeight="true" outlineLevel="3">
       <c r="B404" s="17" t="s">
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>642</v>
+        <v>76</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="true" outlineLevel="3">
@@ -4752,47 +4797,47 @@
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>480</v>
+        <v>42</v>
       </c>
     </row>
     <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="18" t="n">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C406" s="11" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
       <c r="B407" s="17" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
       <c r="B409" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="C409" s="18" t="n">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C409" s="11" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
       <c r="B410" s="17" t="s">
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411" ht="11" customHeight="true" outlineLevel="3">
@@ -4800,15 +4845,15 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
       <c r="B412" s="17" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>735</v>
+        <v>488</v>
       </c>
     </row>
     <row r="413" ht="11" customHeight="true" outlineLevel="3">
@@ -4816,15 +4861,15 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>23</v>
+        <v>381</v>
       </c>
     </row>
     <row r="414" ht="11" customHeight="true" outlineLevel="3">
       <c r="B414" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="18" t="n">
-        <v>1868</v>
+      <c r="C414" s="11" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="415" ht="11" customHeight="true" outlineLevel="3">
@@ -4832,7 +4877,7 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>385</v>
+        <v>35</v>
       </c>
     </row>
     <row r="416" ht="11" customHeight="true" outlineLevel="3">
@@ -4840,46 +4885,166 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>324</v>
+        <v>11</v>
       </c>
     </row>
     <row r="417" ht="11" customHeight="true" outlineLevel="3">
       <c r="B417" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="C417" s="18" t="n">
-        <v>2317</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C417" s="11" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
       <c r="B418" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="C418" s="18" t="n">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="419" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C418" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="3">
       <c r="B419" s="17" t="s">
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B420" s="19" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B420" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="C420" s="14" t="n">
+      <c r="C420" s="11" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="18" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B422" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B423" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B424" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B425" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B426" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B428" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="18" t="n">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B429" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B430" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B431" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B432" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B433" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B434" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B435" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="14" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B421" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C421" s="11" t="n">
+    <row r="436" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B436" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="11" t="n">
         <v>105</v>
       </c>
     </row>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 30.01.2026 8:15:13</t>
+    <t>Период: на 11.02.2026 19:55:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -86,6 +86,9 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
@@ -137,6 +140,12 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -176,9 +185,6 @@
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
@@ -188,9 +194,6 @@
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
@@ -200,9 +203,6 @@
     <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Приправа до курки УБ 25г /34шт</t>
-  </si>
-  <si>
     <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -236,9 +236,6 @@
     <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Прованські трави УБ 10г /28шт</t>
-  </si>
-  <si>
     <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -248,9 +245,6 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -314,6 +308,9 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -332,6 +329,9 @@
     <t>БАТОНИ</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
@@ -356,6 +356,12 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
@@ -368,9 +374,6 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
@@ -383,6 +386,9 @@
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -440,18 +446,33 @@
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -461,9 +482,6 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
@@ -494,6 +512,9 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -512,6 +533,9 @@
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 205г /12шт EU АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
@@ -533,7 +557,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -548,6 +572,9 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -569,9 +596,6 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
@@ -587,22 +611,31 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
@@ -620,6 +653,9 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -638,6 +674,12 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -647,6 +689,9 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -659,9 +704,6 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -671,6 +713,9 @@
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
+    <t>Джеллі РЦ 200г /13шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
@@ -710,6 +755,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -803,9 +851,15 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Cherry Queen heart РЦ 122г /8шт</t>
   </si>
   <si>
@@ -827,12 +881,18 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з бренді-лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -866,6 +926,9 @@
     <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /28шт</t>
+  </si>
+  <si>
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
@@ -914,9 +977,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -1019,6 +1079,9 @@
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1043,45 +1106,63 @@
     <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1094,6 +1175,9 @@
     <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
+  </si>
+  <si>
     <t>Монблан РЦ 240г /15шт /</t>
   </si>
   <si>
@@ -1118,9 +1202,6 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1148,21 +1229,12 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1178,18 +1250,12 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
@@ -1199,9 +1265,6 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -1250,30 +1313,18 @@
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
@@ -1304,9 +1355,6 @@
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1316,16 +1364,7 @@
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП 1</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1555,12 +1594,6 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1580,7 +1613,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C436"/>
+  <dimension ref="C449"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1645,7 +1678,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>551</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1653,7 +1686,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>575316</v>
+        <v>838939</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1677,7 +1710,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>157685</v>
+        <v>222284</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
@@ -1685,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>27876</v>
+        <v>38851</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1693,15 +1726,15 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>3983</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>607</v>
+      <c r="C18" s="18" t="n">
+        <v>1237</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1709,7 +1742,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>4706</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,7 +1750,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>640</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1733,23 +1766,23 @@
         <v>21</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>3545</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="18" t="n">
-        <v>5474</v>
+      <c r="C23" s="11" t="n">
+        <v>644</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>230</v>
+      <c r="C24" s="18" t="n">
+        <v>5390</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1757,23 +1790,23 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>313</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>5647</v>
+      <c r="C26" s="11" t="n">
+        <v>201</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>40</v>
+      <c r="C27" s="18" t="n">
+        <v>5277</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1781,7 +1814,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>227</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1789,7 +1822,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1797,15 +1830,15 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>783</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>28</v>
+      <c r="C31" s="18" t="n">
+        <v>3057</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1813,23 +1846,23 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>95</v>
+        <v>812</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="18" t="n">
-        <v>1059</v>
+      <c r="C33" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>76</v>
+      <c r="C34" s="18" t="n">
+        <v>2996</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1837,31 +1870,31 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>48</v>
+        <v>588</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B37" s="16" t="s">
+      <c r="C36" s="18" t="n">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="12" t="n">
-        <v>73485</v>
-      </c>
-    </row>
-    <row r="38" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B38" s="17" t="s">
+      <c r="C37" s="18" t="n">
+        <v>5057</v>
+      </c>
+    </row>
+    <row r="38" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B38" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>4395</v>
+      <c r="C38" s="12" t="n">
+        <v>80508</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1869,7 +1902,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="18" t="n">
-        <v>54325</v>
+        <v>9234</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1877,23 +1910,23 @@
         <v>39</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>4794</v>
+        <v>28632</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>482</v>
+      <c r="C41" s="18" t="n">
+        <v>6300</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>24</v>
+      <c r="C42" s="18" t="n">
+        <v>2558</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1901,15 +1934,15 @@
         <v>42</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>4208</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>272</v>
+      <c r="C44" s="18" t="n">
+        <v>17617</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1917,15 +1950,15 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>698</v>
+      <c r="C46" s="18" t="n">
+        <v>2088</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1933,23 +1966,23 @@
         <v>46</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="true" outlineLevel="3">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>140</v>
+      <c r="C49" s="18" t="n">
+        <v>2480</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1957,79 +1990,79 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" ht="11" customHeight="true" outlineLevel="3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="true" outlineLevel="3">
       <c r="B51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="18" t="n">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C51" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="true" outlineLevel="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C54" s="18" t="n">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="true" outlineLevel="3">
       <c r="B55" s="17" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="true" outlineLevel="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true" outlineLevel="3">
       <c r="B56" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B58" s="16" t="s">
+      <c r="C57" s="18" t="n">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B58" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="12" t="n">
-        <v>13919</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B59" s="17" t="s">
+      <c r="C58" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B59" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>229</v>
+      <c r="C59" s="12" t="n">
+        <v>31253</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2037,7 +2070,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>136</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2045,7 +2078,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>337</v>
+        <v>694</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2053,15 +2086,15 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>329</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>893</v>
+      <c r="C63" s="18" t="n">
+        <v>1032</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2077,7 +2110,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>493</v>
+        <v>508</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2085,15 +2118,15 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>260</v>
+        <v>624</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>469</v>
+      <c r="C67" s="18" t="n">
+        <v>1350</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2101,7 +2134,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>643</v>
+        <v>477</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2109,7 +2142,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>678</v>
+        <v>806</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2117,15 +2150,15 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>755</v>
+        <v>615</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>111</v>
+      <c r="C71" s="18" t="n">
+        <v>2243</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2133,7 +2166,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>565</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2141,63 +2174,63 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>630</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>184</v>
+      <c r="C74" s="18" t="n">
+        <v>1064</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>99</v>
+      <c r="C75" s="18" t="n">
+        <v>3457</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C76" s="18" t="n">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>21</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C78" s="18" t="n">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>582</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="18" t="n">
-        <v>1211</v>
+      <c r="C80" s="11" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2205,15 +2238,15 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>564</v>
+        <v>437</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>681</v>
+      <c r="C82" s="18" t="n">
+        <v>11653</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
@@ -2221,31 +2254,31 @@
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B84" s="17" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="18" t="n">
-        <v>1403</v>
+      <c r="C84" s="12" t="n">
+        <v>71672</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B86" s="16" t="s">
+      <c r="C85" s="18" t="n">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B86" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="12" t="n">
-        <v>42405</v>
+      <c r="C86" s="18" t="n">
+        <v>6992</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2253,7 +2286,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>1980</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2261,15 +2294,15 @@
         <v>87</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>1323</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>419</v>
+      <c r="C89" s="18" t="n">
+        <v>9788</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,7 +2310,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>2011</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2285,7 +2318,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>8928</v>
+        <v>7460</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2293,7 +2326,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>1211</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2301,7 +2334,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>3388</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,7 +2342,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>1776</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2317,7 +2350,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>1434</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2325,7 +2358,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="18" t="n">
-        <v>4197</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2333,15 +2366,15 @@
         <v>96</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>1687</v>
+        <v>12555</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="18" t="n">
-        <v>10418</v>
+      <c r="C98" s="11" t="n">
+        <v>747</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
@@ -2349,7 +2382,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="18" t="n">
-        <v>2071</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2357,39 +2390,39 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>776</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B102" s="17" t="s">
+      <c r="C101" s="18" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B102" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B103" s="13" t="s">
+      <c r="C102" s="12" t="n">
+        <v>616604</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B103" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="12" t="n">
-        <v>417580</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B104" s="16" t="s">
+        <v>50862</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="12" t="n">
-        <v>78296</v>
+      <c r="C104" s="18" t="n">
+        <v>4380</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="true" outlineLevel="3">
@@ -2397,7 +2430,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="18" t="n">
-        <v>3592</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="true" outlineLevel="3">
@@ -2405,7 +2438,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="18" t="n">
-        <v>3420</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2413,7 +2446,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>11318</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2421,15 +2454,15 @@
         <v>107</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>2700</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="18" t="n">
-        <v>3081</v>
+      <c r="C109" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
@@ -2445,7 +2478,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>5577</v>
+        <v>6916</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
@@ -2453,15 +2486,15 @@
         <v>111</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>4500</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="true" outlineLevel="3">
       <c r="B113" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="18" t="n">
-        <v>2891</v>
+      <c r="C113" s="11" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="true" outlineLevel="3">
@@ -2469,7 +2502,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>2700</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="true" outlineLevel="3">
@@ -2477,7 +2510,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="18" t="n">
-        <v>6977</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2485,7 +2518,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>4500</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="true" outlineLevel="3">
@@ -2493,7 +2526,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>1269</v>
+        <v>6527</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="true" outlineLevel="3">
@@ -2501,7 +2534,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>20980</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="true" outlineLevel="3">
@@ -2509,23 +2542,23 @@
         <v>118</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B120" s="16" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B120" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="12" t="n">
-        <v>6653</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B121" s="17" t="s">
+      <c r="C120" s="18" t="n">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B121" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="18" t="n">
-        <v>1133</v>
+      <c r="C121" s="12" t="n">
+        <v>8742</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2533,7 +2566,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>490</v>
+        <v>733</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2541,15 +2574,15 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>687</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="18" t="n">
-        <v>1726</v>
+      <c r="C124" s="11" t="n">
+        <v>723</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2557,7 +2590,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>459</v>
+        <v>696</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2565,7 +2598,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>1154</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,15 +2606,15 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>272</v>
+        <v>984</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>410</v>
+      <c r="C128" s="18" t="n">
+        <v>2403</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2589,15 +2622,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B130" s="16" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B130" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="12" t="n">
-        <v>107219</v>
+      <c r="C130" s="11" t="n">
+        <v>421</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2605,15 +2638,15 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="132" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B132" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="132" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B132" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>394</v>
+      <c r="C132" s="12" t="n">
+        <v>183125</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2621,7 +2654,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>578</v>
+        <v>445</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,23 +2662,23 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>545</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="18" t="n">
-        <v>3579</v>
+      <c r="C135" s="11" t="n">
+        <v>815</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="18" t="n">
-        <v>22358</v>
+      <c r="C136" s="11" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2653,7 +2686,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="18" t="n">
-        <v>45757</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,7 +2694,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>2025</v>
+        <v>68083</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2669,23 +2702,23 @@
         <v>138</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>21079</v>
+        <v>23357</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>178</v>
+      <c r="C140" s="18" t="n">
+        <v>17275</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="11" t="n">
-        <v>325</v>
+      <c r="C141" s="18" t="n">
+        <v>38079</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,15 +2726,15 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="11" t="n">
-        <v>863</v>
+      <c r="C143" s="18" t="n">
+        <v>4299</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,15 +2742,15 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="11" t="n">
-        <v>82</v>
+      <c r="C145" s="18" t="n">
+        <v>2334</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,15 +2758,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>533</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>319</v>
+      <c r="C147" s="18" t="n">
+        <v>2317</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2741,15 +2774,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>1</v>
+        <v>764</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>742</v>
+      <c r="C149" s="18" t="n">
+        <v>2866</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,39 +2790,39 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" ht="11" customHeight="true" outlineLevel="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="true" outlineLevel="3">
       <c r="B151" s="17" t="s">
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>1344</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>165</v>
+      <c r="C152" s="18" t="n">
+        <v>1761</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>449</v>
+      <c r="C153" s="18" t="n">
+        <v>1159</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="18" t="n">
-        <v>1019</v>
+      <c r="C154" s="11" t="n">
+        <v>236</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2797,39 +2830,39 @@
         <v>154</v>
       </c>
       <c r="C155" s="18" t="n">
-        <v>1416</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="18" t="n">
-        <v>1392</v>
+      <c r="C156" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>6</v>
+      <c r="C157" s="18" t="n">
+        <v>2058</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="18" t="n">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="159" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B159" s="16" t="s">
+      <c r="C158" s="11" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="159" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B159" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="12" t="n">
-        <v>73708</v>
+      <c r="C159" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2837,7 +2870,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="18" t="n">
-        <v>1328</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2845,15 +2878,15 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>245</v>
+        <v>802</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="11" t="n">
-        <v>172</v>
+      <c r="C162" s="18" t="n">
+        <v>1973</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2861,7 +2894,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2869,7 +2902,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="18" t="n">
-        <v>2791</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2877,23 +2910,23 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="166" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B166" s="17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B166" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>269</v>
+      <c r="C166" s="12" t="n">
+        <v>162772</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="11" t="n">
-        <v>255</v>
+      <c r="C167" s="18" t="n">
+        <v>2161</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2901,7 +2934,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>488</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,23 +2942,23 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>19</v>
+        <v>382</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
       <c r="B170" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="18" t="n">
-        <v>3892</v>
+      <c r="C170" s="11" t="n">
+        <v>683</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>505</v>
+      <c r="C171" s="18" t="n">
+        <v>2052</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,7 +2966,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2941,7 +2974,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>232</v>
+        <v>909</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,15 +2982,15 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>289</v>
+        <v>737</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="18" t="n">
-        <v>1640</v>
+      <c r="C175" s="11" t="n">
+        <v>914</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,7 +2998,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>259</v>
+        <v>91</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2973,7 +3006,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>685</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2981,7 +3014,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="18" t="n">
-        <v>3354</v>
+        <v>5095</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,15 +3022,15 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>944</v>
+        <v>346</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>18</v>
+      <c r="C180" s="18" t="n">
+        <v>1115</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3005,23 +3038,23 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>906</v>
+        <v>162</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="18" t="n">
-        <v>1026</v>
+      <c r="C182" s="11" t="n">
+        <v>794</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="18" t="n">
-        <v>2470</v>
+      <c r="C183" s="11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,15 +3062,15 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>104</v>
+        <v>916</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>254</v>
+      <c r="C185" s="18" t="n">
+        <v>2064</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +3078,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>770</v>
+        <v>591</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,7 +3086,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="18" t="n">
-        <v>1483</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3061,7 +3094,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>204</v>
+        <v>690</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3069,15 +3102,15 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="190" ht="22" customHeight="true" outlineLevel="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="17" t="s">
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>257</v>
+        <v>772</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3085,39 +3118,39 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>28</v>
+        <v>949</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C192" s="18" t="n">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="17" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>322</v>
+        <v>247</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="195" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C194" s="18" t="n">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="11" t="n">
-        <v>43</v>
+      <c r="C195" s="18" t="n">
+        <v>1393</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3125,7 +3158,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>413</v>
+        <v>182</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3133,39 +3166,39 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="198" ht="11" customHeight="true" outlineLevel="3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="true" outlineLevel="3">
       <c r="B198" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C198" s="18" t="n">
+        <v>22773</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="18" t="n">
-        <v>3712</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C199" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="true" outlineLevel="3">
       <c r="B200" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="11" t="n">
-        <v>7</v>
+      <c r="C200" s="18" t="n">
+        <v>9564</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>888</v>
+      <c r="C201" s="18" t="n">
+        <v>26730</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3173,39 +3206,39 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="203" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="true" outlineLevel="3">
       <c r="B203" s="17" t="s">
         <v>202</v>
       </c>
       <c r="C203" s="18" t="n">
-        <v>3460</v>
-      </c>
-    </row>
-    <row r="204" ht="11" customHeight="true" outlineLevel="3">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="true" outlineLevel="3">
       <c r="B204" s="17" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>274</v>
+        <v>298</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="18" t="n">
-        <v>1437</v>
+      <c r="C205" s="11" t="n">
+        <v>611</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="11" t="n">
-        <v>95</v>
+      <c r="C206" s="18" t="n">
+        <v>16700</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,23 +3246,23 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>22</v>
+        <v>869</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="18" t="n">
-        <v>1963</v>
+      <c r="C208" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="18" t="n">
-        <v>2443</v>
+      <c r="C209" s="11" t="n">
+        <v>577</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3237,7 +3270,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>186</v>
+        <v>711</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3245,7 +3278,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>1581</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3253,7 +3286,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="18" t="n">
-        <v>18770</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3261,7 +3294,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>562</v>
+        <v>789</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3269,7 +3302,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>396</v>
+        <v>29</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,31 +3310,31 @@
         <v>214</v>
       </c>
       <c r="C215" s="18" t="n">
-        <v>1276</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="18" t="n">
-        <v>1318</v>
+      <c r="C216" s="11" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>639</v>
+      <c r="C217" s="18" t="n">
+        <v>1292</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="11" t="n">
-        <v>111</v>
+      <c r="C218" s="18" t="n">
+        <v>1561</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,23 +3342,23 @@
         <v>218</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1756</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="18" t="n">
-        <v>2951</v>
+      <c r="C220" s="11" t="n">
+        <v>872</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="18" t="n">
-        <v>1051</v>
+      <c r="C221" s="11" t="n">
+        <v>804</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,15 +3366,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="223" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B223" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="223" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B223" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="12" t="n">
-        <v>42245</v>
+      <c r="C223" s="18" t="n">
+        <v>2273</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3357,7 +3390,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>694</v>
+        <v>575</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3365,15 +3398,15 @@
         <v>225</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>1125</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="11" t="n">
-        <v>1</v>
+      <c r="C227" s="18" t="n">
+        <v>17943</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3381,7 +3414,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>598</v>
+        <v>410</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3389,7 +3422,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3397,15 +3430,15 @@
         <v>229</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>3823</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>50</v>
+      <c r="C231" s="18" t="n">
+        <v>2270</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3413,7 +3446,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>96</v>
+        <v>416</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3421,7 +3454,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>173</v>
+        <v>234</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3429,7 +3462,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="18" t="n">
-        <v>1189</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3437,7 +3470,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,31 +3478,31 @@
         <v>235</v>
       </c>
       <c r="C236" s="18" t="n">
-        <v>1231</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="18" t="n">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="238" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B238" s="17" t="s">
+      <c r="C237" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B238" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="18" t="n">
-        <v>1024</v>
+      <c r="C238" s="12" t="n">
+        <v>60314</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>791</v>
+      <c r="C239" s="18" t="n">
+        <v>1190</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,23 +3510,23 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>515</v>
+      <c r="C241" s="18" t="n">
+        <v>1453</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="18" t="n">
-        <v>1169</v>
+      <c r="C242" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3501,79 +3534,79 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>903</v>
+        <v>369</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>206</v>
+      <c r="C244" s="18" t="n">
+        <v>1024</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="11" t="n">
-        <v>865</v>
+      <c r="C245" s="18" t="n">
+        <v>6594</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="18" t="n">
-        <v>1891</v>
+      <c r="C246" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="18" t="n">
-        <v>2328</v>
+      <c r="C247" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="18" t="n">
-        <v>2005</v>
+      <c r="C248" s="11" t="n">
+        <v>476</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="18" t="n">
-        <v>1539</v>
+      <c r="C249" s="11" t="n">
+        <v>271</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="18" t="n">
-        <v>2028</v>
+      <c r="C250" s="11" t="n">
+        <v>783</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="18" t="n">
-        <v>1521</v>
+      <c r="C251" s="11" t="n">
+        <v>452</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>115</v>
+      <c r="C252" s="18" t="n">
+        <v>1866</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3581,7 +3614,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="18" t="n">
-        <v>2015</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,15 +3622,15 @@
         <v>253</v>
       </c>
       <c r="C254" s="18" t="n">
-        <v>1351</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="18" t="n">
-        <v>2080</v>
+      <c r="C255" s="11" t="n">
+        <v>973</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,31 +3638,31 @@
         <v>255</v>
       </c>
       <c r="C256" s="18" t="n">
-        <v>1532</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="18" t="n">
-        <v>4315</v>
+      <c r="C257" s="11" t="n">
+        <v>616</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B259" s="16" t="s">
+      <c r="C258" s="18" t="n">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B259" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="12" t="n">
-        <v>5702</v>
+      <c r="C259" s="11" t="n">
+        <v>886</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3637,63 +3670,63 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>744</v>
+        <v>778</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>251</v>
+      <c r="C261" s="18" t="n">
+        <v>1386</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>625</v>
+      <c r="C262" s="18" t="n">
+        <v>3099</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="11" t="n">
-        <v>25</v>
+      <c r="C263" s="18" t="n">
+        <v>2997</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="11" t="n">
-        <v>777</v>
+      <c r="C264" s="18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="11" t="n">
-        <v>201</v>
+      <c r="C265" s="18" t="n">
+        <v>3071</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="11" t="n">
-        <v>64</v>
+      <c r="C266" s="18" t="n">
+        <v>2739</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="11" t="n">
-        <v>336</v>
+      <c r="C267" s="18" t="n">
+        <v>2164</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3701,63 +3734,63 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="11" t="n">
-        <v>292</v>
+      <c r="C269" s="18" t="n">
+        <v>2977</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>255</v>
+      <c r="C270" s="18" t="n">
+        <v>1916</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>283</v>
+      <c r="C271" s="18" t="n">
+        <v>3834</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>765</v>
+      <c r="C272" s="18" t="n">
+        <v>1606</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>85</v>
+      <c r="C273" s="18" t="n">
+        <v>5850</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="275" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B275" s="17" t="s">
+      <c r="C274" s="18" t="n">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="275" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B275" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="11" t="n">
-        <v>120</v>
+      <c r="C275" s="12" t="n">
+        <v>6502</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3765,7 +3798,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>61</v>
+        <v>308</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3773,7 +3806,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3781,15 +3814,15 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="279" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B279" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B279" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="12" t="n">
-        <v>32502</v>
+      <c r="C279" s="11" t="n">
+        <v>229</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3797,7 +3830,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>708</v>
+        <v>80</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3805,7 +3838,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>369</v>
+        <v>11</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3813,7 +3846,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>90</v>
+        <v>771</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,7 +3854,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>716</v>
+        <v>490</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3829,7 +3862,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>539</v>
+        <v>51</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3837,7 +3870,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>893</v>
+        <v>514</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3845,7 +3878,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>811</v>
+        <v>286</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3853,15 +3886,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="17" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>20</v>
+        <v>869</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3869,7 +3902,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>44</v>
+        <v>345</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3877,95 +3910,95 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>235</v>
+        <v>437</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="18" t="n">
-        <v>1440</v>
+      <c r="C291" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="18" t="n">
-        <v>1164</v>
+      <c r="C292" s="11" t="n">
+        <v>566</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="18" t="n">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="294" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C293" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="17" t="s">
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="17" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="17" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="true" outlineLevel="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="17" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="17" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B299" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B299" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C299" s="12" t="n">
+        <v>51741</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="17" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="17" t="s">
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>36</v>
+        <v>214</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3973,7 +4006,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3981,7 +4014,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>601</v>
+        <v>78</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +4022,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>351</v>
+        <v>515</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,23 +4030,23 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>308</v>
+        <v>366</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="18" t="n">
-        <v>3323</v>
+      <c r="C306" s="11" t="n">
+        <v>557</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="18" t="n">
-        <v>1368</v>
+      <c r="C307" s="11" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4021,23 +4054,23 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>634</v>
+        <v>403</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="18" t="n">
-        <v>3209</v>
+      <c r="C310" s="11" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4045,15 +4078,15 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>7</v>
+        <v>374</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="18" t="n">
-        <v>4114</v>
+      <c r="C312" s="11" t="n">
+        <v>912</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -4061,7 +4094,7 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>169</v>
+        <v>504</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -4069,71 +4102,71 @@
         <v>313</v>
       </c>
       <c r="C314" s="18" t="n">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="315" ht="22" customHeight="true" outlineLevel="3">
       <c r="B315" s="17" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="316" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="true" outlineLevel="3">
       <c r="B316" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="18" t="n">
-        <v>3364</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B317" s="16" t="s">
+      <c r="C316" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="317" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B317" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="12" t="n">
-        <v>39803</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C317" s="11" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="true" outlineLevel="3">
       <c r="B318" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="18" t="n">
-        <v>3118</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C318" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="319" ht="22" customHeight="true" outlineLevel="3">
       <c r="B319" s="17" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="17" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>710</v>
+        <v>339</v>
       </c>
     </row>
     <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="18" t="n">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C321" s="11" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="18" t="n">
-        <v>1918</v>
+      <c r="C322" s="11" t="n">
+        <v>436</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4141,7 +4174,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>943</v>
+        <v>509</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4149,7 +4182,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>849</v>
+        <v>457</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4157,7 +4190,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>918</v>
+        <v>335</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4165,7 +4198,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>1288</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -4173,31 +4206,31 @@
         <v>326</v>
       </c>
       <c r="C327" s="18" t="n">
-        <v>1096</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="11" t="n">
-        <v>398</v>
+      <c r="C328" s="18" t="n">
+        <v>2471</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>68</v>
+      <c r="C329" s="18" t="n">
+        <v>1678</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>96</v>
+      <c r="C330" s="18" t="n">
+        <v>2742</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4205,31 +4238,31 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>491</v>
+        <v>7</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="C332" s="11" t="n">
-        <v>321</v>
+      <c r="C332" s="18" t="n">
+        <v>3495</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>343</v>
+      <c r="C333" s="18" t="n">
+        <v>17039</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="11" t="n">
-        <v>350</v>
+      <c r="C334" s="18" t="n">
+        <v>1195</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4237,7 +4270,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>398</v>
+        <v>194</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4245,15 +4278,15 @@
         <v>335</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B337" s="17" t="s">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B337" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>812</v>
+      <c r="C337" s="12" t="n">
+        <v>68575</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4261,7 +4294,7 @@
         <v>337</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>1215</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4269,31 +4302,31 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>498</v>
+        <v>482</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="18" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="17" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="18" t="n">
-        <v>1606</v>
+      <c r="C342" s="11" t="n">
+        <v>689</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4301,7 +4334,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>156</v>
+        <v>692</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4309,7 +4342,7 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>71</v>
+        <v>609</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4317,15 +4350,15 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>206</v>
+        <v>681</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="11" t="n">
-        <v>299</v>
+      <c r="C346" s="18" t="n">
+        <v>2408</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4333,7 +4366,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>257</v>
+        <v>830</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4341,15 +4374,15 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>334</v>
+        <v>926</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="18" t="n">
-        <v>8027</v>
+      <c r="C349" s="11" t="n">
+        <v>340</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
@@ -4357,23 +4390,23 @@
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>997</v>
+        <v>78</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="18" t="n">
-        <v>5551</v>
+      <c r="C351" s="11" t="n">
+        <v>785</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="18" t="n">
-        <v>1581</v>
+      <c r="C352" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4381,7 +4414,7 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4389,7 +4422,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>29</v>
+        <v>440</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4397,23 +4430,23 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B356" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="14" t="n">
-        <v>259</v>
+      <c r="C356" s="11" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="11" t="n">
-        <v>18</v>
+      <c r="C357" s="18" t="n">
+        <v>1493</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4421,23 +4454,23 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>90</v>
+        <v>598</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B360" s="16" t="s">
+      <c r="C359" s="18" t="n">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="12" t="n">
-        <v>31193</v>
+      <c r="C360" s="11" t="n">
+        <v>539</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4445,7 +4478,7 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>17</v>
+        <v>946</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4453,71 +4486,71 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="C363" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="364" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C363" s="18" t="n">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="11" t="n">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C364" s="18" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="17" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
       <c r="B366" s="17" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="17" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="17" t="s">
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="17" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>451</v>
+        <v>247</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="18" t="n">
-        <v>6704</v>
+      <c r="C370" s="11" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4525,39 +4558,39 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="11" t="n">
-        <v>143</v>
+      <c r="C372" s="18" t="n">
+        <v>1045</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="18" t="n">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C373" s="11" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C374" s="11" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="375" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C374" s="18" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="17" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>460</v>
+        <v>284</v>
       </c>
     </row>
     <row r="376" ht="22" customHeight="true" outlineLevel="3">
@@ -4565,127 +4598,127 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C377" s="18" t="n">
+        <v>9264</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="18" t="n">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C378" s="11" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="11" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C379" s="18" t="n">
+        <v>21033</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C380" s="18" t="n">
+        <v>6472</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="382" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C381" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
       <c r="B382" s="17" t="s">
         <v>381</v>
       </c>
       <c r="C382" s="18" t="n">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="383" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B383" s="17" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B383" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="11" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="384" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C383" s="14" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
       <c r="B384" s="17" t="s">
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="385" ht="22" customHeight="true" outlineLevel="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
       <c r="B385" s="17" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="17" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
       <c r="B387" s="17" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="388" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B388" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B388" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C388" s="12" t="n">
+        <v>23718</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="17" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="391" ht="22" customHeight="true" outlineLevel="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
       <c r="B391" s="17" t="s">
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4693,7 +4726,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>133</v>
+        <v>566</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4701,15 +4734,15 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>51</v>
+        <v>587</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="true" outlineLevel="3">
@@ -4717,7 +4750,7 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>331</v>
+        <v>305</v>
       </c>
     </row>
     <row r="396" ht="22" customHeight="true" outlineLevel="3">
@@ -4725,7 +4758,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="397" ht="22" customHeight="true" outlineLevel="3">
@@ -4733,7 +4766,7 @@
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4741,7 +4774,7 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>330</v>
+        <v>132</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4749,23 +4782,23 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C400" s="18" t="n">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="17" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>24</v>
+        <v>129</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
@@ -4773,7 +4806,7 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>6</v>
+        <v>701</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4781,7 +4814,7 @@
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="404" ht="22" customHeight="true" outlineLevel="3">
@@ -4789,7 +4822,7 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>76</v>
+        <v>835</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="true" outlineLevel="3">
@@ -4797,7 +4830,7 @@
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
     </row>
     <row r="406" ht="22" customHeight="true" outlineLevel="3">
@@ -4805,7 +4838,7 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
     </row>
     <row r="407" ht="22" customHeight="true" outlineLevel="3">
@@ -4813,23 +4846,23 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
       <c r="B409" s="17" t="s">
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>359</v>
+        <v>119</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="true" outlineLevel="3">
@@ -4837,15 +4870,15 @@
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
       <c r="B411" s="17" t="s">
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>268</v>
+        <v>561</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
@@ -4853,47 +4886,47 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="413" ht="11" customHeight="true" outlineLevel="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
       <c r="B413" s="17" t="s">
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="17" t="s">
         <v>413</v>
       </c>
       <c r="C414" s="11" t="n">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
       <c r="B415" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="C415" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C415" s="18" t="n">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
       <c r="B416" s="17" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
       <c r="B417" s="17" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>664</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418" ht="22" customHeight="true" outlineLevel="3">
@@ -4901,7 +4934,7 @@
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>15</v>
+        <v>121</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -4909,31 +4942,31 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
       <c r="B420" s="17" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="true" outlineLevel="3">
       <c r="B421" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="18" t="n">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C421" s="11" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
       <c r="B422" s="17" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>459</v>
+        <v>24</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="true" outlineLevel="3">
@@ -4941,7 +4974,7 @@
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="true" outlineLevel="3">
@@ -4949,39 +4982,39 @@
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
       <c r="B425" s="17" t="s">
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="17" t="s">
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
       <c r="B427" s="17" t="s">
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="18" t="n">
-        <v>1264</v>
+      <c r="C428" s="11" t="n">
+        <v>252</v>
       </c>
     </row>
     <row r="429" ht="11" customHeight="true" outlineLevel="3">
@@ -4989,7 +5022,7 @@
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>280</v>
+        <v>209</v>
       </c>
     </row>
     <row r="430" ht="11" customHeight="true" outlineLevel="3">
@@ -4997,15 +5030,15 @@
         <v>429</v>
       </c>
       <c r="C430" s="11" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
       <c r="B431" s="17" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>303</v>
+        <v>4</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
@@ -5013,7 +5046,7 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="433" ht="11" customHeight="true" outlineLevel="3">
@@ -5021,31 +5054,135 @@
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="434" ht="22" customHeight="true" outlineLevel="3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
       <c r="B434" s="17" t="s">
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="435" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B435" s="19" t="s">
+      <c r="B435" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C435" s="14" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="436" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B436" s="20" t="s">
+      <c r="C435" s="11" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B436" s="17" t="s">
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>105</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B437" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B438" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="18" t="n">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="439" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B439" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="442" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B442" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="443" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B443" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="11" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="444" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B444" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B445" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="18" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="446" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B446" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="11" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="447" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B447" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B448" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="18" t="n">
+        <v>6328</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B449" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>888</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 11.02.2026 19:55:12</t>
+    <t>Период: на 16.02.2026 7:55:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -92,9 +92,6 @@
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -104,9 +101,6 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Ванільний цукор УБ 35г /36шт</t>
   </si>
   <si>
@@ -236,6 +227,9 @@
     <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Прованські трави УБ 10г /28шт</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -308,9 +302,6 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -335,9 +326,6 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
@@ -368,6 +356,9 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
@@ -425,6 +416,9 @@
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -566,9 +560,6 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -647,9 +638,6 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -1076,9 +1064,6 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -1151,6 +1136,9 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -1163,6 +1151,9 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1202,6 +1193,9 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1235,7 +1229,7 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
@@ -1247,7 +1241,7 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
@@ -1256,6 +1250,9 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
@@ -1328,18 +1325,12 @@
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1349,9 +1340,6 @@
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1365,6 +1353,9 @@
   </si>
   <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1604,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C449"/>
+  <dimension ref="C446"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1678,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>478</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1686,7 +1677,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>838939</v>
+        <v>916750</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1710,7 +1701,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>222284</v>
+        <v>241183</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
@@ -1718,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>38851</v>
+        <v>35004</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1726,7 +1717,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>3513</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1742,7 +1733,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>4196</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1750,7 +1741,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>388</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1766,7 +1757,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>3846</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1774,7 +1765,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>644</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1782,7 +1773,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>5390</v>
+        <v>5296</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1790,23 +1781,23 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>32</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>201</v>
+      <c r="C26" s="18" t="n">
+        <v>5064</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="18" t="n">
-        <v>5277</v>
+      <c r="C27" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1814,15 +1805,15 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>1</v>
+      <c r="C29" s="18" t="n">
+        <v>2826</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1830,23 +1821,23 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>136</v>
+        <v>812</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="18" t="n">
-        <v>3057</v>
+      <c r="C31" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>812</v>
+      <c r="C32" s="18" t="n">
+        <v>2801</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1854,7 +1845,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>39</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1862,23 +1853,23 @@
         <v>33</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>2996</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="36" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B36" s="17" t="s">
+      <c r="C35" s="18" t="n">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="36" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B36" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="18" t="n">
-        <v>1401</v>
+      <c r="C36" s="12" t="n">
+        <v>108314</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1886,15 +1877,15 @@
         <v>36</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>5057</v>
-      </c>
-    </row>
-    <row r="38" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B38" s="16" t="s">
+        <v>7498</v>
+      </c>
+    </row>
+    <row r="38" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="12" t="n">
-        <v>80508</v>
+      <c r="C38" s="18" t="n">
+        <v>69457</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1902,7 +1893,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="18" t="n">
-        <v>9234</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1910,7 +1901,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>28632</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1918,15 +1909,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>6300</v>
+        <v>14432</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="18" t="n">
-        <v>2558</v>
+      <c r="C42" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1934,15 +1925,15 @@
         <v>42</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>4794</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="18" t="n">
-        <v>17617</v>
+      <c r="C44" s="11" t="n">
+        <v>259</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1950,7 +1941,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1958,31 +1949,31 @@
         <v>45</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>2088</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="18" t="n">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="48" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C47" s="11" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="18" t="n">
-        <v>2480</v>
+      <c r="C49" s="11" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1990,23 +1981,23 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="true" outlineLevel="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C51" s="18" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2014,7 +2005,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>146</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2022,7 +2013,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>2047</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="true" outlineLevel="3">
@@ -2030,15 +2021,15 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B56" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B56" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>10</v>
+      <c r="C56" s="12" t="n">
+        <v>34417</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2046,23 +2037,23 @@
         <v>56</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="true" outlineLevel="3">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="17" t="s">
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B59" s="16" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B59" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="12" t="n">
-        <v>31253</v>
+      <c r="C59" s="11" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2070,7 +2061,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>464</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2078,7 +2069,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>694</v>
+        <v>587</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2086,15 +2077,15 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>217</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="18" t="n">
-        <v>1032</v>
+      <c r="C63" s="11" t="n">
+        <v>604</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2102,7 +2093,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>655</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2110,7 +2101,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>508</v>
+        <v>405</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2118,23 +2109,23 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>624</v>
+        <v>738</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="18" t="n">
-        <v>1350</v>
+      <c r="C67" s="11" t="n">
+        <v>605</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>477</v>
+      <c r="C68" s="18" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2142,23 +2133,23 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>806</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>615</v>
+      <c r="C70" s="18" t="n">
+        <v>5040</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="18" t="n">
-        <v>2243</v>
+      <c r="C71" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2166,15 +2157,15 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>157</v>
+        <v>894</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>100</v>
+      <c r="C73" s="18" t="n">
+        <v>3366</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2182,15 +2173,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="3">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="true" outlineLevel="3">
       <c r="B75" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="18" t="n">
-        <v>3457</v>
+      <c r="C75" s="11" t="n">
+        <v>338</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2198,23 +2189,23 @@
         <v>75</v>
       </c>
       <c r="C76" s="18" t="n">
-        <v>1456</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="true" outlineLevel="3">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>362</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="18" t="n">
-        <v>1795</v>
+      <c r="C78" s="11" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2222,15 +2213,15 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>264</v>
+      <c r="C80" s="18" t="n">
+        <v>11168</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2238,31 +2229,31 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B82" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="18" t="n">
-        <v>11653</v>
+      <c r="C82" s="12" t="n">
+        <v>63448</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="16" t="s">
+      <c r="C83" s="18" t="n">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B84" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>71672</v>
+      <c r="C84" s="18" t="n">
+        <v>6542</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2270,7 +2261,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>2940</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2278,7 +2269,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>6992</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2286,7 +2277,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>3543</v>
+        <v>9021</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2294,7 +2285,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>3929</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2302,7 +2293,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>9788</v>
+        <v>7029</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2310,7 +2301,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>3460</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2318,7 +2309,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>7460</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2326,7 +2317,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>3816</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2334,7 +2325,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>1908</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2342,7 +2333,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>4606</v>
+        <v>10321</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2350,7 +2341,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>1143</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2358,119 +2349,119 @@
         <v>95</v>
       </c>
       <c r="C96" s="18" t="n">
-        <v>4639</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="18" t="n">
-        <v>12555</v>
+      <c r="C97" s="11" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B99" s="17" t="s">
+      <c r="C98" s="18" t="n">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B99" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="18" t="n">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B100" s="17" t="s">
+      <c r="C99" s="12" t="n">
+        <v>675516</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B100" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="12" t="n">
+        <v>117575</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="17" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="18" t="n">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B102" s="13" t="s">
+        <v>25214</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B102" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="12" t="n">
-        <v>616604</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B103" s="16" t="s">
+      <c r="C102" s="11" t="n">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B103" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="12" t="n">
-        <v>50862</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C103" s="18" t="n">
+        <v>21637</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="18" t="n">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C104" s="11" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="18" t="n">
-        <v>1822</v>
+      <c r="C105" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="18" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C106" s="11" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="17" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>5828</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="17" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>291</v>
+      <c r="C110" s="18" t="n">
+        <v>11884</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2478,15 +2469,15 @@
         <v>110</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>6916</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="18" t="n">
-        <v>1950</v>
+      <c r="C112" s="11" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="true" outlineLevel="3">
@@ -2494,7 +2485,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="true" outlineLevel="3">
@@ -2502,7 +2493,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>5642</v>
+        <v>23446</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="true" outlineLevel="3">
@@ -2510,7 +2501,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="18" t="n">
-        <v>6461</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2518,7 +2509,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>1680</v>
+        <v>21345</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="true" outlineLevel="3">
@@ -2526,39 +2517,39 @@
         <v>116</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>6527</v>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B118" s="17" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="118" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B118" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="18" t="n">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C118" s="12" t="n">
+        <v>7571</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="17" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="true" outlineLevel="3">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="18" t="n">
-        <v>2220</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B121" s="16" t="s">
+      <c r="C120" s="11" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B121" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="12" t="n">
-        <v>8742</v>
+      <c r="C121" s="11" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2566,15 +2557,15 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>733</v>
+        <v>429</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>234</v>
+      <c r="C123" s="18" t="n">
+        <v>1616</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2582,23 +2573,23 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>723</v>
+        <v>712</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>696</v>
+      <c r="C125" s="18" t="n">
+        <v>2081</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="18" t="n">
-        <v>1891</v>
+      <c r="C126" s="11" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2606,23 +2597,23 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>984</v>
+        <v>352</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="18" t="n">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="129" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B129" s="17" t="s">
+      <c r="C128" s="11" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="129" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B129" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="11" t="n">
-        <v>307</v>
+      <c r="C129" s="12" t="n">
+        <v>175424</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2630,7 +2621,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>421</v>
+        <v>986</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2638,15 +2629,15 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="132" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B132" s="16" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="132" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B132" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="12" t="n">
-        <v>183125</v>
+      <c r="C132" s="11" t="n">
+        <v>535</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2654,31 +2645,31 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>445</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>301</v>
+      <c r="C134" s="18" t="n">
+        <v>1223</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>815</v>
+      <c r="C135" s="18" t="n">
+        <v>1501</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>504</v>
+      <c r="C136" s="18" t="n">
+        <v>66283</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2686,7 +2677,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="18" t="n">
-        <v>1727</v>
+        <v>22782</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2694,7 +2685,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>68083</v>
+        <v>16475</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2702,15 +2693,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>23357</v>
+        <v>36904</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="18" t="n">
-        <v>17275</v>
+      <c r="C140" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2718,7 +2709,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="18" t="n">
-        <v>38079</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2726,7 +2717,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>237</v>
+        <v>93</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2734,7 +2725,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="18" t="n">
-        <v>4299</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2742,7 +2733,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2750,7 +2741,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="18" t="n">
-        <v>2334</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2758,7 +2749,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>298</v>
+        <v>759</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2766,7 +2757,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="18" t="n">
-        <v>2317</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2774,39 +2765,39 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="149" ht="11" customHeight="true" outlineLevel="3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="true" outlineLevel="3">
       <c r="B149" s="17" t="s">
         <v>148</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>2866</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="11" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="151" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C150" s="18" t="n">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="17" t="s">
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>5275</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="18" t="n">
-        <v>1761</v>
+      <c r="C152" s="11" t="n">
+        <v>236</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2814,7 +2805,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="18" t="n">
-        <v>1159</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2822,7 +2813,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>236</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2830,7 +2821,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="18" t="n">
-        <v>1535</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2838,23 +2829,23 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>6</v>
+        <v>243</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="18" t="n">
-        <v>2058</v>
+      <c r="C157" s="11" t="n">
+        <v>634</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="11" t="n">
-        <v>474</v>
+      <c r="C158" s="18" t="n">
+        <v>1156</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2862,7 +2853,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>66</v>
+        <v>563</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2870,7 +2861,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="18" t="n">
-        <v>1247</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2878,7 +2869,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>802</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2886,7 +2877,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="18" t="n">
-        <v>1973</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2894,39 +2885,39 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="164" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B164" s="17" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="164" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B164" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="18" t="n">
-        <v>2133</v>
+      <c r="C164" s="12" t="n">
+        <v>157091</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="166" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B166" s="16" t="s">
+      <c r="C165" s="18" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="166" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B166" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="12" t="n">
-        <v>162772</v>
+      <c r="C166" s="11" t="n">
+        <v>357</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="18" t="n">
-        <v>2161</v>
+      <c r="C167" s="11" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2934,15 +2925,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>408</v>
+        <v>625</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="11" t="n">
-        <v>382</v>
+      <c r="C169" s="18" t="n">
+        <v>2041</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2950,15 +2941,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>683</v>
+        <v>600</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="18" t="n">
-        <v>2052</v>
+      <c r="C171" s="11" t="n">
+        <v>904</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2966,7 +2957,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>600</v>
+        <v>541</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2974,7 +2965,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>909</v>
+        <v>881</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2982,7 +2973,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>737</v>
+        <v>64</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2990,15 +2981,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>914</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="11" t="n">
-        <v>91</v>
+      <c r="C176" s="18" t="n">
+        <v>4958</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3006,7 +2997,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>20</v>
+        <v>305</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3014,7 +3005,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="18" t="n">
-        <v>5095</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3022,15 +3013,15 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>346</v>
+        <v>155</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="18" t="n">
-        <v>1115</v>
+      <c r="C180" s="11" t="n">
+        <v>776</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3038,15 +3029,15 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>162</v>
+        <v>870</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>794</v>
+      <c r="C182" s="18" t="n">
+        <v>1033</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3054,7 +3045,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>5</v>
+        <v>583</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3062,15 +3053,15 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>916</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="18" t="n">
-        <v>2064</v>
+      <c r="C185" s="11" t="n">
+        <v>685</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3078,15 +3069,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>591</v>
+        <v>15</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="18" t="n">
-        <v>1046</v>
+      <c r="C187" s="11" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3094,15 +3085,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>690</v>
+        <v>946</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>15</v>
+      <c r="C189" s="18" t="n">
+        <v>1374</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3110,15 +3101,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>772</v>
+        <v>247</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="11" t="n">
-        <v>949</v>
+      <c r="C191" s="18" t="n">
+        <v>3659</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3126,7 +3117,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="18" t="n">
-        <v>2088</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3134,55 +3125,55 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>247</v>
+        <v>125</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="18" t="n">
-        <v>3833</v>
-      </c>
-    </row>
-    <row r="195" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C194" s="11" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="196" ht="11" customHeight="true" outlineLevel="3">
+        <v>22265</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="197" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="true" outlineLevel="3">
       <c r="B197" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="198" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C197" s="18" t="n">
+        <v>9161</v>
+      </c>
+    </row>
+    <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="17" t="s">
         <v>197</v>
       </c>
       <c r="C198" s="18" t="n">
-        <v>22773</v>
-      </c>
-    </row>
-    <row r="199" ht="22" customHeight="true" outlineLevel="3">
+        <v>26215</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200" ht="22" customHeight="true" outlineLevel="3">
@@ -3190,15 +3181,15 @@
         <v>199</v>
       </c>
       <c r="C200" s="18" t="n">
-        <v>9564</v>
-      </c>
-    </row>
-    <row r="201" ht="11" customHeight="true" outlineLevel="3">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="18" t="n">
-        <v>26730</v>
+      <c r="C201" s="11" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3206,23 +3197,23 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="203" ht="22" customHeight="true" outlineLevel="3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="17" t="s">
         <v>202</v>
       </c>
       <c r="C203" s="18" t="n">
-        <v>4816</v>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="true" outlineLevel="3">
+        <v>16187</v>
+      </c>
+    </row>
+    <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="17" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>298</v>
+        <v>861</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3230,15 +3221,15 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>611</v>
+        <v>86</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="18" t="n">
-        <v>16700</v>
+      <c r="C206" s="11" t="n">
+        <v>577</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3246,15 +3237,15 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>869</v>
+        <v>929</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="11" t="n">
-        <v>86</v>
+      <c r="C208" s="18" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3262,7 +3253,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>577</v>
+        <v>773</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3270,7 +3261,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>711</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3278,7 +3269,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>1009</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3286,23 +3277,23 @@
         <v>211</v>
       </c>
       <c r="C212" s="18" t="n">
-        <v>2061</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>789</v>
+      <c r="C213" s="18" t="n">
+        <v>1292</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="11" t="n">
-        <v>29</v>
+      <c r="C214" s="18" t="n">
+        <v>1547</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3310,7 +3301,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="18" t="n">
-        <v>2731</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3318,15 +3309,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>49</v>
+        <v>850</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="18" t="n">
-        <v>1292</v>
+      <c r="C217" s="11" t="n">
+        <v>799</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3334,7 +3325,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="18" t="n">
-        <v>1561</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3342,7 +3333,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1115</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3350,7 +3341,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>872</v>
+        <v>828</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3358,15 +3349,15 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>804</v>
+        <v>327</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="11" t="n">
-        <v>304</v>
+      <c r="C222" s="18" t="n">
+        <v>1057</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3374,7 +3365,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="18" t="n">
-        <v>2273</v>
+        <v>17708</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3382,7 +3373,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>870</v>
+        <v>407</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3390,7 +3381,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>575</v>
+        <v>609</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3398,7 +3389,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>1057</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3406,7 +3397,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="18" t="n">
-        <v>17943</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3414,7 +3405,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3422,7 +3413,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>656</v>
+        <v>225</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3430,23 +3421,23 @@
         <v>229</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>1890</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="18" t="n">
-        <v>2270</v>
+      <c r="C231" s="11" t="n">
+        <v>445</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>416</v>
+      <c r="C232" s="18" t="n">
+        <v>3918</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3454,55 +3445,55 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B234" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B234" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="18" t="n">
-        <v>1544</v>
+      <c r="C234" s="12" t="n">
+        <v>53483</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="11" t="n">
-        <v>457</v>
+      <c r="C235" s="18" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="18" t="n">
-        <v>3933</v>
+      <c r="C236" s="11" t="n">
+        <v>428</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="238" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B238" s="16" t="s">
+      <c r="C237" s="18" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B238" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="12" t="n">
-        <v>60314</v>
+      <c r="C238" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="18" t="n">
-        <v>1190</v>
+      <c r="C239" s="11" t="n">
+        <v>369</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3510,7 +3501,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>489</v>
+        <v>769</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3518,7 +3509,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="18" t="n">
-        <v>1453</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3526,7 +3517,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3534,23 +3525,23 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>369</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="18" t="n">
-        <v>1024</v>
+      <c r="C244" s="11" t="n">
+        <v>457</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="18" t="n">
-        <v>6594</v>
+      <c r="C245" s="11" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3558,7 +3549,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>360</v>
+        <v>706</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3566,31 +3557,31 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>476</v>
+      <c r="C248" s="18" t="n">
+        <v>1340</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>271</v>
+      <c r="C249" s="18" t="n">
+        <v>1894</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>783</v>
+      <c r="C250" s="18" t="n">
+        <v>1626</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3598,23 +3589,23 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>452</v>
+        <v>723</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="18" t="n">
-        <v>1866</v>
+      <c r="C252" s="11" t="n">
+        <v>719</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="18" t="n">
-        <v>2199</v>
+      <c r="C253" s="11" t="n">
+        <v>571</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3622,31 +3613,31 @@
         <v>253</v>
       </c>
       <c r="C254" s="18" t="n">
-        <v>1383</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>973</v>
+      <c r="C255" s="18" t="n">
+        <v>1265</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="18" t="n">
-        <v>1050</v>
+      <c r="C256" s="11" t="n">
+        <v>678</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="n">
-        <v>616</v>
+      <c r="C257" s="18" t="n">
+        <v>1181</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3654,23 +3645,23 @@
         <v>257</v>
       </c>
       <c r="C258" s="18" t="n">
-        <v>1747</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="11" t="n">
-        <v>886</v>
+      <c r="C259" s="18" t="n">
+        <v>3283</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>778</v>
+      <c r="C260" s="18" t="n">
+        <v>1735</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3678,7 +3669,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>1386</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3686,7 +3677,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>3099</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3694,7 +3685,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>2997</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3702,7 +3693,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>2025</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3710,7 +3701,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>3071</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3718,7 +3709,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>2739</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3726,15 +3717,15 @@
         <v>266</v>
       </c>
       <c r="C267" s="18" t="n">
-        <v>2164</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="11" t="n">
-        <v>90</v>
+      <c r="C268" s="18" t="n">
+        <v>1696</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3742,7 +3733,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="18" t="n">
-        <v>2977</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3750,47 +3741,47 @@
         <v>269</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B271" s="17" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B271" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="18" t="n">
-        <v>3834</v>
+      <c r="C271" s="12" t="n">
+        <v>5095</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="18" t="n">
-        <v>1606</v>
+      <c r="C272" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="18" t="n">
-        <v>5850</v>
+      <c r="C273" s="11" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="18" t="n">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="275" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B275" s="16" t="s">
+      <c r="C274" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="275" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B275" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="12" t="n">
-        <v>6502</v>
+      <c r="C275" s="11" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3798,7 +3789,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>308</v>
+        <v>80</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3806,7 +3797,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>114</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3814,7 +3805,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>80</v>
+        <v>418</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3822,7 +3813,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>229</v>
+        <v>390</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3830,7 +3821,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3838,7 +3829,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>11</v>
+        <v>437</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3846,7 +3837,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>771</v>
+        <v>286</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3854,7 +3845,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>490</v>
+        <v>555</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3862,7 +3853,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>51</v>
+        <v>829</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3870,7 +3861,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>514</v>
+        <v>345</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3878,7 +3869,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3886,7 +3877,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>607</v>
+        <v>60</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3894,7 +3885,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>869</v>
+        <v>429</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3902,7 +3893,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>345</v>
+        <v>35</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3910,7 +3901,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>437</v>
+        <v>142</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3918,7 +3909,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3926,7 +3917,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>566</v>
+        <v>112</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3934,7 +3925,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3942,15 +3933,15 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B295" s="17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B295" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="11" t="n">
-        <v>58</v>
+      <c r="C295" s="12" t="n">
+        <v>53377</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -3958,7 +3949,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>119</v>
+        <v>485</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3966,7 +3957,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3974,15 +3965,15 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B299" s="16" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B299" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="12" t="n">
-        <v>51741</v>
+      <c r="C299" s="11" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3990,7 +3981,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>579</v>
+        <v>490</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3998,7 +3989,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>214</v>
+        <v>349</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4006,7 +3997,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4014,7 +4005,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4022,15 +4013,15 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="305" ht="11" customHeight="true" outlineLevel="3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="true" outlineLevel="3">
       <c r="B305" s="17" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4038,7 +4029,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>557</v>
+        <v>73</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4046,7 +4037,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>493</v>
+        <v>292</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4054,55 +4045,55 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="11" t="n">
-        <v>403</v>
+      <c r="C309" s="18" t="n">
+        <v>1794</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C310" s="18" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="17" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="17" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="17" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="314" ht="11" customHeight="true" outlineLevel="3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="true" outlineLevel="3">
       <c r="B314" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="18" t="n">
-        <v>1181</v>
+      <c r="C314" s="11" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="315" ht="22" customHeight="true" outlineLevel="3">
@@ -4110,7 +4101,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>18</v>
+        <v>400</v>
       </c>
     </row>
     <row r="316" ht="22" customHeight="true" outlineLevel="3">
@@ -4118,7 +4109,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>42</v>
+        <v>286</v>
       </c>
     </row>
     <row r="317" ht="22" customHeight="true" outlineLevel="3">
@@ -4126,71 +4117,71 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="17" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="17" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="17" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>104</v>
+        <v>275</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>436</v>
+      <c r="C322" s="18" t="n">
+        <v>4258</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>509</v>
+      <c r="C323" s="18" t="n">
+        <v>2451</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="11" t="n">
-        <v>457</v>
+      <c r="C324" s="18" t="n">
+        <v>2039</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>335</v>
+      <c r="C325" s="18" t="n">
+        <v>1322</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4198,15 +4189,15 @@
         <v>325</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>2724</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="18" t="n">
-        <v>2905</v>
+      <c r="C327" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4214,7 +4205,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="18" t="n">
-        <v>2471</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4222,7 +4213,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="18" t="n">
-        <v>1678</v>
+        <v>17195</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4230,7 +4221,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="18" t="n">
-        <v>2742</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4238,7 +4229,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>7</v>
+        <v>194</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4246,15 +4237,15 @@
         <v>331</v>
       </c>
       <c r="C332" s="18" t="n">
-        <v>3495</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B333" s="17" t="s">
+        <v>5687</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B333" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="18" t="n">
-        <v>17039</v>
+      <c r="C333" s="12" t="n">
+        <v>60967</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4262,7 +4253,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="18" t="n">
-        <v>1195</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4270,31 +4261,31 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>194</v>
+        <v>382</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="18" t="n">
-        <v>6758</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B337" s="16" t="s">
+      <c r="C336" s="11" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B337" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="12" t="n">
-        <v>68575</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C337" s="11" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="17" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>2401</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4302,31 +4293,31 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>482</v>
+        <v>839</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="18" t="n">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="17" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="11" t="n">
-        <v>689</v>
+      <c r="C342" s="18" t="n">
+        <v>1655</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4334,7 +4325,7 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>692</v>
+        <v>830</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4342,7 +4333,7 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>609</v>
+        <v>678</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4350,15 +4341,15 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>681</v>
+        <v>297</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="18" t="n">
-        <v>2408</v>
+      <c r="C346" s="11" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4366,7 +4357,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>830</v>
+        <v>703</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4374,7 +4365,7 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>926</v>
+        <v>295</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4382,7 +4373,7 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>340</v>
+        <v>427</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
@@ -4390,7 +4381,7 @@
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4398,15 +4389,15 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>785</v>
+        <v>397</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>295</v>
+      <c r="C352" s="18" t="n">
+        <v>1297</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4414,15 +4405,15 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>61</v>
+        <v>498</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="11" t="n">
-        <v>440</v>
+      <c r="C354" s="18" t="n">
+        <v>1061</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4430,7 +4421,7 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>78</v>
+        <v>491</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
@@ -4438,23 +4429,23 @@
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>397</v>
+        <v>828</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="18" t="n">
-        <v>1493</v>
+      <c r="C357" s="11" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="11" t="n">
-        <v>598</v>
+      <c r="C358" s="18" t="n">
+        <v>3324</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4462,7 +4453,7 @@
         <v>358</v>
       </c>
       <c r="C359" s="18" t="n">
-        <v>1263</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4470,55 +4461,55 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
       <c r="B361" s="17" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="362" ht="22" customHeight="true" outlineLevel="3">
       <c r="B362" s="17" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="C363" s="18" t="n">
-        <v>3631</v>
+      <c r="C363" s="11" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="18" t="n">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C364" s="11" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
       <c r="B365" s="17" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="17" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>381</v>
+        <v>257</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="true" outlineLevel="3">
@@ -4526,7 +4517,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>310</v>
+        <v>754</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4534,39 +4525,39 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="true" outlineLevel="3">
       <c r="B369" s="17" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="true" outlineLevel="3">
       <c r="B371" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="17" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1045</v>
+        <v>7892</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
@@ -4574,31 +4565,31 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="374" ht="22" customHeight="true" outlineLevel="3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C374" s="18" t="n">
-        <v>1080</v>
+      <c r="C374" s="11" t="n">
+        <v>521</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="11" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="376" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C375" s="18" t="n">
+        <v>18805</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
       <c r="B376" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="11" t="n">
-        <v>746</v>
+      <c r="C376" s="18" t="n">
+        <v>5837</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4606,7 +4597,7 @@
         <v>376</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>9264</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
@@ -4614,47 +4605,47 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>451</v>
+        <v>93</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="18" t="n">
-        <v>21033</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B380" s="17" t="s">
+      <c r="C379" s="11" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B380" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="18" t="n">
-        <v>6472</v>
+      <c r="C380" s="14" t="n">
+        <v>253</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="18" t="n">
-        <v>1603</v>
+      <c r="C381" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
       <c r="B382" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="18" t="n">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B383" s="16" t="s">
+      <c r="C382" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="14" t="n">
-        <v>253</v>
+      <c r="C383" s="11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4662,15 +4653,15 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B385" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B385" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="11" t="n">
-        <v>85</v>
+      <c r="C385" s="12" t="n">
+        <v>44680</v>
       </c>
     </row>
     <row r="386" ht="11" customHeight="true" outlineLevel="3">
@@ -4678,7 +4669,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4686,31 +4677,31 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B388" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B388" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="12" t="n">
-        <v>23718</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C388" s="11" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="17" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>71</v>
+        <v>169</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4718,31 +4709,31 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
       <c r="B392" s="17" t="s">
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>566</v>
+        <v>44</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
       <c r="B393" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="11" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C393" s="18" t="n">
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
       <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>587</v>
+        <v>77</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="true" outlineLevel="3">
@@ -4750,23 +4741,23 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
       <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4774,7 +4765,7 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>132</v>
+        <v>436</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4782,31 +4773,31 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="18" t="n">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C400" s="11" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
       <c r="B401" s="17" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>129</v>
+        <v>42</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="C402" s="11" t="n">
-        <v>701</v>
+      <c r="C402" s="18" t="n">
+        <v>4214</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4814,7 +4805,7 @@
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="404" ht="22" customHeight="true" outlineLevel="3">
@@ -4822,23 +4813,23 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>835</v>
+        <v>110</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="11" t="n">
-        <v>95</v>
+      <c r="C405" s="18" t="n">
+        <v>3915</v>
       </c>
     </row>
     <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="11" t="n">
-        <v>42</v>
+      <c r="C406" s="18" t="n">
+        <v>4023</v>
       </c>
     </row>
     <row r="407" ht="22" customHeight="true" outlineLevel="3">
@@ -4846,7 +4837,7 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="408" ht="22" customHeight="true" outlineLevel="3">
@@ -4854,7 +4845,7 @@
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>451</v>
+        <v>36</v>
       </c>
     </row>
     <row r="409" ht="22" customHeight="true" outlineLevel="3">
@@ -4862,7 +4853,7 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="true" outlineLevel="3">
@@ -4870,7 +4861,7 @@
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" ht="22" customHeight="true" outlineLevel="3">
@@ -4878,7 +4869,7 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>561</v>
+        <v>18</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
@@ -4886,7 +4877,7 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="true" outlineLevel="3">
@@ -4894,7 +4885,7 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
@@ -4902,15 +4893,15 @@
         <v>413</v>
       </c>
       <c r="C414" s="11" t="n">
-        <v>85</v>
+        <v>543</v>
       </c>
     </row>
     <row r="415" ht="22" customHeight="true" outlineLevel="3">
       <c r="B415" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="C415" s="18" t="n">
-        <v>1270</v>
+      <c r="C415" s="11" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="416" ht="22" customHeight="true" outlineLevel="3">
@@ -4918,7 +4909,7 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>239</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417" ht="22" customHeight="true" outlineLevel="3">
@@ -4926,15 +4917,15 @@
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="3">
       <c r="B418" s="17" t="s">
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -4942,15 +4933,15 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
       <c r="B420" s="17" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="true" outlineLevel="3">
@@ -4958,7 +4949,7 @@
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>147</v>
+        <v>24</v>
       </c>
     </row>
     <row r="422" ht="22" customHeight="true" outlineLevel="3">
@@ -4966,7 +4957,7 @@
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="true" outlineLevel="3">
@@ -4974,7 +4965,7 @@
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="true" outlineLevel="3">
@@ -4982,7 +4973,7 @@
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="425" ht="22" customHeight="true" outlineLevel="3">
@@ -4990,15 +4981,15 @@
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="C426" s="11" t="n">
-        <v>125</v>
+      <c r="C426" s="18" t="n">
+        <v>4489</v>
       </c>
     </row>
     <row r="427" ht="22" customHeight="true" outlineLevel="3">
@@ -5006,15 +4997,15 @@
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
       <c r="B428" s="17" t="s">
         <v>427</v>
       </c>
       <c r="C428" s="11" t="n">
-        <v>252</v>
+        <v>176</v>
       </c>
     </row>
     <row r="429" ht="11" customHeight="true" outlineLevel="3">
@@ -5022,23 +5013,23 @@
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
       <c r="B430" s="17" t="s">
         <v>429</v>
       </c>
       <c r="C430" s="11" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="3">
       <c r="B431" s="17" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
@@ -5046,7 +5037,7 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>270</v>
+        <v>415</v>
       </c>
     </row>
     <row r="433" ht="11" customHeight="true" outlineLevel="3">
@@ -5054,7 +5045,7 @@
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>536</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="434" ht="11" customHeight="true" outlineLevel="3">
@@ -5062,39 +5053,39 @@
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
     </row>
     <row r="435" ht="11" customHeight="true" outlineLevel="3">
       <c r="B435" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C435" s="11" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C435" s="18" t="n">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
       <c r="B436" s="17" t="s">
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="437" ht="11" customHeight="true" outlineLevel="3">
       <c r="B437" s="17" t="s">
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
     </row>
     <row r="438" ht="22" customHeight="true" outlineLevel="3">
       <c r="B438" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="18" t="n">
-        <v>1436</v>
+      <c r="C438" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="439" ht="11" customHeight="true" outlineLevel="3">
@@ -5102,23 +5093,23 @@
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="440" ht="11" customHeight="true" outlineLevel="3">
       <c r="B440" s="17" t="s">
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="441" ht="11" customHeight="true" outlineLevel="3">
       <c r="B441" s="17" t="s">
         <v>440</v>
       </c>
       <c r="C441" s="11" t="n">
-        <v>4</v>
+        <v>785</v>
       </c>
     </row>
     <row r="442" ht="11" customHeight="true" outlineLevel="3">
@@ -5126,7 +5117,7 @@
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="443" ht="11" customHeight="true" outlineLevel="3">
@@ -5134,55 +5125,31 @@
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>900</v>
+        <v>222</v>
       </c>
     </row>
     <row r="444" ht="11" customHeight="true" outlineLevel="3">
       <c r="B444" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="11" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C444" s="18" t="n">
+        <v>6160</v>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="true" outlineLevel="3">
       <c r="B445" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="C445" s="18" t="n">
-        <v>1020</v>
+      <c r="C445" s="11" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="446" ht="11" customHeight="true" outlineLevel="3">
       <c r="B446" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="C446" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="447" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B447" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="448" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B448" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="18" t="n">
-        <v>6328</v>
-      </c>
-    </row>
-    <row r="449" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B449" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="11" t="n">
-        <v>888</v>
+      <c r="C446" s="18" t="n">
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.02.2026 7:55:13</t>
+    <t>Период: на 23.02.2026 11:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -92,6 +92,9 @@
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -110,9 +116,6 @@
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
@@ -194,6 +197,9 @@
     <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -323,45 +329,48 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -383,9 +392,6 @@
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
-  </si>
-  <si>
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -413,9 +419,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -425,6 +428,9 @@
     <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>KONAFETTO з молочною начинкою ВКФ 140г /15шт DE</t>
+  </si>
+  <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -446,15 +452,9 @@
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -479,9 +479,6 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -527,9 +524,6 @@
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 205г /12шт EU АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
@@ -563,15 +557,9 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -584,6 +572,9 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -605,18 +596,15 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -638,6 +626,9 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -671,6 +662,9 @@
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -683,6 +677,9 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -692,6 +689,9 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -848,12 +848,6 @@
     <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -965,6 +959,9 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -992,9 +989,15 @@
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP DE</t>
+  </si>
+  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP DE</t>
+  </si>
+  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1067,9 +1070,6 @@
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
-  </si>
-  <si>
     <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -1100,12 +1100,6 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1175,9 +1169,6 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -1187,6 +1178,12 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
@@ -1202,9 +1199,6 @@
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
@@ -1214,12 +1208,18 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1229,39 +1229,42 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -1289,6 +1292,9 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1304,27 +1310,33 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1340,7 +1352,13 @@
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
+  </si>
+  <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1604,7 +1622,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C446"/>
+  <dimension ref="C452"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1669,7 +1687,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>511</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1677,7 +1695,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>916750</v>
+        <v>977289</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1701,7 +1719,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>241183</v>
+        <v>267889</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
@@ -1709,7 +1727,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>35004</v>
+        <v>21453</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,15 +1735,15 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2347</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>1237</v>
+      <c r="C18" s="11" t="n">
+        <v>907</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1733,7 +1751,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>4193</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1741,7 +1759,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>108</v>
+        <v>724</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1756,16 +1774,16 @@
       <c r="B22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="18" t="n">
-        <v>3682</v>
+      <c r="C22" s="11" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>364</v>
+      <c r="C23" s="18" t="n">
+        <v>1484</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1773,7 +1791,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>5296</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1781,23 +1799,23 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>201</v>
+        <v>896</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>5064</v>
+      <c r="C26" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>36</v>
+      <c r="C27" s="18" t="n">
+        <v>2738</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1805,7 +1823,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1813,7 +1831,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>2826</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1821,7 +1839,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>812</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1829,7 +1847,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>39</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1837,7 +1855,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>2801</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1845,7 +1863,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>196</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1853,7 +1871,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>1322</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1861,23 +1879,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>4340</v>
-      </c>
-    </row>
-    <row r="36" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B36" s="16" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="36" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="12" t="n">
-        <v>108314</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B37" s="17" t="s">
+      <c r="C36" s="18" t="n">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B37" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>7498</v>
+      <c r="C37" s="12" t="n">
+        <v>145597</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1885,7 +1903,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="18" t="n">
-        <v>69457</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1893,7 +1911,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="18" t="n">
-        <v>2512</v>
+        <v>96921</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1901,7 +1919,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>4794</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1909,71 +1927,71 @@
         <v>40</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>14432</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>16</v>
+      <c r="C42" s="18" t="n">
+        <v>22427</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="18" t="n">
-        <v>1710</v>
+      <c r="C43" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>259</v>
+      <c r="C44" s="18" t="n">
+        <v>3292</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>2</v>
+      <c r="C45" s="18" t="n">
+        <v>5349</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="18" t="n">
-        <v>2462</v>
+      <c r="C46" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C47" s="18" t="n">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1981,63 +1999,63 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="18" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C51" s="11" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C52" s="18" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="true" outlineLevel="3">
       <c r="B53" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="18" t="n">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C54" s="11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
+      <c r="C55" s="18" t="n">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B56" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="11" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="56" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B56" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="12" t="n">
-        <v>34417</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B57" s="17" t="s">
+    <row r="57" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B57" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="18" t="n">
-        <v>3319</v>
+      <c r="C57" s="12" t="n">
+        <v>43065</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2045,7 +2063,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>694</v>
+        <v>886</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2053,15 +2071,15 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>149</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>36</v>
+      <c r="C60" s="18" t="n">
+        <v>1882</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,15 +2087,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>587</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>443</v>
+      <c r="C62" s="18" t="n">
+        <v>2735</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2085,15 +2103,15 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>604</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>449</v>
+      <c r="C64" s="18" t="n">
+        <v>3394</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2101,15 +2119,15 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>405</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>738</v>
+      <c r="C66" s="18" t="n">
+        <v>2452</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2117,15 +2135,15 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>605</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="18" t="n">
-        <v>1398</v>
+      <c r="C68" s="11" t="n">
+        <v>540</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2133,7 +2151,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>21</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2141,7 +2159,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>5040</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2149,23 +2167,23 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>894</v>
+      <c r="C72" s="18" t="n">
+        <v>4861</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="18" t="n">
-        <v>3366</v>
+      <c r="C73" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2173,15 +2191,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="true" outlineLevel="3">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>338</v>
+      <c r="C75" s="18" t="n">
+        <v>3084</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2189,23 +2207,23 @@
         <v>75</v>
       </c>
       <c r="C76" s="18" t="n">
-        <v>1651</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>256</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>209</v>
+      <c r="C78" s="18" t="n">
+        <v>2704</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2213,7 +2231,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>377</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2221,7 +2239,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>11168</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2229,31 +2247,31 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B82" s="16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B82" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="12" t="n">
-        <v>63448</v>
+      <c r="C82" s="18" t="n">
+        <v>5587</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="18" t="n">
-        <v>2645</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B84" s="17" t="s">
+      <c r="C83" s="11" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="18" t="n">
-        <v>6542</v>
+      <c r="C84" s="12" t="n">
+        <v>57774</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2261,7 +2279,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>3418</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2269,7 +2287,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>3777</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,7 +2295,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>9021</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2285,7 +2303,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>3177</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2293,7 +2311,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>7029</v>
+        <v>5589</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2301,7 +2319,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>3670</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,7 +2327,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>1276</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2317,7 +2335,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>4004</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2325,7 +2343,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>1123</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2333,15 +2351,15 @@
         <v>93</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>10321</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="18" t="n">
-        <v>3703</v>
+      <c r="C95" s="11" t="n">
+        <v>931</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2349,15 +2367,15 @@
         <v>95</v>
       </c>
       <c r="C96" s="18" t="n">
-        <v>1875</v>
+        <v>19059</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>247</v>
+      <c r="C97" s="18" t="n">
+        <v>1601</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
@@ -2365,95 +2383,95 @@
         <v>97</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B99" s="13" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B99" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="12" t="n">
-        <v>675516</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B100" s="16" t="s">
+      <c r="C99" s="11" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B100" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="12" t="n">
-        <v>117575</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B101" s="17" t="s">
+      <c r="C100" s="11" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B101" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="18" t="n">
-        <v>25214</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B102" s="17" t="s">
+      <c r="C101" s="12" t="n">
+        <v>709349</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B102" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="12" t="n">
+        <v>112847</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="17" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>21637</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+        <v>12669</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C104" s="18" t="n">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>24</v>
+      <c r="C105" s="18" t="n">
+        <v>2160</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C106" s="18" t="n">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="17" t="s">
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+        <v>10672</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="17" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="true" outlineLevel="3">
+        <v>12330</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>11</v>
+      <c r="C109" s="18" t="n">
+        <v>2040</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
@@ -2461,7 +2479,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="18" t="n">
-        <v>11884</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2469,23 +2487,23 @@
         <v>110</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>5320</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>900</v>
+      <c r="C112" s="18" t="n">
+        <v>3212</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="true" outlineLevel="3">
       <c r="B113" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>30</v>
+      <c r="C113" s="18" t="n">
+        <v>2520</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="true" outlineLevel="3">
@@ -2493,15 +2511,15 @@
         <v>113</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>23446</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="true" outlineLevel="3">
       <c r="B115" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="18" t="n">
-        <v>1500</v>
+      <c r="C115" s="11" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2509,7 +2527,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>21345</v>
+        <v>24359</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="true" outlineLevel="3">
@@ -2517,55 +2535,55 @@
         <v>116</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B118" s="16" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B118" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="12" t="n">
-        <v>7571</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C118" s="18" t="n">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="true" outlineLevel="3">
       <c r="B119" s="17" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="3">
+        <v>17284</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="true" outlineLevel="3">
       <c r="B120" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B121" s="17" t="s">
+      <c r="C120" s="18" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B121" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="11" t="n">
-        <v>540</v>
+      <c r="C121" s="12" t="n">
+        <v>10876</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>429</v>
+      <c r="C122" s="18" t="n">
+        <v>1202</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="18" t="n">
-        <v>1616</v>
+      <c r="C123" s="11" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,7 +2591,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>712</v>
+        <v>669</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2581,39 +2599,39 @@
         <v>124</v>
       </c>
       <c r="C125" s="18" t="n">
-        <v>2081</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>170</v>
+      <c r="C126" s="18" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>352</v>
+      <c r="C127" s="18" t="n">
+        <v>1471</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="129" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B129" s="16" t="s">
+      <c r="C128" s="18" t="n">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="129" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B129" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="12" t="n">
-        <v>175424</v>
+      <c r="C129" s="18" t="n">
+        <v>1366</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2621,15 +2639,15 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="131" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B131" s="17" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="131" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B131" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>934</v>
+      <c r="C131" s="12" t="n">
+        <v>161755</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2637,7 +2655,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>535</v>
+        <v>818</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,23 +2663,23 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>60</v>
+        <v>694</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="18" t="n">
-        <v>1223</v>
+      <c r="C134" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="18" t="n">
-        <v>1501</v>
+      <c r="C135" s="11" t="n">
+        <v>687</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2669,15 +2687,15 @@
         <v>135</v>
       </c>
       <c r="C136" s="18" t="n">
-        <v>66283</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="18" t="n">
-        <v>22782</v>
+      <c r="C137" s="11" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2685,7 +2703,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>16475</v>
+        <v>61323</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,15 +2711,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>36904</v>
+        <v>19457</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>235</v>
+      <c r="C140" s="18" t="n">
+        <v>17100</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +2727,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="18" t="n">
-        <v>3432</v>
+        <v>33604</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,7 +2735,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,7 +2743,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="18" t="n">
-        <v>1491</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,15 +2751,15 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>136</v>
+        <v>438</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="18" t="n">
-        <v>1446</v>
+      <c r="C145" s="11" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2749,15 +2767,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>759</v>
+        <v>709</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="18" t="n">
-        <v>2051</v>
+      <c r="C147" s="11" t="n">
+        <v>991</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2783,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>263</v>
+        <v>221</v>
       </c>
     </row>
     <row r="149" ht="22" customHeight="true" outlineLevel="3">
@@ -2773,15 +2791,15 @@
         <v>148</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>4433</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="18" t="n">
-        <v>1364</v>
+      <c r="C150" s="11" t="n">
+        <v>790</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,15 +2807,15 @@
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>2431</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>236</v>
+      <c r="C152" s="18" t="n">
+        <v>1891</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2805,23 +2823,23 @@
         <v>152</v>
       </c>
       <c r="C153" s="18" t="n">
-        <v>1241</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>6</v>
+      <c r="C154" s="18" t="n">
+        <v>2354</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
       <c r="B155" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="18" t="n">
-        <v>1592</v>
+      <c r="C155" s="11" t="n">
+        <v>490</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,79 +2847,79 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>243</v>
+        <v>760</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>634</v>
+      <c r="C157" s="18" t="n">
+        <v>1602</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="18" t="n">
-        <v>1156</v>
+      <c r="C158" s="11" t="n">
+        <v>922</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>563</v>
+      <c r="C159" s="18" t="n">
+        <v>3118</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="18" t="n">
-        <v>1682</v>
+      <c r="C160" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
       <c r="B161" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="11" t="n">
-        <v>6</v>
+      <c r="C161" s="18" t="n">
+        <v>1371</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="18" t="n">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B163" s="17" t="s">
+      <c r="C162" s="11" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B163" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="164" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B164" s="16" t="s">
+      <c r="C163" s="12" t="n">
+        <v>147670</v>
+      </c>
+    </row>
+    <row r="164" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B164" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="12" t="n">
-        <v>157091</v>
+      <c r="C164" s="18" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="18" t="n">
-        <v>2156</v>
+      <c r="C165" s="11" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,7 +2927,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>357</v>
+        <v>266</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2917,23 +2935,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>358</v>
+        <v>715</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>625</v>
+      <c r="C168" s="18" t="n">
+        <v>4162</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="18" t="n">
-        <v>2041</v>
+      <c r="C169" s="11" t="n">
+        <v>641</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2941,15 +2959,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>600</v>
+        <v>376</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>904</v>
+      <c r="C171" s="18" t="n">
+        <v>1286</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2957,7 +2975,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>541</v>
+        <v>816</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,31 +2983,31 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>881</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>64</v>
+      <c r="C174" s="18" t="n">
+        <v>4397</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="11" t="n">
-        <v>17</v>
+      <c r="C175" s="18" t="n">
+        <v>1242</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="18" t="n">
-        <v>4958</v>
+      <c r="C176" s="11" t="n">
+        <v>871</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2997,15 +3015,15 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>305</v>
+        <v>511</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="18" t="n">
-        <v>1084</v>
+      <c r="C178" s="11" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3013,7 +3031,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>155</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3021,31 +3039,31 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>776</v>
+        <v>332</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>870</v>
+      <c r="C181" s="18" t="n">
+        <v>1251</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="18" t="n">
-        <v>1033</v>
+      <c r="C182" s="11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>583</v>
+      <c r="C183" s="18" t="n">
+        <v>1431</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,7 +3071,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>183</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3061,15 +3079,15 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>685</v>
+        <v>864</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
       <c r="B186" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="11" t="n">
-        <v>15</v>
+      <c r="C186" s="18" t="n">
+        <v>1232</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3077,15 +3095,15 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>91</v>
+        <v>-77</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>946</v>
+      <c r="C188" s="18" t="n">
+        <v>3060</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3093,7 +3111,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="18" t="n">
-        <v>1374</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3101,31 +3119,31 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>247</v>
+        <v>89</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="18" t="n">
-        <v>3659</v>
-      </c>
-    </row>
-    <row r="192" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C191" s="11" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="true" outlineLevel="3">
       <c r="B192" s="17" t="s">
         <v>191</v>
       </c>
       <c r="C192" s="18" t="n">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+        <v>20736</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>125</v>
+      <c r="C193" s="18" t="n">
+        <v>7819</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3136,60 +3154,60 @@
         <v>522</v>
       </c>
     </row>
-    <row r="195" ht="22" customHeight="true" outlineLevel="3">
+    <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>22265</v>
+        <v>25007</v>
       </c>
     </row>
     <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="11" t="n">
-        <v>54</v>
+      <c r="C196" s="18" t="n">
+        <v>4101</v>
       </c>
     </row>
     <row r="197" ht="22" customHeight="true" outlineLevel="3">
       <c r="B197" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="18" t="n">
-        <v>9161</v>
+      <c r="C197" s="11" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="18" t="n">
-        <v>26215</v>
+      <c r="C198" s="11" t="n">
+        <v>577</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C199" s="18" t="n">
+        <v>15017</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="18" t="n">
-        <v>4761</v>
-      </c>
-    </row>
-    <row r="201" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C200" s="11" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>298</v>
+        <v>86</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3197,15 +3215,15 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>611</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="18" t="n">
-        <v>16187</v>
+      <c r="C203" s="11" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,7 +3231,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>861</v>
+        <v>556</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3221,7 +3239,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>86</v>
+        <v>608</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,7 +3247,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>577</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3237,7 +3255,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>929</v>
+        <v>430</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3245,7 +3263,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="18" t="n">
-        <v>1009</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3253,15 +3271,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>773</v>
+        <v>962</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>26</v>
+      <c r="C210" s="18" t="n">
+        <v>1259</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3269,63 +3287,63 @@
         <v>210</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>2564</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="18" t="n">
-        <v>1577</v>
+      <c r="C212" s="11" t="n">
+        <v>701</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="18" t="n">
-        <v>1292</v>
+      <c r="C213" s="11" t="n">
+        <v>668</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="18" t="n">
-        <v>1547</v>
+      <c r="C214" s="11" t="n">
+        <v>656</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="18" t="n">
-        <v>1068</v>
+      <c r="C215" s="11" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>850</v>
+      <c r="C216" s="18" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>799</v>
+      <c r="C217" s="18" t="n">
+        <v>2238</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="18" t="n">
-        <v>2064</v>
+      <c r="C218" s="11" t="n">
+        <v>785</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,7 +3351,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>2273</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3341,7 +3359,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>828</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3349,7 +3367,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>327</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3357,23 +3375,23 @@
         <v>221</v>
       </c>
       <c r="C222" s="18" t="n">
-        <v>1057</v>
+        <v>17231</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="18" t="n">
-        <v>17708</v>
+      <c r="C223" s="11" t="n">
+        <v>382</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
       <c r="B224" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="11" t="n">
-        <v>407</v>
+      <c r="C224" s="18" t="n">
+        <v>1015</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3381,7 +3399,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>609</v>
+        <v>529</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3389,7 +3407,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>1889</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3397,7 +3415,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="18" t="n">
-        <v>2274</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3413,15 +3431,15 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="18" t="n">
-        <v>1539</v>
+      <c r="C230" s="11" t="n">
+        <v>748</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3429,7 +3447,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>445</v>
+        <v>395</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3437,7 +3455,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>3918</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,7 +3463,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="2">
@@ -3453,7 +3471,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="12" t="n">
-        <v>53483</v>
+        <v>75273</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3461,7 +3479,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>1009</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3469,7 +3487,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>428</v>
+        <v>462</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,7 +3495,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="18" t="n">
-        <v>1275</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3485,23 +3503,23 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>369</v>
+      <c r="C239" s="18" t="n">
+        <v>1493</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="11" t="n">
-        <v>769</v>
+      <c r="C240" s="18" t="n">
+        <v>1339</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3509,7 +3527,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="18" t="n">
-        <v>5334</v>
+        <v>6777</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3517,7 +3535,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3533,7 +3551,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>457</v>
+        <v>398</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3541,7 +3559,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3549,7 +3567,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>706</v>
+        <v>974</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3557,7 +3575,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>400</v>
+        <v>318</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3565,7 +3583,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="18" t="n">
-        <v>1340</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3573,7 +3591,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="18" t="n">
-        <v>1894</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3581,23 +3599,23 @@
         <v>249</v>
       </c>
       <c r="C250" s="18" t="n">
-        <v>1626</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>723</v>
+      <c r="C251" s="18" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>719</v>
+      <c r="C252" s="18" t="n">
+        <v>1565</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,15 +3623,15 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>571</v>
+        <v>321</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="18" t="n">
-        <v>1471</v>
+      <c r="C254" s="11" t="n">
+        <v>981</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3621,7 +3639,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="18" t="n">
-        <v>1265</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3629,7 +3647,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>678</v>
+        <v>434</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3637,7 +3655,7 @@
         <v>256</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>1181</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3645,7 +3663,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="18" t="n">
-        <v>2687</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3653,7 +3671,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="18" t="n">
-        <v>3283</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="18" t="n">
-        <v>1735</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3669,7 +3687,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>2396</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3677,7 +3695,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>2629</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,7 +3703,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>1491</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3693,7 +3711,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>1349</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3701,7 +3719,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>2704</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3709,7 +3727,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>1643</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3717,7 +3735,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="18" t="n">
-        <v>3356</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3725,7 +3743,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="18" t="n">
-        <v>1696</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3733,7 +3751,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="18" t="n">
-        <v>4500</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3741,7 +3759,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>1223</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="2">
@@ -3749,7 +3767,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="12" t="n">
-        <v>5095</v>
+        <v>5857</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3757,7 +3775,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>35</v>
+        <v>272</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3765,7 +3783,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3773,7 +3791,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3781,7 +3799,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>165</v>
+        <v>498</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3789,7 +3807,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3797,7 +3815,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>5</v>
+        <v>384</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3805,7 +3823,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>418</v>
+        <v>16</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3813,7 +3831,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>390</v>
+        <v>194</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,7 +3839,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>49</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3829,7 +3847,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>437</v>
+        <v>569</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3837,7 +3855,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>286</v>
+        <v>661</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3845,7 +3863,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>555</v>
+        <v>345</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3853,7 +3871,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>829</v>
+        <v>258</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3861,7 +3879,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>345</v>
+        <v>60</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3869,7 +3887,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>312</v>
+        <v>455</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3877,7 +3895,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3885,7 +3903,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>429</v>
+        <v>960</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3893,7 +3911,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3901,7 +3919,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>142</v>
+        <v>557</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3909,7 +3927,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3917,15 +3935,15 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B293" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B293" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="11" t="n">
-        <v>7</v>
+      <c r="C293" s="12" t="n">
+        <v>63144</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3933,15 +3951,15 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B295" s="16" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B295" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="12" t="n">
-        <v>53377</v>
+      <c r="C295" s="11" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -3949,7 +3967,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>485</v>
+        <v>340</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3957,7 +3975,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3965,7 +3983,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>409</v>
+        <v>269</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3973,7 +3991,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3981,7 +3999,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>490</v>
+        <v>775</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +4007,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>349</v>
+        <v>604</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,15 +4015,15 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="17" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>129</v>
+        <v>215</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4013,15 +4031,15 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="17" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>365</v>
+        <v>188</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4029,15 +4047,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>73</v>
+        <v>657</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>292</v>
+      <c r="C307" s="18" t="n">
+        <v>1547</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4045,31 +4063,31 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="18" t="n">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C309" s="11" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="18" t="n">
-        <v>1044</v>
+      <c r="C310" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="11" t="n">
-        <v>982</v>
+      <c r="C311" s="18" t="n">
+        <v>1266</v>
       </c>
     </row>
     <row r="312" ht="22" customHeight="true" outlineLevel="3">
@@ -4077,15 +4095,15 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="11" t="n">
-        <v>464</v>
+      <c r="C313" s="18" t="n">
+        <v>1282</v>
       </c>
     </row>
     <row r="314" ht="22" customHeight="true" outlineLevel="3">
@@ -4093,7 +4111,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>108</v>
+        <v>186</v>
       </c>
     </row>
     <row r="315" ht="22" customHeight="true" outlineLevel="3">
@@ -4101,7 +4119,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>400</v>
+        <v>151</v>
       </c>
     </row>
     <row r="316" ht="22" customHeight="true" outlineLevel="3">
@@ -4109,15 +4127,15 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="317" ht="22" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="17" t="s">
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>92</v>
+        <v>657</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4125,7 +4143,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>354</v>
+        <v>52</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4133,7 +4151,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>442</v>
+        <v>928</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4141,15 +4159,15 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>386</v>
+        <v>148</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>275</v>
+      <c r="C321" s="18" t="n">
+        <v>2601</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -4157,15 +4175,15 @@
         <v>321</v>
       </c>
       <c r="C322" s="18" t="n">
-        <v>4258</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="18" t="n">
-        <v>2451</v>
+      <c r="C323" s="11" t="n">
+        <v>765</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4173,15 +4191,15 @@
         <v>323</v>
       </c>
       <c r="C324" s="18" t="n">
-        <v>2039</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="18" t="n">
-        <v>1322</v>
+      <c r="C325" s="11" t="n">
+        <v>741</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4189,23 +4207,23 @@
         <v>325</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>4238</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="11" t="n">
-        <v>7</v>
+      <c r="C327" s="18" t="n">
+        <v>4702</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="18" t="n">
-        <v>3750</v>
+      <c r="C328" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4213,7 +4231,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="18" t="n">
-        <v>17195</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4221,47 +4239,47 @@
         <v>329</v>
       </c>
       <c r="C330" s="18" t="n">
-        <v>1195</v>
+        <v>21479</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>194</v>
+      <c r="C331" s="18" t="n">
+        <v>1151</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="C332" s="18" t="n">
-        <v>5687</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B333" s="16" t="s">
+      <c r="C332" s="11" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="12" t="n">
-        <v>60967</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="17" t="s">
+      <c r="C333" s="18" t="n">
+        <v>7716</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B334" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="18" t="n">
-        <v>2253</v>
+      <c r="C334" s="12" t="n">
+        <v>69209</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>382</v>
+      <c r="C335" s="18" t="n">
+        <v>1745</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4269,31 +4287,31 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>376</v>
+      <c r="C337" s="18" t="n">
+        <v>1507</v>
       </c>
     </row>
     <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="C338" s="18" t="n">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C338" s="11" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>839</v>
+      <c r="C339" s="18" t="n">
+        <v>1183</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4301,7 +4319,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4309,23 +4327,23 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="18" t="n">
-        <v>1655</v>
+      <c r="C342" s="11" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="11" t="n">
-        <v>830</v>
+      <c r="C343" s="18" t="n">
+        <v>2786</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4333,15 +4351,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>678</v>
+        <v>708</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>297</v>
+      <c r="C345" s="18" t="n">
+        <v>1092</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4349,7 +4367,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>78</v>
+        <v>436</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4357,7 +4375,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>703</v>
+        <v>78</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4365,7 +4383,7 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>295</v>
+        <v>754</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4373,15 +4391,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>427</v>
+        <v>295</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>17</v>
+      <c r="C350" s="18" t="n">
+        <v>1143</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4389,15 +4407,15 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>397</v>
+        <v>703</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="18" t="n">
-        <v>1297</v>
+      <c r="C352" s="11" t="n">
+        <v>926</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4405,7 +4423,7 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>498</v>
+        <v>442</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4413,7 +4431,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="18" t="n">
-        <v>1061</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4421,7 +4439,7 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>491</v>
+        <v>764</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
@@ -4429,7 +4447,7 @@
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>828</v>
+        <v>784</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4437,7 +4455,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4445,7 +4463,7 @@
         <v>357</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>3324</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4453,7 +4471,7 @@
         <v>358</v>
       </c>
       <c r="C359" s="18" t="n">
-        <v>1002</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4461,18 +4479,18 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="17" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="17" t="s">
         <v>361</v>
       </c>
@@ -4480,12 +4498,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+    <row r="363" ht="22" customHeight="true" outlineLevel="3">
       <c r="B363" s="17" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>231</v>
+        <v>38</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4493,7 +4511,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>245</v>
+        <v>164</v>
       </c>
     </row>
     <row r="365" ht="22" customHeight="true" outlineLevel="3">
@@ -4501,7 +4519,7 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>124</v>
+        <v>660</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
@@ -4509,7 +4527,7 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>257</v>
+        <v>186</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="true" outlineLevel="3">
@@ -4517,7 +4535,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>754</v>
+        <v>843</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4525,7 +4543,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4533,47 +4551,47 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>818</v>
+        <v>745</v>
       </c>
     </row>
     <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="11" t="n">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C370" s="18" t="n">
+        <v>11999</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>559</v>
+        <v>450</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="18" t="n">
-        <v>7892</v>
+      <c r="C372" s="11" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="11" t="n">
-        <v>480</v>
+      <c r="C373" s="18" t="n">
+        <v>17694</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C374" s="11" t="n">
-        <v>521</v>
+      <c r="C374" s="18" t="n">
+        <v>7860</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4581,31 +4599,31 @@
         <v>374</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>18805</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
       <c r="B376" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="18" t="n">
-        <v>5837</v>
+      <c r="C376" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="18" t="n">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B378" s="17" t="s">
+      <c r="C377" s="11" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B378" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>93</v>
+      <c r="C378" s="14" t="n">
+        <v>880</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
@@ -4613,15 +4631,15 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B380" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B380" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="14" t="n">
-        <v>253</v>
+      <c r="C380" s="11" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
@@ -4629,7 +4647,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>37</v>
+        <v>295</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4637,15 +4655,15 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B383" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B383" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="11" t="n">
-        <v>43</v>
+      <c r="C383" s="12" t="n">
+        <v>61838</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4653,39 +4671,39 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B385" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B385" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="12" t="n">
-        <v>44680</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C385" s="11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C386" s="18" t="n">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
       <c r="B387" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="C387" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C387" s="18" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="17" t="s">
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
     </row>
     <row r="389" ht="22" customHeight="true" outlineLevel="3">
@@ -4693,15 +4711,15 @@
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="11" t="n">
-        <v>169</v>
+      <c r="C390" s="18" t="n">
+        <v>3128</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4709,55 +4727,55 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="392" ht="11" customHeight="true" outlineLevel="3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
       <c r="B392" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="C392" s="11" t="n">
-        <v>44</v>
+      <c r="C392" s="18" t="n">
+        <v>5233</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
       <c r="B393" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="18" t="n">
-        <v>3896</v>
-      </c>
-    </row>
-    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C393" s="11" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
       <c r="B395" s="17" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>51</v>
+        <v>231</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
       <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="11" t="n">
-        <v>48</v>
+      <c r="C396" s="18" t="n">
+        <v>2624</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="11" t="n">
-        <v>59</v>
+      <c r="C397" s="18" t="n">
+        <v>1760</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4765,15 +4783,15 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
       <c r="B399" s="17" t="s">
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>251</v>
+        <v>36</v>
       </c>
     </row>
     <row r="400" ht="22" customHeight="true" outlineLevel="3">
@@ -4781,7 +4799,7 @@
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>587</v>
+        <v>28</v>
       </c>
     </row>
     <row r="401" ht="22" customHeight="true" outlineLevel="3">
@@ -4789,15 +4807,15 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>42</v>
+        <v>168</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="C402" s="18" t="n">
-        <v>4214</v>
+      <c r="C402" s="11" t="n">
+        <v>961</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4813,23 +4831,23 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="18" t="n">
-        <v>3915</v>
+      <c r="C405" s="11" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="18" t="n">
-        <v>4023</v>
+      <c r="C406" s="11" t="n">
+        <v>458</v>
       </c>
     </row>
     <row r="407" ht="22" customHeight="true" outlineLevel="3">
@@ -4837,15 +4855,15 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>74</v>
+        <v>528</v>
       </c>
     </row>
     <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="C408" s="11" t="n">
-        <v>36</v>
+      <c r="C408" s="18" t="n">
+        <v>2177</v>
       </c>
     </row>
     <row r="409" ht="22" customHeight="true" outlineLevel="3">
@@ -4853,7 +4871,7 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>107</v>
+        <v>38</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="true" outlineLevel="3">
@@ -4861,7 +4879,7 @@
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="411" ht="22" customHeight="true" outlineLevel="3">
@@ -4869,7 +4887,7 @@
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>18</v>
+        <v>354</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
@@ -4877,7 +4895,7 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>35</v>
+        <v>360</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="true" outlineLevel="3">
@@ -4885,15 +4903,15 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="11" t="n">
-        <v>543</v>
+      <c r="C414" s="18" t="n">
+        <v>3797</v>
       </c>
     </row>
     <row r="415" ht="22" customHeight="true" outlineLevel="3">
@@ -4901,7 +4919,7 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>198</v>
+        <v>726</v>
       </c>
     </row>
     <row r="416" ht="22" customHeight="true" outlineLevel="3">
@@ -4909,7 +4927,7 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="417" ht="22" customHeight="true" outlineLevel="3">
@@ -4917,15 +4935,15 @@
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
       <c r="B418" s="17" t="s">
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>209</v>
+        <v>26</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -4933,15 +4951,15 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
       <c r="B420" s="17" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>66</v>
+        <v>922</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="true" outlineLevel="3">
@@ -4949,7 +4967,7 @@
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="422" ht="22" customHeight="true" outlineLevel="3">
@@ -4957,15 +4975,15 @@
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="true" outlineLevel="3">
       <c r="B423" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="C423" s="11" t="n">
-        <v>20</v>
+      <c r="C423" s="18" t="n">
+        <v>1416</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="true" outlineLevel="3">
@@ -4973,7 +4991,7 @@
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="425" ht="22" customHeight="true" outlineLevel="3">
@@ -4981,15 +4999,15 @@
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>140</v>
+        <v>72</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="C426" s="18" t="n">
-        <v>4489</v>
+      <c r="C426" s="11" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="427" ht="22" customHeight="true" outlineLevel="3">
@@ -4997,39 +5015,39 @@
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C428" s="18" t="n">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="17" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="430" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
       <c r="B430" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="C430" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C430" s="18" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
       <c r="B431" s="17" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>195</v>
+        <v>500</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
@@ -5037,39 +5055,39 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
       <c r="B433" s="17" t="s">
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434" ht="11" customHeight="true" outlineLevel="3">
       <c r="B434" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="C434" s="11" t="n">
-        <v>241</v>
+      <c r="C434" s="18" t="n">
+        <v>1666</v>
       </c>
     </row>
     <row r="435" ht="11" customHeight="true" outlineLevel="3">
       <c r="B435" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C435" s="18" t="n">
-        <v>5067</v>
-      </c>
-    </row>
-    <row r="436" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C435" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="436" ht="11" customHeight="true" outlineLevel="3">
       <c r="B436" s="17" t="s">
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>801</v>
+        <v>32</v>
       </c>
     </row>
     <row r="437" ht="11" customHeight="true" outlineLevel="3">
@@ -5077,47 +5095,47 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="438" ht="11" customHeight="true" outlineLevel="3">
       <c r="B438" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="439" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C438" s="18" t="n">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
       <c r="B439" s="17" t="s">
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="440" ht="11" customHeight="true" outlineLevel="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
       <c r="B440" s="17" t="s">
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>708</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441" ht="11" customHeight="true" outlineLevel="3">
       <c r="B441" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="C441" s="11" t="n">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C441" s="18" t="n">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
       <c r="B442" s="17" t="s">
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="443" ht="11" customHeight="true" outlineLevel="3">
@@ -5125,7 +5143,7 @@
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>222</v>
+        <v>45</v>
       </c>
     </row>
     <row r="444" ht="11" customHeight="true" outlineLevel="3">
@@ -5133,23 +5151,71 @@
         <v>443</v>
       </c>
       <c r="C444" s="18" t="n">
-        <v>6160</v>
-      </c>
-    </row>
-    <row r="445" ht="22" customHeight="true" outlineLevel="3">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
       <c r="B445" s="17" t="s">
         <v>444</v>
       </c>
       <c r="C445" s="11" t="n">
-        <v>888</v>
+        <v>624</v>
       </c>
     </row>
     <row r="446" ht="11" customHeight="true" outlineLevel="3">
       <c r="B446" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="C446" s="18" t="n">
-        <v>3408</v>
+      <c r="C446" s="11" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="447" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B447" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="11" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B448" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="18" t="n">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="449" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B449" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B450" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="18" t="n">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="11" t="n">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B452" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="18" t="n">
+        <v>1828</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceDP.xlsx
+++ b/client/public/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.02.2026 11:15:12</t>
+    <t>Период: на 19.03.2026 20:05:30</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -77,24 +77,18 @@
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -104,30 +98,30 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -137,10 +131,13 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Ванільний цукор УБ 35г /36шт</t>
   </si>
   <si>
-    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
+    <t>Глазур декоративна біла УБ 75г /40шт</t>
   </si>
   <si>
     <t>Желатин УБ 25г /42шт</t>
@@ -155,6 +152,27 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Посипка декоративна в асортименті УБ 7г /54шт</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
@@ -200,15 +218,9 @@
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
@@ -242,9 +254,15 @@
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
+    <t>Суміш зелені УБ 10г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -305,21 +323,24 @@
     <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
-  </si>
-  <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
+    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>РОШЕН</t>
   </si>
   <si>
@@ -335,9 +356,15 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 39г /180шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
@@ -347,9 +374,21 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
   </si>
   <si>
@@ -362,7 +401,10 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
@@ -374,24 +416,30 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
   </si>
   <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
+  </si>
+  <si>
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -416,7 +464,7 @@
     <t>Konafetto cocoa з начинкою крем-какао ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
     <t>Konafetto з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
@@ -452,9 +500,15 @@
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -479,19 +533,25 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао-молоко ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт</t>
+    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
@@ -512,6 +572,9 @@
     <t>Beri РЦ 180г /12шт</t>
   </si>
   <si>
+    <t>Beri РЦ 180г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Bonny-Fruit літній мікс ВКФ 200г /18шт /</t>
   </si>
   <si>
@@ -524,6 +587,9 @@
     <t>Korivka Roshen 205г/12</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 205г /12шт EU АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Milky Splash РЦ 150г /12пак</t>
   </si>
   <si>
@@ -539,6 +605,9 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -563,7 +632,7 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
@@ -572,12 +641,15 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
@@ -590,6 +662,9 @@
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Pandas ВКФ 65г /11шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
@@ -605,12 +680,12 @@
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
@@ -620,34 +695,34 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
@@ -656,28 +731,31 @@
     <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
@@ -689,9 +767,6 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -731,9 +806,6 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>CoffeeLike ВКФ 1кг /7пак /</t>
-  </si>
-  <si>
     <t>CoffeeLike КрКФ 1кг /7пак /</t>
   </si>
   <si>
@@ -836,18 +908,21 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
     <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -860,6 +935,9 @@
     <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
@@ -884,12 +962,15 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 352г /7шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Київ вечірній ККФ 176г /7шт</t>
   </si>
   <si>
@@ -929,6 +1010,9 @@
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
+    <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -944,6 +1028,9 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт DE</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -983,24 +1070,30 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP DE</t>
   </si>
   <si>
-    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
-  </si>
-  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP DE</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
@@ -1049,24 +1142,33 @@
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>KONAFETTO blanc ВКФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -1097,6 +1199,9 @@
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1106,9 +1211,6 @@
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1133,15 +1235,15 @@
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ 1</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
+    <t>Сливки-Ленивки ВКФ 1кг АКЦІЯ</t>
+  </si>
+  <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1151,6 +1253,9 @@
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1169,6 +1274,12 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -1181,27 +1292,45 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1220,7 +1349,7 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
@@ -1229,34 +1358,55 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
@@ -1265,13 +1415,19 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1298,24 +1454,36 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1328,7 +1496,13 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
@@ -1337,13 +1511,16 @@
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
@@ -1352,6 +1529,9 @@
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1364,6 +1544,9 @@
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
   </si>
   <si>
@@ -1374,6 +1557,24 @@
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
+  </si>
+  <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 40г /24шт</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 60г /20шт</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1603,6 +1804,12 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1622,7 +1829,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C452"/>
+  <dimension ref="C519"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1687,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>628</v>
+        <v>879</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1695,7 +1902,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>977289</v>
+        <v>1428087</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1719,7 +1926,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>267889</v>
+        <v>459858</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="2">
@@ -1727,7 +1934,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>21453</v>
+        <v>70699</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1735,7 +1942,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>1727</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1743,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>907</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1751,7 +1958,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2681</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1759,23 +1966,23 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>724</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
       <c r="B21" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>4</v>
+      <c r="C21" s="18" t="n">
+        <v>14415</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>206</v>
+      <c r="C22" s="18" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1783,23 +1990,23 @@
         <v>22</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1484</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>2863</v>
+      <c r="C24" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>896</v>
+      <c r="C25" s="18" t="n">
+        <v>9874</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1807,23 +2014,23 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="18" t="n">
-        <v>2738</v>
+      <c r="C27" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>36</v>
+      <c r="C28" s="18" t="n">
+        <v>4605</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1831,7 +2038,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1008</v>
+        <v>13199</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1839,31 +2046,31 @@
         <v>29</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>155</v>
+      <c r="C31" s="18" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>1372</v>
+      <c r="C32" s="11" t="n">
+        <v>375</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>292</v>
+      <c r="C33" s="18" t="n">
+        <v>1801</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1871,15 +2078,15 @@
         <v>33</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="35" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B35" s="17" t="s">
+        <v>13760</v>
+      </c>
+    </row>
+    <row r="35" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B35" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="18" t="n">
-        <v>1002</v>
+      <c r="C35" s="12" t="n">
+        <v>235714</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1887,31 +2094,31 @@
         <v>35</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B37" s="16" t="s">
+        <v>17341</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="12" t="n">
-        <v>145597</v>
+      <c r="C37" s="18" t="n">
+        <v>44481</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>4339</v>
+      <c r="C38" s="11" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="18" t="n">
-        <v>96921</v>
+      <c r="C39" s="11" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1919,7 +2126,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>2213</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1927,7 +2134,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>4794</v>
+        <v>17346</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
@@ -1935,15 +2142,15 @@
         <v>41</v>
       </c>
       <c r="C42" s="18" t="n">
-        <v>22427</v>
+        <v>8396</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>16</v>
+      <c r="C43" s="18" t="n">
+        <v>8321</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1951,7 +2158,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>3292</v>
+        <v>12988</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1959,15 +2166,15 @@
         <v>44</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>5349</v>
+        <v>23455</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>7</v>
+      <c r="C46" s="18" t="n">
+        <v>25070</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1975,55 +2182,55 @@
         <v>46</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>2075</v>
+        <v>18424</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C48" s="18" t="n">
+        <v>19130</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>26</v>
+      <c r="C49" s="18" t="n">
+        <v>13925</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>140</v>
+      <c r="C50" s="18" t="n">
+        <v>15390</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>148</v>
+      <c r="C51" s="18" t="n">
+        <v>1728</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="18" t="n">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C52" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>44</v>
+        <v>954</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2031,31 +2238,31 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="true" outlineLevel="3">
       <c r="B55" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="18" t="n">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C55" s="11" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true" outlineLevel="3">
       <c r="B56" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B57" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B57" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="12" t="n">
-        <v>43065</v>
+      <c r="C57" s="11" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2063,23 +2270,23 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="59" ht="11" customHeight="true" outlineLevel="3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="true" outlineLevel="3">
       <c r="B59" s="17" t="s">
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>655</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="18" t="n">
-        <v>1882</v>
+      <c r="C60" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2087,23 +2294,23 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" ht="11" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="true" outlineLevel="3">
       <c r="B62" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="18" t="n">
-        <v>2735</v>
-      </c>
-    </row>
-    <row r="63" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B63" s="17" t="s">
+      <c r="C62" s="11" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B63" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>502</v>
+      <c r="C63" s="12" t="n">
+        <v>62199</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2111,7 +2318,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>3394</v>
+        <v>5013</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2119,7 +2326,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>554</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2127,31 +2334,31 @@
         <v>65</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>2452</v>
+        <v>8094</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>359</v>
+      <c r="C67" s="18" t="n">
+        <v>3097</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>540</v>
+      <c r="C68" s="18" t="n">
+        <v>2135</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>560</v>
+      <c r="C69" s="18" t="n">
+        <v>1872</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2159,7 +2366,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>3877</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2167,7 +2374,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>19</v>
+        <v>519</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2175,7 +2382,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>4861</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2183,7 +2390,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2191,15 +2398,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>1735</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="18" t="n">
-        <v>3084</v>
+      <c r="C75" s="11" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2207,15 +2414,15 @@
         <v>75</v>
       </c>
       <c r="C76" s="18" t="n">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="true" outlineLevel="3">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>336</v>
+      <c r="C77" s="18" t="n">
+        <v>1828</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2223,15 +2430,15 @@
         <v>77</v>
       </c>
       <c r="C78" s="18" t="n">
-        <v>2704</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>256</v>
+      <c r="C79" s="18" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2239,7 +2446,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>3489</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2247,7 +2454,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>347</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2255,23 +2462,23 @@
         <v>81</v>
       </c>
       <c r="C82" s="18" t="n">
-        <v>5587</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="16" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B84" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>57774</v>
+      <c r="C84" s="18" t="n">
+        <v>3092</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2279,7 +2486,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>1363</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2287,15 +2494,15 @@
         <v>85</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>5899</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="18" t="n">
-        <v>2388</v>
+      <c r="C87" s="11" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2303,23 +2510,23 @@
         <v>87</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>2332</v>
+        <v>12143</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="18" t="n">
-        <v>5589</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B90" s="17" t="s">
+      <c r="C89" s="11" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B90" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="18" t="n">
-        <v>1739</v>
+      <c r="C90" s="12" t="n">
+        <v>91246</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2327,7 +2534,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>5846</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2335,7 +2542,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>2269</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2343,7 +2550,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>3360</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2351,15 +2558,15 @@
         <v>93</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>2265</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>931</v>
+      <c r="C95" s="18" t="n">
+        <v>5643</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
@@ -2367,7 +2574,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="18" t="n">
-        <v>19059</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="97" ht="11" customHeight="true" outlineLevel="3">
@@ -2375,7 +2582,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>1601</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
@@ -2383,103 +2590,103 @@
         <v>97</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>2283</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>79</v>
+      <c r="C99" s="18" t="n">
+        <v>4068</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B101" s="13" t="s">
+      <c r="C100" s="18" t="n">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B101" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="12" t="n">
-        <v>709349</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B102" s="16" t="s">
+      <c r="C101" s="18" t="n">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B102" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="12" t="n">
-        <v>112847</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C102" s="18" t="n">
+        <v>15985</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="17" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>12669</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
+        <v>5308</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
       <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="18" t="n">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="17" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="18" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+        <v>13430</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="18" t="n">
-        <v>2110</v>
+      <c r="C106" s="11" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="18" t="n">
-        <v>10672</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B108" s="17" t="s">
+      <c r="C107" s="11" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B108" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="18" t="n">
-        <v>12330</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B109" s="17" t="s">
+      <c r="C108" s="12" t="n">
+        <v>968178</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B109" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="18" t="n">
-        <v>2040</v>
+      <c r="C109" s="12" t="n">
+        <v>131084</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="18" t="n">
-        <v>1170</v>
+      <c r="C110" s="11" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2487,7 +2694,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>6601</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
@@ -2495,7 +2702,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>3212</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="true" outlineLevel="3">
@@ -2503,207 +2710,207 @@
         <v>112</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>2520</v>
+        <v>7610</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="true" outlineLevel="3">
       <c r="B114" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="18" t="n">
-        <v>5900</v>
+      <c r="C114" s="11" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="true" outlineLevel="3">
       <c r="B115" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C115" s="18" t="n">
+        <v>3274</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="17" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>24359</v>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="true" outlineLevel="3">
+        <v>21960</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="17" t="s">
         <v>116</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="true" outlineLevel="3">
+        <v>11940</v>
+      </c>
+    </row>
+    <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="17" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>3210</v>
-      </c>
-    </row>
-    <row r="119" ht="22" customHeight="true" outlineLevel="3">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="17" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>17284</v>
+        <v>6681</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="true" outlineLevel="3">
       <c r="B120" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="18" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B121" s="16" t="s">
+      <c r="C120" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B121" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="12" t="n">
-        <v>10876</v>
-      </c>
-    </row>
-    <row r="122" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C121" s="18" t="n">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="true" outlineLevel="3">
       <c r="B122" s="17" t="s">
         <v>121</v>
       </c>
       <c r="C122" s="18" t="n">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="3">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C123" s="18" t="n">
+        <v>10470</v>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="true" outlineLevel="3">
       <c r="B124" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="125" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C124" s="18" t="n">
+        <v>4922</v>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="true" outlineLevel="3">
       <c r="B125" s="17" t="s">
         <v>124</v>
       </c>
       <c r="C125" s="18" t="n">
-        <v>2386</v>
-      </c>
-    </row>
-    <row r="126" ht="11" customHeight="true" outlineLevel="3">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="true" outlineLevel="3">
       <c r="B126" s="17" t="s">
         <v>125</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="127" ht="11" customHeight="true" outlineLevel="3">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="true" outlineLevel="3">
       <c r="B127" s="17" t="s">
         <v>126</v>
       </c>
       <c r="C127" s="18" t="n">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="128" ht="11" customHeight="true" outlineLevel="3">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="true" outlineLevel="3">
       <c r="B128" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="18" t="n">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="129" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C128" s="11" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="true" outlineLevel="3">
       <c r="B129" s="17" t="s">
         <v>128</v>
       </c>
       <c r="C129" s="18" t="n">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="130" ht="11" customHeight="true" outlineLevel="3">
+        <v>11058</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="true" outlineLevel="3">
       <c r="B130" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="131" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B131" s="16" t="s">
+      <c r="C130" s="18" t="n">
+        <v>13201</v>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B131" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="12" t="n">
-        <v>161755</v>
-      </c>
-    </row>
-    <row r="132" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C131" s="18" t="n">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="true" outlineLevel="3">
       <c r="B132" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="133" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C132" s="18" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="true" outlineLevel="3">
       <c r="B133" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C133" s="18" t="n">
+        <v>6694</v>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="true" outlineLevel="3">
       <c r="B134" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="135" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C134" s="18" t="n">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="true" outlineLevel="3">
       <c r="B135" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="136" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C135" s="18" t="n">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="true" outlineLevel="3">
       <c r="B136" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="18" t="n">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="137" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B137" s="17" t="s">
+      <c r="C136" s="11" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="137" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B137" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>720</v>
+      <c r="C137" s="12" t="n">
+        <v>10143</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
       <c r="B138" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="18" t="n">
-        <v>61323</v>
+      <c r="C138" s="11" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2711,7 +2918,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>19457</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2719,23 +2926,23 @@
         <v>139</v>
       </c>
       <c r="C140" s="18" t="n">
-        <v>17100</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="18" t="n">
-        <v>33604</v>
+      <c r="C141" s="11" t="n">
+        <v>954</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>100</v>
+      <c r="C142" s="18" t="n">
+        <v>1969</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2743,7 +2950,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="18" t="n">
-        <v>1590</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2751,7 +2958,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>438</v>
+        <v>623</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2759,7 +2966,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>92</v>
+        <v>281</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2767,15 +2974,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="147" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B147" s="17" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="147" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B147" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>991</v>
+      <c r="C147" s="12" t="n">
+        <v>139297</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2783,15 +2990,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="149" ht="22" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="17" t="s">
         <v>148</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>2655</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2799,7 +3006,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>790</v>
+        <v>50</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2807,7 +3014,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>1508</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2815,15 +3022,15 @@
         <v>151</v>
       </c>
       <c r="C152" s="18" t="n">
-        <v>1891</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="18" t="n">
-        <v>2366</v>
+      <c r="C153" s="11" t="n">
+        <v>651</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2831,23 +3038,23 @@
         <v>153</v>
       </c>
       <c r="C154" s="18" t="n">
-        <v>2354</v>
+        <v>54675</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
       <c r="B155" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>490</v>
+      <c r="C155" s="18" t="n">
+        <v>7932</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
       <c r="B156" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="11" t="n">
-        <v>760</v>
+      <c r="C156" s="18" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2855,7 +3062,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="18" t="n">
-        <v>1602</v>
+        <v>25328</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2863,15 +3070,15 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>922</v>
+        <v>217</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="18" t="n">
-        <v>3118</v>
+      <c r="C159" s="11" t="n">
+        <v>831</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2879,15 +3086,15 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>37</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
       <c r="B161" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="18" t="n">
-        <v>1371</v>
+      <c r="C161" s="11" t="n">
+        <v>326</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2895,31 +3102,31 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B163" s="16" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B163" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="12" t="n">
-        <v>147670</v>
+      <c r="C163" s="11" t="n">
+        <v>241</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="18" t="n">
-        <v>1370</v>
+      <c r="C164" s="11" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>255</v>
+      <c r="C165" s="18" t="n">
+        <v>1176</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2927,31 +3134,31 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="167" ht="11" customHeight="true" outlineLevel="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="true" outlineLevel="3">
       <c r="B167" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="11" t="n">
-        <v>715</v>
+      <c r="C167" s="18" t="n">
+        <v>2586</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="18" t="n">
-        <v>4162</v>
+      <c r="C168" s="11" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="11" t="n">
-        <v>641</v>
+      <c r="C169" s="18" t="n">
+        <v>5556</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2959,7 +3166,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>376</v>
+        <v>845</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2967,15 +3174,15 @@
         <v>170</v>
       </c>
       <c r="C171" s="18" t="n">
-        <v>1286</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
       <c r="B172" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="11" t="n">
-        <v>816</v>
+      <c r="C172" s="18" t="n">
+        <v>1664</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2983,15 +3190,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>490</v>
+        <v>861</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="18" t="n">
-        <v>4397</v>
+      <c r="C174" s="11" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2999,7 +3206,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="18" t="n">
-        <v>1242</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3007,31 +3214,31 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>871</v>
+        <v>246</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>511</v>
+      <c r="C177" s="18" t="n">
+        <v>1306</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>400</v>
+      <c r="C178" s="18" t="n">
+        <v>1664</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="11" t="n">
-        <v>426</v>
+      <c r="C179" s="18" t="n">
+        <v>4273</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3039,7 +3246,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>332</v>
+        <v>37</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3047,7 +3254,7 @@
         <v>180</v>
       </c>
       <c r="C181" s="18" t="n">
-        <v>1251</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3055,39 +3262,39 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="183" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B183" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="183" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B183" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="18" t="n">
-        <v>1431</v>
+      <c r="C183" s="12" t="n">
+        <v>168770</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>58</v>
+      <c r="C184" s="18" t="n">
+        <v>5258</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>864</v>
+      <c r="C185" s="18" t="n">
+        <v>1536</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
       <c r="B186" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="18" t="n">
-        <v>1232</v>
+      <c r="C186" s="11" t="n">
+        <v>481</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3095,15 +3302,15 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>-77</v>
+        <v>695</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="18" t="n">
-        <v>3060</v>
+      <c r="C188" s="11" t="n">
+        <v>937</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3111,7 +3318,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="18" t="n">
-        <v>1603</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3119,7 +3326,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>89</v>
+        <v>208</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3127,23 +3334,23 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="192" ht="22" customHeight="true" outlineLevel="3">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="18" t="n">
-        <v>20736</v>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C192" s="11" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="18" t="n">
-        <v>7819</v>
+      <c r="C193" s="11" t="n">
+        <v>694</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3151,7 +3358,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>522</v>
+        <v>371</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3159,23 +3366,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>25007</v>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="true" outlineLevel="3">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="18" t="n">
-        <v>4101</v>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C196" s="11" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>298</v>
+      <c r="C197" s="18" t="n">
+        <v>3016</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3183,31 +3390,31 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>577</v>
+        <v>999</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="18" t="n">
-        <v>15017</v>
+      <c r="C199" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="11" t="n">
-        <v>296</v>
+      <c r="C200" s="18" t="n">
+        <v>1604</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>86</v>
+      <c r="C201" s="18" t="n">
+        <v>1462</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3215,7 +3422,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>444</v>
+        <v>775</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3223,23 +3430,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>161</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="11" t="n">
-        <v>556</v>
+      <c r="C204" s="18" t="n">
+        <v>1131</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>608</v>
+      <c r="C205" s="18" t="n">
+        <v>8520</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3247,55 +3454,55 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>470</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>430</v>
+      <c r="C207" s="18" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="18" t="n">
-        <v>1775</v>
+      <c r="C208" s="11" t="n">
+        <v>734</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="210" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C209" s="18" t="n">
+        <v>5923</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="true" outlineLevel="3">
       <c r="B210" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="18" t="n">
-        <v>1259</v>
+      <c r="C210" s="11" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="18" t="n">
-        <v>1218</v>
+      <c r="C211" s="11" t="n">
+        <v>346</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="11" t="n">
-        <v>701</v>
+      <c r="C212" s="18" t="n">
+        <v>2397</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3303,7 +3510,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>668</v>
+        <v>315</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3311,55 +3518,55 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>656</v>
+        <v>726</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>125</v>
+      <c r="C215" s="18" t="n">
+        <v>1408</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="18" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="217" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C216" s="11" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="217" ht="22" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
       <c r="C217" s="18" t="n">
-        <v>2238</v>
-      </c>
-    </row>
-    <row r="218" ht="11" customHeight="true" outlineLevel="3">
+        <v>15932</v>
+      </c>
+    </row>
+    <row r="218" ht="22" customHeight="true" outlineLevel="3">
       <c r="B218" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="11" t="n">
-        <v>785</v>
+      <c r="C218" s="18" t="n">
+        <v>6552</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="18" t="n">
-        <v>1830</v>
+      <c r="C219" s="11" t="n">
+        <v>313</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>-3</v>
+      <c r="C220" s="18" t="n">
+        <v>18237</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3367,15 +3574,15 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="222" ht="11" customHeight="true" outlineLevel="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="true" outlineLevel="3">
       <c r="B222" s="17" t="s">
         <v>221</v>
       </c>
       <c r="C222" s="18" t="n">
-        <v>17231</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3383,7 +3590,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>382</v>
+        <v>66</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3391,7 +3598,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>1015</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3399,7 +3606,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>529</v>
+        <v>341</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3407,15 +3614,15 @@
         <v>225</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>1166</v>
+        <v>10637</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="18" t="n">
-        <v>2683</v>
+      <c r="C227" s="11" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3423,7 +3630,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>416</v>
+        <v>689</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3431,7 +3638,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>201</v>
+        <v>238</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3439,7 +3646,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>748</v>
+        <v>402</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3447,55 +3654,55 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>395</v>
+        <v>131</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="18" t="n">
-        <v>3300</v>
+      <c r="C232" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B234" s="16" t="s">
+      <c r="C233" s="18" t="n">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B234" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="12" t="n">
-        <v>75273</v>
-      </c>
-    </row>
-    <row r="235" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C234" s="18" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="235" ht="22" customHeight="true" outlineLevel="3">
       <c r="B235" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="18" t="n">
-        <v>1430</v>
+      <c r="C235" s="11" t="n">
+        <v>304</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>462</v>
+      <c r="C236" s="18" t="n">
+        <v>1648</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="18" t="n">
-        <v>2796</v>
+      <c r="C237" s="11" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3503,39 +3710,39 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>2</v>
+        <v>262</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="18" t="n">
-        <v>1493</v>
+      <c r="C239" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="18" t="n">
-        <v>1339</v>
+      <c r="C240" s="11" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="18" t="n">
-        <v>6777</v>
+      <c r="C241" s="11" t="n">
+        <v>648</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="11" t="n">
-        <v>300</v>
+      <c r="C242" s="18" t="n">
+        <v>1918</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3543,7 +3750,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3551,7 +3758,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>398</v>
+        <v>135</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3559,7 +3766,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3567,7 +3774,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>974</v>
+        <v>616</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3575,7 +3782,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>318</v>
+        <v>399</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3583,7 +3790,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="18" t="n">
-        <v>2096</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3591,15 +3798,15 @@
         <v>248</v>
       </c>
       <c r="C249" s="18" t="n">
-        <v>1763</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="18" t="n">
-        <v>2242</v>
+      <c r="C250" s="11" t="n">
+        <v>884</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3607,7 +3814,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>1093</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3615,7 +3822,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="18" t="n">
-        <v>1565</v>
+        <v>5452</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3623,7 +3830,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>321</v>
+        <v>416</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3631,7 +3838,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>981</v>
+        <v>728</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3639,7 +3846,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="18" t="n">
-        <v>1394</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3647,7 +3854,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>434</v>
+        <v>569</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3655,23 +3862,23 @@
         <v>256</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>1906</v>
+        <v>5716</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="18" t="n">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="259" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B259" s="17" t="s">
+      <c r="C258" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B259" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="18" t="n">
-        <v>4659</v>
+      <c r="C259" s="12" t="n">
+        <v>102682</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3679,15 +3886,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="18" t="n">
-        <v>3289</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="18" t="n">
-        <v>4344</v>
+      <c r="C261" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3695,7 +3902,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>4597</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3703,7 +3910,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>1755</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3711,7 +3918,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>1913</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3719,39 +3926,39 @@
         <v>264</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>3346</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="18" t="n">
-        <v>3599</v>
+      <c r="C266" s="11" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="18" t="n">
-        <v>4605</v>
+      <c r="C267" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="18" t="n">
-        <v>2845</v>
+      <c r="C268" s="11" t="n">
+        <v>477</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="18" t="n">
-        <v>6236</v>
+      <c r="C269" s="11" t="n">
+        <v>596</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3759,55 +3966,55 @@
         <v>269</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B271" s="16" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B271" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="12" t="n">
-        <v>5857</v>
+      <c r="C271" s="11" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>272</v>
+      <c r="C272" s="18" t="n">
+        <v>3249</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>55</v>
+      <c r="C273" s="18" t="n">
+        <v>2726</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>69</v>
+      <c r="C274" s="18" t="n">
+        <v>2683</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="11" t="n">
-        <v>498</v>
+      <c r="C275" s="18" t="n">
+        <v>1240</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>78</v>
+      <c r="C276" s="18" t="n">
+        <v>2077</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3815,23 +4022,23 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>384</v>
+        <v>906</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="11" t="n">
-        <v>16</v>
+      <c r="C278" s="18" t="n">
+        <v>1840</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>194</v>
+      <c r="C279" s="18" t="n">
+        <v>1677</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3846,120 +4053,120 @@
       <c r="B281" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>569</v>
+      <c r="C281" s="18" t="n">
+        <v>2997</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="11" t="n">
-        <v>661</v>
+      <c r="C282" s="18" t="n">
+        <v>4575</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>345</v>
+      <c r="C283" s="18" t="n">
+        <v>6684</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>258</v>
+      <c r="C284" s="18" t="n">
+        <v>3604</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>60</v>
+      <c r="C285" s="18" t="n">
+        <v>4695</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="11" t="n">
-        <v>455</v>
+      <c r="C286" s="18" t="n">
+        <v>7196</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="11" t="n">
-        <v>30</v>
+      <c r="C287" s="18" t="n">
+        <v>2907</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="11" t="n">
-        <v>960</v>
+      <c r="C288" s="18" t="n">
+        <v>3194</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="11" t="n">
-        <v>22</v>
+      <c r="C289" s="18" t="n">
+        <v>5361</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>557</v>
+      <c r="C290" s="18" t="n">
+        <v>3403</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="11" t="n">
-        <v>7</v>
+      <c r="C291" s="18" t="n">
+        <v>6431</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B293" s="16" t="s">
+      <c r="C292" s="18" t="n">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B293" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="12" t="n">
-        <v>63144</v>
+      <c r="C293" s="18" t="n">
+        <v>8668</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="11" t="n">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B295" s="17" t="s">
+      <c r="C294" s="18" t="n">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B295" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="11" t="n">
-        <v>990</v>
+      <c r="C295" s="12" t="n">
+        <v>5698</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -3967,7 +4174,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>340</v>
+        <v>849</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3975,7 +4182,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3983,7 +4190,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>269</v>
+        <v>32</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3991,7 +4198,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>151</v>
+        <v>481</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3999,7 +4206,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>775</v>
+        <v>78</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4007,7 +4214,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>604</v>
+        <v>32</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4015,15 +4222,15 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="17" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>215</v>
+        <v>171</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4031,7 +4238,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>451</v>
+        <v>627</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4039,7 +4246,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>188</v>
+        <v>108</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4047,15 +4254,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>657</v>
+        <v>32</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="18" t="n">
-        <v>1547</v>
+      <c r="C307" s="11" t="n">
+        <v>797</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4063,71 +4270,71 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="true" outlineLevel="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="18" t="n">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C311" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="17" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="18" t="n">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="314" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C313" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="17" t="s">
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="315" ht="22" customHeight="true" outlineLevel="3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="17" t="s">
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="17" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4135,7 +4342,7 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>657</v>
+        <v>20</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4143,7 +4350,7 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4151,31 +4358,31 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B320" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B320" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="11" t="n">
-        <v>148</v>
+      <c r="C320" s="12" t="n">
+        <v>65088</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="18" t="n">
-        <v>2601</v>
+      <c r="C321" s="11" t="n">
+        <v>704</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="18" t="n">
-        <v>2570</v>
+      <c r="C322" s="11" t="n">
+        <v>762</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4183,15 +4390,15 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>765</v>
+        <v>376</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="18" t="n">
-        <v>1960</v>
+      <c r="C324" s="11" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4199,23 +4406,23 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>741</v>
+        <v>147</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="18" t="n">
-        <v>1940</v>
+      <c r="C326" s="11" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="18" t="n">
-        <v>4702</v>
+      <c r="C327" s="11" t="n">
+        <v>516</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4223,31 +4430,31 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>7</v>
+        <v>535</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="18" t="n">
-        <v>3628</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C329" s="11" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="18" t="n">
-        <v>21479</v>
-      </c>
-    </row>
-    <row r="331" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C330" s="11" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="331" ht="22" customHeight="true" outlineLevel="3">
       <c r="B331" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="18" t="n">
-        <v>1151</v>
+      <c r="C331" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4255,23 +4462,23 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>194</v>
+        <v>104</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="18" t="n">
-        <v>7716</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B334" s="16" t="s">
+      <c r="C333" s="11" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B334" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="12" t="n">
-        <v>69209</v>
+      <c r="C334" s="18" t="n">
+        <v>1269</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4279,23 +4486,23 @@
         <v>334</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>1745</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="11" t="n">
-        <v>281</v>
+      <c r="C336" s="18" t="n">
+        <v>1515</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="18" t="n">
-        <v>1507</v>
+      <c r="C337" s="11" t="n">
+        <v>636</v>
       </c>
     </row>
     <row r="338" ht="22" customHeight="true" outlineLevel="3">
@@ -4303,63 +4510,63 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>303</v>
+        <v>633</v>
       </c>
     </row>
     <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="18" t="n">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="340" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C339" s="11" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="true" outlineLevel="3">
       <c r="B340" s="17" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="17" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="18" t="n">
-        <v>2786</v>
-      </c>
-    </row>
-    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C343" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="17" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="true" outlineLevel="3">
       <c r="B345" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="18" t="n">
-        <v>1092</v>
+      <c r="C345" s="11" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4367,7 +4574,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4375,7 +4582,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4383,7 +4590,7 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>754</v>
+        <v>828</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4391,7 +4598,7 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>295</v>
+        <v>628</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
@@ -4399,23 +4606,23 @@
         <v>349</v>
       </c>
       <c r="C350" s="18" t="n">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
       <c r="B351" s="17" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>703</v>
+        <v>264</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>926</v>
+      <c r="C352" s="18" t="n">
+        <v>6394</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4423,7 +4630,7 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>442</v>
+        <v>264</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4431,7 +4638,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="18" t="n">
-        <v>1155</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4439,111 +4646,111 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>764</v>
+        <v>582</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>784</v>
+      <c r="C356" s="18" t="n">
+        <v>1321</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="11" t="n">
-        <v>130</v>
+      <c r="C357" s="18" t="n">
+        <v>2849</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="18" t="n">
-        <v>2529</v>
+      <c r="C358" s="11" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="18" t="n">
-        <v>2126</v>
+      <c r="C359" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
       <c r="B360" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="11" t="n">
-        <v>172</v>
+      <c r="C360" s="18" t="n">
+        <v>6011</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="11" t="n">
-        <v>57</v>
+      <c r="C361" s="18" t="n">
+        <v>15429</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="11" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C362" s="18" t="n">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="17" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>38</v>
+        <v>194</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="11" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B365" s="17" t="s">
+      <c r="C364" s="18" t="n">
+        <v>8688</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B365" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="11" t="n">
-        <v>660</v>
+      <c r="C365" s="12" t="n">
+        <v>65940</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C366" s="18" t="n">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="17" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>843</v>
+        <v>63</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="11" t="n">
-        <v>270</v>
+      <c r="C368" s="18" t="n">
+        <v>4390</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4551,23 +4758,23 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="18" t="n">
-        <v>11999</v>
+      <c r="C370" s="11" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="11" t="n">
-        <v>450</v>
+      <c r="C371" s="18" t="n">
+        <v>3967</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4575,7 +4782,7 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>299</v>
+        <v>880</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
@@ -4583,7 +4790,7 @@
         <v>372</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>17694</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4591,7 +4798,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>7860</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4599,7 +4806,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>2823</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4607,7 +4814,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>10</v>
+        <v>352</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4615,15 +4822,15 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B378" s="16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B378" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="14" t="n">
-        <v>880</v>
+      <c r="C378" s="11" t="n">
+        <v>302</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
@@ -4631,15 +4838,15 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="11" t="n">
-        <v>85</v>
+      <c r="C380" s="18" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
@@ -4647,7 +4854,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4655,15 +4862,15 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B383" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="12" t="n">
-        <v>61838</v>
+      <c r="C383" s="11" t="n">
+        <v>314</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4671,7 +4878,7 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>24</v>
+        <v>722</v>
       </c>
     </row>
     <row r="385" ht="11" customHeight="true" outlineLevel="3">
@@ -4679,47 +4886,47 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="17" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>3362</v>
-      </c>
-    </row>
-    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
       <c r="B387" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="C387" s="18" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="388" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C387" s="11" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C388" s="18" t="n">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="17" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>93</v>
+        <v>789</v>
       </c>
     </row>
     <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="18" t="n">
-        <v>3128</v>
+      <c r="C390" s="11" t="n">
+        <v>757</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4727,23 +4934,23 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
       <c r="B392" s="17" t="s">
         <v>391</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>5233</v>
-      </c>
-    </row>
-    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
       <c r="B393" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="11" t="n">
-        <v>618</v>
+      <c r="C393" s="18" t="n">
+        <v>3886</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
@@ -4751,7 +4958,7 @@
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="395" ht="11" customHeight="true" outlineLevel="3">
@@ -4759,23 +4966,23 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
       <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="18" t="n">
-        <v>2624</v>
+      <c r="C396" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="18" t="n">
-        <v>1760</v>
+      <c r="C397" s="11" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4783,7 +4990,7 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>418</v>
+        <v>217</v>
       </c>
     </row>
     <row r="399" ht="22" customHeight="true" outlineLevel="3">
@@ -4791,15 +4998,15 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="401" ht="22" customHeight="true" outlineLevel="3">
@@ -4807,15 +5014,15 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
       <c r="B402" s="17" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>961</v>
+        <v>77</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4823,127 +5030,127 @@
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="404" ht="22" customHeight="true" outlineLevel="3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
       <c r="B404" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C404" s="18" t="n">
+        <v>9191</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
       <c r="B405" s="17" t="s">
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="407" ht="22" customHeight="true" outlineLevel="3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="11" t="n">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C407" s="18" t="n">
+        <v>11063</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="C408" s="18" t="n">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C408" s="11" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
       <c r="B409" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="C409" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C409" s="18" t="n">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
       <c r="B410" s="17" t="s">
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
       <c r="B411" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="11" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C411" s="18" t="n">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="412" ht="11" customHeight="true" outlineLevel="3">
       <c r="B412" s="17" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="17" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="413" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B413" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="C413" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C413" s="14" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="3">
       <c r="B414" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="18" t="n">
-        <v>3797</v>
-      </c>
-    </row>
-    <row r="415" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C414" s="11" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
       <c r="B415" s="17" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
       <c r="B416" s="17" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="3">
       <c r="B417" s="17" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B418" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B418" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="C418" s="11" t="n">
-        <v>26</v>
+      <c r="C418" s="12" t="n">
+        <v>279056</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -4951,7 +5158,7 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>66</v>
+        <v>214</v>
       </c>
     </row>
     <row r="420" ht="11" customHeight="true" outlineLevel="3">
@@ -4959,23 +5166,23 @@
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="3">
       <c r="B421" s="17" t="s">
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
       <c r="B422" s="17" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>23</v>
+        <v>105</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="true" outlineLevel="3">
@@ -4983,7 +5190,7 @@
         <v>422</v>
       </c>
       <c r="C423" s="18" t="n">
-        <v>1416</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="true" outlineLevel="3">
@@ -4991,15 +5198,15 @@
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="425" ht="22" customHeight="true" outlineLevel="3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="425" ht="33" customHeight="true" outlineLevel="3">
       <c r="B425" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="C425" s="11" t="n">
-        <v>72</v>
+      <c r="C425" s="18" t="n">
+        <v>20698</v>
       </c>
     </row>
     <row r="426" ht="22" customHeight="true" outlineLevel="3">
@@ -5007,7 +5214,7 @@
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>260</v>
+        <v>189</v>
       </c>
     </row>
     <row r="427" ht="22" customHeight="true" outlineLevel="3">
@@ -5015,23 +5222,23 @@
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>136</v>
+        <v>32</v>
       </c>
     </row>
     <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="18" t="n">
-        <v>3914</v>
+      <c r="C428" s="11" t="n">
+        <v>178</v>
       </c>
     </row>
     <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="C429" s="11" t="n">
-        <v>7</v>
+      <c r="C429" s="18" t="n">
+        <v>4940</v>
       </c>
     </row>
     <row r="430" ht="11" customHeight="true" outlineLevel="3">
@@ -5039,47 +5246,47 @@
         <v>429</v>
       </c>
       <c r="C430" s="18" t="n">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="431" ht="11" customHeight="true" outlineLevel="3">
       <c r="B431" s="17" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
       <c r="B432" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="C432" s="11" t="n">
-        <v>22</v>
+      <c r="C432" s="18" t="n">
+        <v>19377</v>
       </c>
     </row>
     <row r="433" ht="22" customHeight="true" outlineLevel="3">
       <c r="B433" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="C433" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C433" s="18" t="n">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
       <c r="B434" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="C434" s="18" t="n">
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C434" s="11" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="435" ht="22" customHeight="true" outlineLevel="3">
       <c r="B435" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C435" s="11" t="n">
-        <v>66</v>
+      <c r="C435" s="18" t="n">
+        <v>25795</v>
       </c>
     </row>
     <row r="436" ht="11" customHeight="true" outlineLevel="3">
@@ -5087,7 +5294,7 @@
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>32</v>
+        <v>781</v>
       </c>
     </row>
     <row r="437" ht="11" customHeight="true" outlineLevel="3">
@@ -5095,39 +5302,39 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>60</v>
+        <v>177</v>
       </c>
     </row>
     <row r="438" ht="11" customHeight="true" outlineLevel="3">
       <c r="B438" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="18" t="n">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C438" s="11" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="439" ht="11" customHeight="true" outlineLevel="3">
       <c r="B439" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="C439" s="11" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C439" s="18" t="n">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="440" ht="11" customHeight="true" outlineLevel="3">
       <c r="B440" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="C440" s="11" t="n">
-        <v>2</v>
+      <c r="C440" s="18" t="n">
+        <v>1650</v>
       </c>
     </row>
     <row r="441" ht="11" customHeight="true" outlineLevel="3">
       <c r="B441" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="C441" s="18" t="n">
-        <v>4385</v>
+      <c r="C441" s="11" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="442" ht="22" customHeight="true" outlineLevel="3">
@@ -5135,71 +5342,71 @@
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="443" ht="11" customHeight="true" outlineLevel="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="true" outlineLevel="3">
       <c r="B443" s="17" t="s">
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="444" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="444" ht="22" customHeight="true" outlineLevel="3">
       <c r="B444" s="17" t="s">
         <v>443</v>
       </c>
       <c r="C444" s="18" t="n">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+        <v>7810</v>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="true" outlineLevel="3">
       <c r="B445" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="C445" s="11" t="n">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="446" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C445" s="18" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
       <c r="B446" s="17" t="s">
         <v>445</v>
       </c>
       <c r="C446" s="11" t="n">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="447" ht="11" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
       <c r="B447" s="17" t="s">
         <v>446</v>
       </c>
       <c r="C447" s="11" t="n">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="448" ht="22" customHeight="true" outlineLevel="3">
       <c r="B448" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="C448" s="18" t="n">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="449" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C448" s="11" t="n">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
       <c r="B449" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="C449" s="11" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C449" s="18" t="n">
+        <v>24111</v>
+      </c>
+    </row>
+    <row r="450" ht="22" customHeight="true" outlineLevel="3">
       <c r="B450" s="17" t="s">
         <v>449</v>
       </c>
       <c r="C450" s="18" t="n">
-        <v>3946</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="true" outlineLevel="3">
@@ -5207,15 +5414,551 @@
         <v>450</v>
       </c>
       <c r="C451" s="11" t="n">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="452" ht="22" customHeight="true" outlineLevel="3">
       <c r="B452" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="C452" s="18" t="n">
-        <v>1828</v>
+      <c r="C452" s="11" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="453" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B453" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="18" t="n">
+        <v>13875</v>
+      </c>
+    </row>
+    <row r="454" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B454" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B455" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B456" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B457" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="18" t="n">
+        <v>17414</v>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B458" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="11" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="459" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B459" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B460" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="11" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B461" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="18" t="n">
+        <v>6184</v>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B462" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B463" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="18" t="n">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B464" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="18" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B465" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="11" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B466" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="18" t="n">
+        <v>18028</v>
+      </c>
+    </row>
+    <row r="467" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B467" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B468" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B469" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="470" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B470" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="18" t="n">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B471" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="11" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="11" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="473" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B473" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="474" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B474" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="475" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B475" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="11" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="476" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B476" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B477" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="C477" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B478" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="C478" s="11" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B479" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="C479" s="11" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B480" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="C480" s="11" t="n">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B481" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="C481" s="11" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="482" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B482" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="C482" s="18" t="n">
+        <v>19358</v>
+      </c>
+    </row>
+    <row r="483" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B483" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="C483" s="18" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="484" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B484" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="C484" s="11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="485" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B485" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="C485" s="18" t="n">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="486" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B486" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="C486" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B487" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="C487" s="18" t="n">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="488" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B488" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="C488" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="489" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B489" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C489" s="18" t="n">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="490" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B490" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="C490" s="18" t="n">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="491" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B491" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C491" s="18" t="n">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="492" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B492" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="C492" s="11" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="493" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B493" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="C493" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="494" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B494" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="C494" s="18" t="n">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="495" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B495" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="C495" s="18" t="n">
+        <v>5035</v>
+      </c>
+    </row>
+    <row r="496" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B496" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="C496" s="18" t="n">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="497" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B497" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="C497" s="11" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="498" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B498" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C498" s="18" t="n">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="499" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B499" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="C499" s="18" t="n">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="500" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B500" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="C500" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B501" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="C501" s="18" t="n">
+        <v>5035</v>
+      </c>
+    </row>
+    <row r="502" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B502" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="C502" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="503" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B503" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="C503" s="18" t="n">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="504" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B504" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="C504" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="505" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B505" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="C505" s="11" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="506" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B506" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="C506" s="18" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="507" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B507" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="C507" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="508" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B508" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="C508" s="11" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B509" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="C509" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="510" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B510" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="C510" s="11" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="511" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B511" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="C511" s="18" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="512" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B512" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="C512" s="11" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="513" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B513" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="C513" s="11" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="514" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B514" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="C514" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="515" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B515" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="C515" s="12" t="n">
+        <v>19895</v>
+      </c>
+    </row>
+    <row r="516" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B516" s="20" t="s">
+        <v>515</v>
+      </c>
+      <c r="C516" s="18" t="n">
+        <v>10535</v>
+      </c>
+    </row>
+    <row r="517" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B517" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="C517" s="11" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="518" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B518" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="C518" s="18" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="519" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B519" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="C519" s="18" t="n">
+        <v>1320</v>
       </c>
     </row>
   </sheetData>
